--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -129,19 +129,19 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -153,7 +153,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,7 +540,7 @@
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>모델명</t>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9170,7 +9173,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G136" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9193,7 +9196,7 @@
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr"/>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="N136" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9203,11 +9206,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
-      <c r="P136" s="5" t="inlineStr">
-        <is>
-          <t>국내 판매 종료 연도 자료 상충(2022~2024)</t>
-        </is>
-      </c>
+      <c r="P136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -9240,7 +9239,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G137" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9263,7 +9262,7 @@
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr"/>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="N137" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9273,11 +9272,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
-      <c r="P137" s="5" t="inlineStr">
-        <is>
-          <t>국내 판매 종료 연도 자료 상충(2022~2024)</t>
-        </is>
-      </c>
+      <c r="P137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -9310,7 +9305,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G138" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9333,7 +9328,7 @@
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr"/>
-      <c r="N138" s="5" t="inlineStr">
+      <c r="N138" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9343,11 +9338,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
-      <c r="P138" s="5" t="inlineStr">
-        <is>
-          <t>국내 판매 종료 연도 자료 상충(2022~2024)</t>
-        </is>
-      </c>
+      <c r="P138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -9380,7 +9371,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G139" s="5" t="inlineStr">
+      <c r="G139" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9403,7 +9394,7 @@
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr"/>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="N139" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9413,11 +9404,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769), autotribune(국내 11년간 1,941대 판매 후 단종)</t>
         </is>
       </c>
-      <c r="P139" s="5" t="inlineStr">
-        <is>
-          <t>국내 판매 종료 연도 자료 상충(2022~2024)</t>
-        </is>
-      </c>
+      <c r="P139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
@@ -9485,7 +9472,7 @@
       </c>
       <c r="P140" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9542,7 @@
       </c>
       <c r="P141" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9612,7 @@
       </c>
       <c r="P142" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9682,7 @@
       </c>
       <c r="P143" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9752,7 @@
       </c>
       <c r="P144" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9822,7 @@
       </c>
       <c r="P145" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9888,7 @@
       </c>
       <c r="P146" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9954,7 @@
       </c>
       <c r="P147" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10020,7 @@
       </c>
       <c r="P148" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10086,7 @@
       </c>
       <c r="P149" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10152,7 @@
       </c>
       <c r="P150" s="5" t="inlineStr">
         <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
         </is>
       </c>
     </row>
@@ -12742,26 +12729,26 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+      <c r="G190" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H190" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I190" s="11" t="inlineStr"/>
       <c r="J190" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K190" s="11" t="inlineStr"/>
       <c r="L190" s="11" t="n"/>
       <c r="M190" s="11" t="inlineStr"/>
-      <c r="N190" s="5" t="inlineStr">
+      <c r="N190" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -12771,11 +12758,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P190" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -12808,26 +12791,26 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+      <c r="G191" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I191" s="11" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K191" s="11" t="inlineStr"/>
       <c r="L191" s="11" t="n"/>
       <c r="M191" s="11" t="inlineStr"/>
-      <c r="N191" s="5" t="inlineStr">
+      <c r="N191" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -12837,11 +12820,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P191" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -12874,7 +12853,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G192" s="5" t="inlineStr">
+      <c r="G192" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -12887,13 +12866,17 @@
       <c r="I192" s="11" t="inlineStr"/>
       <c r="J192" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K192" s="11" t="inlineStr"/>
-      <c r="L192" s="11" t="n"/>
+      <c r="L192" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M192" s="11" t="inlineStr"/>
-      <c r="N192" s="5" t="inlineStr">
+      <c r="N192" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -12903,11 +12886,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P192" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -12940,7 +12919,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G193" s="5" t="inlineStr">
+      <c r="G193" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -12953,13 +12932,17 @@
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K193" s="11" t="inlineStr"/>
-      <c r="L193" s="11" t="n"/>
+      <c r="L193" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M193" s="11" t="inlineStr"/>
-      <c r="N193" s="5" t="inlineStr">
+      <c r="N193" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -12969,11 +12952,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P193" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -13006,7 +12985,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G194" s="5" t="inlineStr">
+      <c r="G194" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -13019,13 +12998,17 @@
       <c r="I194" s="11" t="inlineStr"/>
       <c r="J194" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K194" s="11" t="inlineStr"/>
-      <c r="L194" s="11" t="n"/>
+      <c r="L194" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M194" s="11" t="inlineStr"/>
-      <c r="N194" s="5" t="inlineStr">
+      <c r="N194" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -13035,11 +13018,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P194" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
@@ -13072,7 +13051,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G195" s="5" t="inlineStr">
+      <c r="G195" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -13085,13 +13064,17 @@
       <c r="I195" s="11" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K195" s="11" t="inlineStr"/>
-      <c r="L195" s="11" t="n"/>
+      <c r="L195" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M195" s="11" t="inlineStr"/>
-      <c r="N195" s="5" t="inlineStr">
+      <c r="N195" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -13101,11 +13084,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P195" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
@@ -13138,7 +13117,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G196" s="5" t="inlineStr">
+      <c r="G196" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -13151,13 +13130,17 @@
       <c r="I196" s="11" t="inlineStr"/>
       <c r="J196" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K196" s="11" t="inlineStr"/>
-      <c r="L196" s="11" t="n"/>
+      <c r="L196" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M196" s="11" t="inlineStr"/>
-      <c r="N196" s="5" t="inlineStr">
+      <c r="N196" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -13167,11 +13150,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
-      <c r="P196" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
@@ -13204,7 +13183,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G197" s="5" t="inlineStr">
+      <c r="G197" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
@@ -13217,13 +13196,17 @@
       <c r="I197" s="11" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>DWO5[자료 상충], HU100[자료 상충]</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K197" s="11" t="inlineStr"/>
-      <c r="L197" s="11" t="n"/>
+      <c r="L197" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M197" s="11" t="inlineStr"/>
-      <c r="N197" s="5" t="inlineStr">
+      <c r="N197" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
@@ -13233,11 +13216,7 @@
           <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz), namu.wiki(2018.5 생산 중단, 재고 판매 후 단종)</t>
         </is>
       </c>
-      <c r="P197" s="5" t="inlineStr">
-        <is>
-          <t>국내 스마트키 적용·품번 자료 없음, 블레이드 표기 상충(DWO5/HU100)</t>
-        </is>
-      </c>
+      <c r="P197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
@@ -15362,170 +15341,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -168,6 +168,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -13244,7 +13247,7 @@
       <c r="K198" s="11" t="inlineStr"/>
       <c r="L198" s="11" t="inlineStr"/>
       <c r="M198" s="11" t="inlineStr"/>
-      <c r="N198" s="4" t="inlineStr"/>
+      <c r="N198" s="15" t="inlineStr"/>
       <c r="O198" s="11" t="inlineStr">
         <is>
           <t>검색 결과(2023.8 바오준 530 기반 2세대 캡티바는 중남미·동남아 판매, 국내 미출시)</t>
@@ -13752,7 +13755,7 @@
       <c r="K206" s="11" t="inlineStr"/>
       <c r="L206" s="11" t="inlineStr"/>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr"/>
+      <c r="N206" s="15" t="inlineStr"/>
       <c r="O206" s="11" t="inlineStr">
         <is>
           <t>ebn.co.kr(한국GM 이쿼녹스 EV 출시 계획 최종 철회), bloter(1년째 출시 약속 못 지킴), sisajournal-e(2024.9 환경부 인증)</t>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'쉐보레(GM대우) 트랜스폰더 DB'!$A$1:$P$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'쉐보레(GM대우) 트랜스폰더 DB'!$A$1:$P$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P229"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1420,7 +1423,7 @@
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>해당 없음[2013년형], ID46(PCF7941E)[2014년형~]</t>
         </is>
@@ -1439,7 +1442,7 @@
       <c r="K18" s="11" t="inlineStr"/>
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="11" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>미적용[2013년형], 트랜스폰더 이모빌라이저[2014년형~]</t>
         </is>
@@ -1449,11 +1452,7 @@
           <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>2014년형(2013 하반기)부터 이모빌라이저 — 연식만으로 구분 불가</t>
-        </is>
-      </c>
+      <c r="P18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -5450,7 +5449,7 @@
       <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" s="14" t="inlineStr">
         <is>
           <t>해당 없음[2006년형], ID60(4D60)[2007년형~]</t>
         </is>
@@ -5465,7 +5464,7 @@
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="N79" s="14" t="inlineStr">
         <is>
           <t>미적용[2006년형], 트랜스폰더 이모빌라이저[2007년형, 2006.11~]</t>
         </is>
@@ -5475,11 +5474,7 @@
           <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
         </is>
       </c>
-      <c r="P79" s="5" t="inlineStr">
-        <is>
-          <t>2006년형 미적용·2007년형(2006.11~) 적용 — 칩은 같은 차 수출형(에피카) 4D60 기준</t>
-        </is>
-      </c>
+      <c r="P79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -13229,35 +13224,63 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 2세대, 리뱃지)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>2024 (국내 미출시)</t>
-        </is>
-      </c>
-      <c r="D198" s="3" t="inlineStr"/>
-      <c r="E198" s="3" t="inlineStr"/>
-      <c r="F198" s="3" t="inlineStr"/>
-      <c r="G198" s="4" t="inlineStr"/>
-      <c r="H198" s="11" t="inlineStr"/>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
+        </is>
+      </c>
+      <c r="H198" s="11" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="I198" s="11" t="inlineStr"/>
-      <c r="J198" s="11" t="inlineStr"/>
+      <c r="J198" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K198" s="11" t="inlineStr"/>
-      <c r="L198" s="11" t="inlineStr"/>
+      <c r="L198" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
       <c r="M198" s="11" t="inlineStr"/>
-      <c r="N198" s="15" t="inlineStr"/>
+      <c r="N198" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
+        </is>
+      </c>
       <c r="O198" s="11" t="inlineStr">
         <is>
-          <t>검색 결과(2023.8 바오준 530 기반 2세대 캡티바는 중남미·동남아 판매, 국내 미출시)</t>
-        </is>
-      </c>
-      <c r="P198" s="4" t="inlineStr">
-        <is>
-          <t>국내 미출시</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P198" s="11" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
@@ -13272,7 +13295,7 @@
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -13320,7 +13343,7 @@
       </c>
       <c r="O199" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
         </is>
       </c>
       <c r="P199" s="11" t="inlineStr"/>
@@ -13338,7 +13361,7 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -13404,7 +13427,7 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -13452,7 +13475,7 @@
       </c>
       <c r="O201" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
         </is>
       </c>
       <c r="P201" s="11" t="inlineStr"/>
@@ -13470,7 +13493,7 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -13518,7 +13541,7 @@
       </c>
       <c r="O202" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
         </is>
       </c>
       <c r="P202" s="11" t="inlineStr"/>
@@ -13536,7 +13559,7 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -13554,7 +13577,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G203" s="11" t="inlineStr">
+      <c r="G203" s="5" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13577,17 +13600,21 @@
         </is>
       </c>
       <c r="M203" s="11" t="inlineStr"/>
-      <c r="N203" s="11" t="inlineStr">
+      <c r="N203" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O203" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
-        </is>
-      </c>
-      <c r="P203" s="11" t="inlineStr"/>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+        </is>
+      </c>
+      <c r="P203" s="5" t="inlineStr">
+        <is>
+          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
@@ -13602,7 +13629,7 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -13650,7 +13677,7 @@
       </c>
       <c r="O204" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
         </is>
       </c>
       <c r="P204" s="5" t="inlineStr">
@@ -13667,12 +13694,12 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -13690,7 +13717,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr">
+      <c r="G205" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13709,25 +13736,21 @@
       <c r="K205" s="11" t="inlineStr"/>
       <c r="L205" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M205" s="11" t="inlineStr"/>
-      <c r="N205" s="5" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N205" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
-        </is>
-      </c>
-      <c r="P205" s="5" t="inlineStr">
-        <is>
-          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
-        </is>
-      </c>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P205" s="11" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -13737,35 +13760,63 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 EV (쉐보레)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>2024 (국내 미출시)</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr"/>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="4" t="inlineStr"/>
-      <c r="H206" s="11" t="inlineStr"/>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
+        </is>
+      </c>
+      <c r="H206" s="11" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
       <c r="I206" s="11" t="inlineStr"/>
-      <c r="J206" s="11" t="inlineStr"/>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K206" s="11" t="inlineStr"/>
-      <c r="L206" s="11" t="inlineStr"/>
+      <c r="L206" s="11" t="inlineStr">
+        <is>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
+        </is>
+      </c>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="15" t="inlineStr"/>
+      <c r="N206" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+        </is>
+      </c>
       <c r="O206" s="11" t="inlineStr">
         <is>
-          <t>ebn.co.kr(한국GM 이쿼녹스 EV 출시 계획 최종 철회), bloter(1년째 출시 약속 못 지킴), sisajournal-e(2024.9 환경부 인증)</t>
-        </is>
-      </c>
-      <c r="P206" s="4" t="inlineStr">
-        <is>
-          <t>국내 미출시(인증 후 출시 철회)</t>
-        </is>
-      </c>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
+        </is>
+      </c>
+      <c r="P206" s="11" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -13780,7 +13831,7 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -13798,7 +13849,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G207" s="11" t="inlineStr">
+      <c r="G207" s="5" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13817,21 +13868,25 @@
       <c r="K207" s="11" t="inlineStr"/>
       <c r="L207" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M207" s="11" t="inlineStr"/>
-      <c r="N207" s="11" t="inlineStr">
+      <c r="N207" s="5" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P207" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+        </is>
+      </c>
+      <c r="P207" s="5" t="inlineStr">
+        <is>
+          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -13846,7 +13901,7 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -13864,7 +13919,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G208" s="11" t="inlineStr">
+      <c r="G208" s="5" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13883,21 +13938,25 @@
       <c r="K208" s="11" t="inlineStr"/>
       <c r="L208" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M208" s="11" t="inlineStr"/>
-      <c r="N208" s="11" t="inlineStr">
+      <c r="N208" s="5" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O208" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
-        </is>
-      </c>
-      <c r="P208" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+        </is>
+      </c>
+      <c r="P208" s="5" t="inlineStr">
+        <is>
+          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -13912,7 +13971,7 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -13982,7 +14041,7 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -14052,7 +14111,7 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -14100,7 +14159,7 @@
       </c>
       <c r="O211" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
         </is>
       </c>
       <c r="P211" s="5" t="inlineStr">
@@ -14117,22 +14176,22 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D212" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
@@ -14140,9 +14199,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H212" s="11" t="inlineStr">
@@ -14159,25 +14218,21 @@
       <c r="K212" s="11" t="inlineStr"/>
       <c r="L212" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M212" s="11" t="inlineStr"/>
-      <c r="N212" s="5" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O212" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P212" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P212" s="11" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -14187,22 +14242,22 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
-        </is>
-      </c>
-      <c r="D213" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
@@ -14210,9 +14265,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -14229,25 +14284,21 @@
       <c r="K213" s="11" t="inlineStr"/>
       <c r="L213" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M213" s="11" t="inlineStr"/>
-      <c r="N213" s="5" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N213" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O213" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
-        </is>
-      </c>
-      <c r="P213" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
+        </is>
+      </c>
+      <c r="P213" s="11" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -14262,7 +14313,7 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
@@ -14310,7 +14361,7 @@
       </c>
       <c r="O214" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
         </is>
       </c>
       <c r="P214" s="11" t="inlineStr"/>
@@ -14328,7 +14379,7 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
@@ -14376,7 +14427,7 @@
       </c>
       <c r="O215" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
         </is>
       </c>
       <c r="P215" s="11" t="inlineStr"/>
@@ -14389,7 +14440,7 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C216" s="11" t="inlineStr">
@@ -14412,7 +14463,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G216" s="11" t="inlineStr">
+      <c r="G216" s="14" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -14431,21 +14482,21 @@
       <c r="K216" s="11" t="inlineStr"/>
       <c r="L216" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M216" s="11" t="inlineStr"/>
-      <c r="N216" s="11" t="inlineStr">
+      <c r="N216" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
       <c r="O216" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
-        </is>
-      </c>
-      <c r="P216" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P216" s="14" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -14455,12 +14506,12 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
@@ -14478,7 +14529,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G217" s="11" t="inlineStr">
+      <c r="G217" s="14" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -14497,21 +14548,21 @@
       <c r="K217" s="11" t="inlineStr"/>
       <c r="L217" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M217" s="11" t="inlineStr"/>
-      <c r="N217" s="11" t="inlineStr">
+      <c r="N217" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
       <c r="O217" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
-        </is>
-      </c>
-      <c r="P217" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
@@ -14526,7 +14577,7 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
@@ -14544,7 +14595,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G218" s="5" t="inlineStr">
+      <c r="G218" s="14" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -14567,7 +14618,7 @@
         </is>
       </c>
       <c r="M218" s="11" t="inlineStr"/>
-      <c r="N218" s="5" t="inlineStr">
+      <c r="N218" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -14577,11 +14628,7 @@
           <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
         </is>
       </c>
-      <c r="P218" s="5" t="inlineStr">
-        <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
-        </is>
-      </c>
+      <c r="P218" s="14" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="inlineStr">
@@ -14591,22 +14638,22 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D219" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -14614,44 +14661,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I219" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, ILCO B119</t>
         </is>
       </c>
       <c r="K219" s="11" t="inlineStr"/>
-      <c r="L219" s="11" t="inlineStr">
-        <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
+      <c r="L219" s="11" t="inlineStr"/>
       <c r="M219" s="11" t="inlineStr"/>
-      <c r="N219" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N219" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O219" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P219" s="5" t="inlineStr">
-        <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
-        </is>
-      </c>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P219" s="11" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
@@ -14661,22 +14704,22 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D220" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -14684,44 +14727,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G220" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I220" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J220" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, ILCO B119</t>
         </is>
       </c>
       <c r="K220" s="11" t="inlineStr"/>
-      <c r="L220" s="11" t="inlineStr">
-        <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
+      <c r="L220" s="11" t="inlineStr"/>
       <c r="M220" s="11" t="inlineStr"/>
-      <c r="N220" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N220" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O220" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P220" s="5" t="inlineStr">
-        <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
-        </is>
-      </c>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P220" s="11" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
@@ -14731,22 +14770,22 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D221" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
@@ -14754,44 +14793,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I221" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I221" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, ILCO B119</t>
         </is>
       </c>
       <c r="K221" s="11" t="inlineStr"/>
-      <c r="L221" s="11" t="inlineStr">
-        <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
+      <c r="L221" s="11" t="inlineStr"/>
       <c r="M221" s="11" t="inlineStr"/>
-      <c r="N221" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N221" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O221" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P221" s="5" t="inlineStr">
-        <is>
-          <t>한국GM 공식 판매 자료 없음(수입업체 판매만)</t>
-        </is>
-      </c>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P221" s="11" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
@@ -14806,7 +14841,7 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
@@ -14854,7 +14889,7 @@
       </c>
       <c r="O222" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
         </is>
       </c>
       <c r="P222" s="11" t="inlineStr"/>
@@ -14872,7 +14907,7 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
@@ -14938,17 +14973,17 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D224" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -14958,12 +14993,12 @@
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>ID46[Extended]</t>
+          <t>ID46[2세대, ~2024.4], ID49[3세대, 2024.7~]</t>
         </is>
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I224" s="11" t="inlineStr">
@@ -14977,16 +15012,20 @@
         </is>
       </c>
       <c r="K224" s="11" t="inlineStr"/>
-      <c r="L224" s="11" t="inlineStr"/>
+      <c r="L224" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
       <c r="M224" s="11" t="inlineStr"/>
       <c r="N224" s="11" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저</t>
+          <t>트랜스폰더 이모빌라이저[2세대], PEPS[3세대]</t>
         </is>
       </c>
       <c r="O224" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
         </is>
       </c>
       <c r="P224" s="11" t="inlineStr"/>
@@ -15004,17 +15043,17 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
@@ -15024,35 +15063,35 @@
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>ID46[Extended]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I225" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="inlineStr"/>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K225" s="11" t="inlineStr"/>
-      <c r="L225" s="11" t="inlineStr"/>
+      <c r="L225" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
       <c r="M225" s="11" t="inlineStr"/>
       <c r="N225" s="11" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
         </is>
       </c>
       <c r="P225" s="11" t="inlineStr"/>
@@ -15070,17 +15109,17 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -15090,243 +15129,41 @@
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
-          <t>ID46[Extended]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I226" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I226" s="11" t="inlineStr"/>
       <c r="J226" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K226" s="11" t="inlineStr"/>
-      <c r="L226" s="11" t="inlineStr"/>
+      <c r="L226" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
       <c r="M226" s="11" t="inlineStr"/>
       <c r="N226" s="11" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O226" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
         </is>
       </c>
       <c r="P226" s="11" t="inlineStr"/>
     </row>
-    <row r="227">
-      <c r="A227" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B227" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C227" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D227" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G227" s="11" t="inlineStr">
-        <is>
-          <t>ID46[2세대, ~2024.4], ID49[3세대, 2024.7~]</t>
-        </is>
-      </c>
-      <c r="H227" s="11" t="inlineStr">
-        <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I227" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J227" s="11" t="inlineStr">
-        <is>
-          <t>HU100, ILCO B119</t>
-        </is>
-      </c>
-      <c r="K227" s="11" t="inlineStr"/>
-      <c r="L227" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M227" s="11" t="inlineStr"/>
-      <c r="N227" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[2세대], PEPS[3세대]</t>
-        </is>
-      </c>
-      <c r="O227" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
-        </is>
-      </c>
-      <c r="P227" s="11" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B228" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C228" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D228" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G228" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H228" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="inlineStr"/>
-      <c r="J228" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K228" s="11" t="inlineStr"/>
-      <c r="L228" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M228" s="11" t="inlineStr"/>
-      <c r="N228" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O228" s="11" t="inlineStr">
-        <is>
-          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
-        </is>
-      </c>
-      <c r="P228" s="11" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B229" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C229" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D229" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G229" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H229" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I229" s="11" t="inlineStr"/>
-      <c r="J229" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K229" s="11" t="inlineStr"/>
-      <c r="L229" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M229" s="11" t="inlineStr"/>
-      <c r="N229" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O229" s="11" t="inlineStr">
-        <is>
-          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
-        </is>
-      </c>
-      <c r="P229" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P229"/>
+  <autoFilter ref="A1:P226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15337,7 +15174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -15624,6 +15461,44 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>- 스파크 2013: 2013년형은 이모빌라이저 없음, 2014년형(2013.5.14 출시)부터 이모빌라이저 폴딩키 적용(나무위키 스파크 2세대·차프라이스 2013.5 가격표) — 전환기라 색 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>- 토스카 2006: 2007년형(2006.11 출시)부터 이모빌라이저 신규 적용(이투데이 "GM대우 2007년형 토스카 출시") — 전환기라 색 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>- 서버번: 한국GM이 2024.10부터 국내 정식 판매(위키백과) — 2023년식 행 삭제. 키는 타호와 같은 스마트키(YG0G21TB2, 433MHz, ID49)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -541,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P226"/>
+  <dimension ref="A1:P227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14976,14 +14979,14 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D224" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E224" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -14993,12 +14996,12 @@
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>ID46[2세대, ~2024.4], ID49[3세대, 2024.7~]</t>
+          <t>ID46[2세대, ~2024.4]</t>
         </is>
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I224" s="11" t="inlineStr">
@@ -15011,16 +15014,12 @@
           <t>HU100, ILCO B119</t>
         </is>
       </c>
-      <c r="K224" s="11" t="inlineStr"/>
-      <c r="L224" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M224" s="11" t="inlineStr"/>
+      <c r="K224" s="11" t="n"/>
+      <c r="L224" s="11" t="n"/>
+      <c r="M224" s="11" t="n"/>
       <c r="N224" s="11" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저[2세대], PEPS[3세대]</t>
+          <t>트랜스폰더 이모빌라이저[2세대]</t>
         </is>
       </c>
       <c r="O224" s="11" t="inlineStr">
@@ -15028,7 +15027,7 @@
           <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
         </is>
       </c>
-      <c r="P224" s="11" t="inlineStr"/>
+      <c r="P224" s="11" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
@@ -15043,7 +15042,7 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
@@ -15063,7 +15062,7 @@
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49[3세대, 2024.7~]</t>
         </is>
       </c>
       <c r="H225" s="11" t="inlineStr">
@@ -15071,30 +15070,30 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I225" s="11" t="inlineStr"/>
+      <c r="I225" s="11" t="n"/>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K225" s="11" t="inlineStr"/>
+          <t>HU100, ILCO B119</t>
+        </is>
+      </c>
+      <c r="K225" s="11" t="n"/>
       <c r="L225" s="11" t="inlineStr">
         <is>
           <t>13548441[3세대], FCC YG0G21TB2</t>
         </is>
       </c>
-      <c r="M225" s="11" t="inlineStr"/>
+      <c r="M225" s="11" t="n"/>
       <c r="N225" s="11" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>PEPS[3세대]</t>
         </is>
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
-        </is>
-      </c>
-      <c r="P225" s="11" t="inlineStr"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P225" s="11" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
@@ -15109,7 +15108,7 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
@@ -15161,6 +15160,72 @@
         </is>
       </c>
       <c r="P226" s="11" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>쉐보레(GM대우)</t>
+        </is>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>콜로라도 (쉐보레)</t>
+        </is>
+      </c>
+      <c r="C227" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
+        </is>
+      </c>
+      <c r="H227" s="11" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="inlineStr"/>
+      <c r="J227" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
+      <c r="K227" s="11" t="inlineStr"/>
+      <c r="L227" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
+      <c r="M227" s="11" t="inlineStr"/>
+      <c r="N227" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
+        </is>
+      </c>
+      <c r="O227" s="11" t="inlineStr">
+        <is>
+          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
+        </is>
+      </c>
+      <c r="P227" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P226"/>
@@ -15174,288 +15239,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="16" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
+      <c r="A14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="A18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n"/>
+      <c r="A27" s="16" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="n"/>
+      <c r="A35" s="16" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
@@ -15496,6 +15561,13 @@
       <c r="A49" s="16" t="inlineStr">
         <is>
           <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>- 세대가 바뀌는 해는 세대별로 행을 나눔(구세대 1행 + 신세대 1행). 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 한 행에 전·후 값을 함께 적음</t>
         </is>
       </c>
     </row>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF9C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF006100"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +180,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -544,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P227"/>
+  <dimension ref="A1:P229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1423,31 +1434,27 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>해당 없음[2013년형], ID46(PCF7941E)[2014년형~]</t>
+          <t>해당 없음[2013년형]</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>막대키,폴딩키</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>HU100[M400 폴딩키 기준]</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr"/>
-      <c r="L18" s="11" t="inlineStr"/>
-      <c r="M18" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>미적용[2013년형], 트랜스폰더 이모빌라이저[2014년형~]</t>
+          <t>미적용[2013년형]</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -1470,27 +1477,27 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)</t>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)[2014년형~]</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -1498,18 +1505,18 @@
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>HU100[M400 폴딩키 기준]</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr"/>
-      <c r="L19" s="11" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저[2014년형~]</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
@@ -1517,11 +1524,7 @@
           <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>M300 폴딩키 자료 없음 — M400 폴딩키 기준 추정</t>
-        </is>
-      </c>
+      <c r="P19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -1536,7 +1539,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1554,7 +1557,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7941E)</t>
         </is>
@@ -1572,22 +1575,22 @@
       </c>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>13579213[M400, 2버튼, 2015.7~]</t>
-        </is>
-      </c>
-      <c r="N20" s="11" t="inlineStr">
+      <c r="M20" s="11" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), gmplusmall(더뉴/더넥스트 스파크 폴딩키 13579213: PCF7941E Hitag2 ID46, 433MHz, HU100), wikipedia(M400 2015.7 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P20" s="11" t="inlineStr"/>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>M300 폴딩키 자료 없음 — M400 폴딩키 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -1602,7 +1605,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1633,14 +1636,14 @@
       <c r="I21" s="11" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100[M400 폴딩키 기준]</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>13579213[2버튼]</t>
+          <t>13579213[M400, 2버튼, 2015.7~]</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
@@ -1650,7 +1653,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), gmplusmall(더뉴/더넥스트 스파크 폴딩키 13579213: PCF7941E Hitag2 ID46, 433MHz, HU100)</t>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), gmplusmall(더뉴/더넥스트 스파크 폴딩키 13579213: PCF7941E Hitag2 ID46, 433MHz, HU100), wikipedia(M400 2015.7 국내 출시)</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr"/>
@@ -1668,7 +1671,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1734,7 +1737,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1800,7 +1803,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1866,7 +1869,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1932,7 +1935,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1998,7 +2001,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2059,63 +2062,63 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>칼로스 (GM대우)</t>
+          <t>스파크 (쉐보레, M300)</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>ID48[수출형 기준]</t>
+          <t>2022(단종)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>DWO4R</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
-      <c r="M28" s="11" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>이모빌라이저 박스[수출형 기준]</t>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>13579213[2버튼]</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), wikipedia(칼로스 2002.5.2 출시)</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 칼로스 ID48 기준</t>
-        </is>
-      </c>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), gmplusmall(더뉴/더넥스트 스파크 폴딩키 13579213: PCF7941E Hitag2 ID46, 433MHz, HU100)</t>
+        </is>
+      </c>
+      <c r="P28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -2130,7 +2133,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -2174,7 +2177,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), wikipedia(칼로스 2002.5.2 출시)</t>
         </is>
       </c>
       <c r="P29" s="5" t="inlineStr">
@@ -2196,7 +2199,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -2262,7 +2265,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -2328,7 +2331,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -2394,7 +2397,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>2007(단종)</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -2438,7 +2441,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), mobilityhumanities.org(칼로스 2002.5~2007.10 생산)</t>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
         </is>
       </c>
       <c r="P33" s="5" t="inlineStr">
@@ -2455,12 +2458,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>젠트라 (GM대우)</t>
+          <t>칼로스 (GM대우)</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2007(단종)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -2504,12 +2507,12 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592), wikipedia(젠트라 2005.9 출시)</t>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), mobilityhumanities.org(칼로스 2002.5~2007.10 생산)</t>
         </is>
       </c>
       <c r="P34" s="5" t="inlineStr">
         <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 아베오 T250 ID48 기준</t>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 칼로스 ID48 기준</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2529,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -2570,7 +2573,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592)</t>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592), wikipedia(젠트라 2005.9 출시)</t>
         </is>
       </c>
       <c r="P35" s="5" t="inlineStr">
@@ -2592,7 +2595,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -2658,7 +2661,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -2724,7 +2727,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -2790,7 +2793,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -2856,7 +2859,7 @@
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -2900,7 +2903,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592), encar(젠트라 2011.2 단종)</t>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592)</t>
         </is>
       </c>
       <c r="P40" s="5" t="inlineStr">
@@ -2917,63 +2920,63 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>아베오 (쉐보레, T300)</t>
+          <t>젠트라 (GM대우)</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7937), ID46(PCF7941E)</t>
+          <t>2011(단종)</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ID48[수출형 기준]</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO4R</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
       <c r="L41" s="11" t="inlineStr"/>
-      <c r="M41" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼], 13504196[2버튼], 13504273[2버튼]</t>
-        </is>
-      </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="M41" s="11" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>이모빌라이저 박스[수출형 기준]</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), brunch/heydealer·namu.wiki(아베오 T300 2011.3~2016.12 판매)</t>
-        </is>
-      </c>
-      <c r="P41" s="11" t="inlineStr"/>
+          <t>transpondery.com(대우 칼로스 2002-2006·에반다 2003-2006 Megamos Crypto ID48), car-keys-online.com(DWO4R/ID48: 대우 칼로스 2002-2005·쉐보레 칼로스 2005-2008·타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), locksmithkeyless.com(아베오 T250 2004-2011 ID48 DWO4RT6, OE 96650592), encar(젠트라 2011.2 단종)</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 아베오 T250 ID48 기준</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2988,7 +2991,7 @@
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -3036,7 +3039,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), brunch/heydealer·namu.wiki(아베오 T300 2011.3~2016.12 판매)</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr"/>
@@ -3054,7 +3057,7 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3120,7 +3123,7 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -3186,7 +3189,7 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -3252,7 +3255,7 @@
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>2016(단종)</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3300,7 +3303,7 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), brunch/heydealer·namu.wiki(아베오 T300 2011.3~2016.12 판매)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM)</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr"/>
@@ -3313,12 +3316,12 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>라세티 (GM대우, J200, 1세대)</t>
+          <t>아베오 (쉐보레, T300)</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2016(단종)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3336,40 +3339,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[수출형 기준]</t>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937), ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>DWO4R</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
-      <c r="M47" s="11" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼], 13504196[2버튼], 13504273[2버튼]</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>autokeyshop.ru·smartkeys.ru(라세티 2004-2013 4D60 칩, DWO4R — 누비라 2000+는 ID48), dkgcc.com(옵트라/라세티 3버튼 리모컨키 433MHz 4D-60), wikipedia(라세티 2002.11.18 출시)</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 라세티/옵트라(2004~) 4D60 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), brunch/heydealer·namu.wiki(아베오 T300 2011.3~2016.12 판매)</t>
+        </is>
+      </c>
+      <c r="P47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -3384,7 +3387,7 @@
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3428,7 +3431,7 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>autokeyshop.ru·smartkeys.ru(라세티 2004-2013 4D60 칩, DWO4R — 누비라 2000+는 ID48), dkgcc.com(옵트라/라세티 3버튼 리모컨키 433MHz 4D-60)</t>
+          <t>autokeyshop.ru·smartkeys.ru(라세티 2004-2013 4D60 칩, DWO4R — 누비라 2000+는 ID48), dkgcc.com(옵트라/라세티 3버튼 리모컨키 433MHz 4D-60), wikipedia(라세티 2002.11.18 출시)</t>
         </is>
       </c>
       <c r="P48" s="5" t="inlineStr">
@@ -3450,7 +3453,7 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3516,7 +3519,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3582,7 +3585,7 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3648,7 +3651,7 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3714,7 +3717,7 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>2008(단종)</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -3775,12 +3778,12 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>라세티 프리미어 (GM대우, J300)</t>
+          <t>라세티 (GM대우, J200, 1세대)</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2008(단종)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -3800,40 +3803,36 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
+          <t>ID60(4D60)[수출형 기준]</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr"/>
       <c r="J54" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO4R</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
-      <c r="L54" s="11" t="n"/>
-      <c r="M54" s="11" t="inlineStr">
-        <is>
-          <t>13500218[수출형]</t>
-        </is>
-      </c>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr">
         <is>
-          <t>BCM, PEPS</t>
+          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
         </is>
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), blog.gm-korea.co.kr(라세티 프리미어 버튼타입 스마트키, 방전 시 컵홀더 밑 키 슬롯), blog.daum.net/locksmith(크루즈 스마트키 = 올란도·베리타스·알페온 동일 쉐보레 폴딩 스마트키)</t>
+          <t>autokeyshop.ru·smartkeys.ru(라세티 2004-2013 4D60 칩, DWO4R — 누비라 2000+는 ID48), dkgcc.com(옵트라/라세티 3버튼 리모컨키 433MHz 4D-60)</t>
         </is>
       </c>
       <c r="P54" s="5" t="inlineStr">
         <is>
-          <t>칩은 같은 차 수출형(크루즈 J300) 기준 — 국내 품번 미확인</t>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 라세티/옵트라(2004~) 4D60 기준</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3849,7 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -3920,7 +3919,7 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -3990,7 +3989,7 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -4055,12 +4054,12 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>크루즈 (쉐보레, J300, 1세대)</t>
+          <t>라세티 프리미어 (GM대우, J300)</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -4078,7 +4077,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G58" s="11" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
         </is>
@@ -4098,20 +4097,24 @@
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="11" t="inlineStr">
         <is>
-          <t>13500218[수출형], 13504196[수출형], 13500219[수출형]</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
+          <t>13500218[수출형]</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
-        </is>
-      </c>
-      <c r="P58" s="11" t="inlineStr"/>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), blog.gm-korea.co.kr(라세티 프리미어 버튼타입 스마트키, 방전 시 컵홀더 밑 키 슬롯), blog.daum.net/locksmith(크루즈 스마트키 = 올란도·베리타스·알페온 동일 쉐보레 폴딩 스마트키)</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>칩은 같은 차 수출형(크루즈 J300) 기준 — 국내 품번 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -4126,7 +4129,7 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -4174,7 +4177,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
         </is>
       </c>
       <c r="P59" s="11" t="inlineStr"/>
@@ -4192,7 +4195,7 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -4258,7 +4261,7 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -4324,7 +4327,7 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -4372,7 +4375,7 @@
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777)</t>
         </is>
       </c>
       <c r="P62" s="11" t="inlineStr"/>
@@ -4390,7 +4393,7 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -4438,7 +4441,7 @@
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
         </is>
       </c>
       <c r="P63" s="11" t="inlineStr"/>
@@ -4456,7 +4459,7 @@
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>2017(단종)</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -4504,7 +4507,7 @@
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777)</t>
         </is>
       </c>
       <c r="P64" s="11" t="inlineStr"/>
@@ -4517,12 +4520,12 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>크루즈 (쉐보레, D2XX, 2세대)</t>
+          <t>크루즈 (쉐보레, J300, 1세대)</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017(단종)</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -4542,7 +4545,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7937E)</t>
+          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -4557,20 +4560,20 @@
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>13508771[수출형], 13508769[수출형], FCC HYQ4EA</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>13500218[수출형], 13504196[수출형], 13500219[수출형]</t>
+        </is>
+      </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), danawa(올 뉴 크루즈 D2LC 2017.1~2019.7)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), danawa(크루즈 J300 2011.3~2015.1, 어메이징 뉴 크루즈 2015.1~2017.11)</t>
         </is>
       </c>
       <c r="P65" s="11" t="inlineStr"/>
@@ -4588,7 +4591,7 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -4636,7 +4639,7 @@
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), danawa(올 뉴 크루즈 D2LC 2017.1~2019.7)</t>
         </is>
       </c>
       <c r="P66" s="11" t="inlineStr"/>
@@ -4654,7 +4657,7 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -4702,7 +4705,7 @@
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), danawa(올 뉴 크루즈 D2LC 2017.1~2019.7)</t>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
         </is>
       </c>
       <c r="P67" s="11" t="inlineStr"/>
@@ -4715,12 +4718,12 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>볼트 (쉐보레, Volt, 플러그인 하이브리드)</t>
+          <t>크루즈 (쉐보레, D2XX, 2세대)</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019(단종)</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -4738,14 +4741,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr"/>
@@ -4755,23 +4758,23 @@
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr"/>
-      <c r="L68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>13508771[수출형], 13508769[수출형], FCC HYQ4EA</t>
+        </is>
+      </c>
       <c r="M68" s="11" t="inlineStr"/>
-      <c r="N68" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N68" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
-        </is>
-      </c>
-      <c r="P68" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), danawa(올 뉴 크루즈 D2LC 2017.1~2019.7)</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
@@ -4786,7 +4789,7 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -4852,7 +4855,7 @@
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -4918,7 +4921,7 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -4979,43 +4982,43 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>매그너스 (GM대우)</t>
+          <t>볼트 (쉐보레, Volt, 플러그인 하이브리드)</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2019(단종)</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>ID48[수출형 기준]</t>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr"/>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K72" s="11" t="inlineStr"/>
@@ -5023,17 +5026,17 @@
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 에반다 2003-2006 Megamos ID48), car-keys-online.com(DWO5R/ID48 대우 레간자), wikipedia(매그너스 = 쉐보레 에반다/에피카), ko.wikipedia(매그너스 1999.12 판매 시작)</t>
+          <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
         </is>
       </c>
       <c r="P72" s="5" t="inlineStr">
         <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 에반다 ID48 기준</t>
+          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5053,7 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -5094,7 +5097,7 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com(대우 에반다 2003-2006 Megamos ID48), car-keys-online.com(DWO5R/ID48 대우 레간자), wikipedia(매그너스 = 쉐보레 에반다/에피카)</t>
+          <t>transpondery.com(대우 에반다 2003-2006 Megamos ID48), car-keys-online.com(DWO5R/ID48 대우 레간자), wikipedia(매그너스 = 쉐보레 에반다/에피카), ko.wikipedia(매그너스 1999.12 판매 시작)</t>
         </is>
       </c>
       <c r="P73" s="5" t="inlineStr">
@@ -5116,7 +5119,7 @@
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -5182,7 +5185,7 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -5248,7 +5251,7 @@
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -5314,7 +5317,7 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -5380,7 +5383,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>2006(단종)</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -5441,20 +5444,32 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>토스카 (GM대우/쉐보레)</t>
+          <t>매그너스 (GM대우)</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>해당 없음[2006년형], ID60(4D60)[2007년형~]</t>
+          <t>2006(단종)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>ID48[수출형 기준]</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -5463,21 +5478,29 @@
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="11" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
-      <c r="N79" s="14" t="inlineStr">
-        <is>
-          <t>미적용[2006년형], 트랜스폰더 이모빌라이저[2007년형, 2006.11~]</t>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
         </is>
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
-        </is>
-      </c>
-      <c r="P79" s="14" t="n"/>
+          <t>transpondery.com(대우 에반다 2003-2006 Megamos ID48), car-keys-online.com(DWO5R/ID48 대우 레간자), wikipedia(매그너스 = 쉐보레 에반다/에피카)</t>
+        </is>
+      </c>
+      <c r="P79" s="5" t="inlineStr">
+        <is>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 에반다 ID48 기준</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
@@ -5492,27 +5515,15 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n"/>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>해당 없음[2006년형]</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -5520,14 +5531,14 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="11" t="inlineStr"/>
-      <c r="L80" s="11" t="inlineStr"/>
-      <c r="M80" s="11" t="inlineStr"/>
-      <c r="N80" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="11" t="n"/>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="14" t="inlineStr">
+        <is>
+          <t>미적용[2006년형]</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
@@ -5535,11 +5546,7 @@
           <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
         </is>
       </c>
-      <c r="P80" s="5" t="inlineStr">
-        <is>
-          <t>칩은 같은 차 수출형(에피카) 4D60 기준</t>
-        </is>
-      </c>
+      <c r="P80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
@@ -5554,27 +5561,27 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[2007년형~]</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -5582,14 +5589,14 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
-      <c r="J81" s="11" t="inlineStr"/>
-      <c r="K81" s="11" t="inlineStr"/>
-      <c r="L81" s="11" t="inlineStr"/>
-      <c r="M81" s="11" t="inlineStr"/>
-      <c r="N81" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저[2007년형, 2006.11~]</t>
         </is>
       </c>
       <c r="O81" s="11" t="inlineStr">
@@ -5597,11 +5604,7 @@
           <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
         </is>
       </c>
-      <c r="P81" s="5" t="inlineStr">
-        <is>
-          <t>칩은 같은 차 수출형(에피카) 4D60 기준</t>
-        </is>
-      </c>
+      <c r="P81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
@@ -5616,7 +5619,7 @@
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -5678,7 +5681,7 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -5740,7 +5743,7 @@
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -5797,12 +5800,12 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>말리부 (쉐보레, 8세대)</t>
+          <t>토스카 (GM대우/쉐보레)</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -5820,36 +5823,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G85" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr"/>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
+      <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="inlineStr">
-        <is>
-          <t>BCM, PEPS</t>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O85" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), namu.wiki(말리부 8세대 트림별 버튼시동·스마트키)</t>
-        </is>
-      </c>
-      <c r="P85" s="11" t="inlineStr"/>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="inlineStr">
+        <is>
+          <t>칩은 같은 차 수출형(에피카) 4D60 기준</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
@@ -5859,12 +5862,12 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>말리부 (쉐보레, 8세대)</t>
+          <t>토스카 (GM대우/쉐보레)</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -5882,36 +5885,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G86" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
+      <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr"/>
-      <c r="L86" s="11" t="n"/>
-      <c r="M86" s="11" t="n"/>
-      <c r="N86" s="11" t="inlineStr">
-        <is>
-          <t>BCM, PEPS</t>
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O86" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), namu.wiki(말리부 8세대 트림별 버튼시동·스마트키)</t>
-        </is>
-      </c>
-      <c r="P86" s="11" t="inlineStr"/>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+        </is>
+      </c>
+      <c r="P86" s="5" t="inlineStr">
+        <is>
+          <t>칩은 같은 차 수출형(에피카) 4D60 기준</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
@@ -5926,7 +5929,7 @@
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -5988,7 +5991,7 @@
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -6023,11 +6026,7 @@
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
-      <c r="L88" s="11" t="inlineStr">
-        <is>
-          <t>P13586777[2014~2015]</t>
-        </is>
-      </c>
+      <c r="L88" s="11" t="n"/>
       <c r="M88" s="11" t="n"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
@@ -6054,7 +6053,7 @@
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -6089,11 +6088,7 @@
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
-      <c r="L89" s="11" t="inlineStr">
-        <is>
-          <t>P13586777[2014~2015]</t>
-        </is>
-      </c>
+      <c r="L89" s="11" t="n"/>
       <c r="M89" s="11" t="n"/>
       <c r="N89" s="11" t="inlineStr">
         <is>
@@ -6120,7 +6115,7 @@
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>2016(단종)</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -6155,7 +6150,11 @@
         </is>
       </c>
       <c r="K90" s="11" t="inlineStr"/>
-      <c r="L90" s="11" t="n"/>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>P13586777[2014~2015]</t>
+        </is>
+      </c>
       <c r="M90" s="11" t="n"/>
       <c r="N90" s="11" t="inlineStr">
         <is>
@@ -6177,12 +6176,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>말리부 (쉐보레, 9세대)</t>
+          <t>말리부 (쉐보레, 8세대)</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -6202,12 +6201,12 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7937E)</t>
+          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr"/>
@@ -6219,18 +6218,18 @@
       <c r="K91" s="11" t="inlineStr"/>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>13508769, 13529662, FCC HYQ4EA</t>
-        </is>
-      </c>
-      <c r="M91" s="11" t="inlineStr"/>
+          <t>P13586777[2014~2015]</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="n"/>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O91" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
+          <t>abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), namu.wiki(말리부 8세대 트림별 버튼시동·스마트키)</t>
         </is>
       </c>
       <c r="P91" s="11" t="inlineStr"/>
@@ -6243,12 +6242,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>말리부 (쉐보레, 9세대)</t>
+          <t>말리부 (쉐보레, 8세대)</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016(단종)</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -6268,12 +6267,12 @@
       </c>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7937E)</t>
+          <t>ID46(PCF7941E)[폴딩키], ID46(PCF7952)[스마트키]</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr"/>
@@ -6283,20 +6282,16 @@
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
-      <c r="L92" s="11" t="inlineStr">
-        <is>
-          <t>13508769, 13529662, FCC HYQ4EA</t>
-        </is>
-      </c>
-      <c r="M92" s="11" t="inlineStr"/>
+      <c r="L92" s="11" t="n"/>
+      <c r="M92" s="11" t="n"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O92" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
+          <t>abkeys.com(크루즈·임팔라·말리부 2013+ 스마트키 PCF7952E ID46, 433MHz 5912546/13587073), gmplusmall(말리부 2014~2015 스마트키 P13586777), remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), namu.wiki(말리부 8세대 트림별 버튼시동·스마트키)</t>
         </is>
       </c>
       <c r="P92" s="11" t="inlineStr"/>
@@ -6314,7 +6309,7 @@
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -6446,7 +6441,7 @@
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -6512,7 +6507,7 @@
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -6578,7 +6573,7 @@
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -6626,7 +6621,7 @@
       </c>
       <c r="O97" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), namu.wiki(말리부 9세대 2022.7 발주 중단·8.23 생산 종료, 재고 2023 상반기까지)</t>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
         </is>
       </c>
       <c r="P97" s="11" t="inlineStr"/>
@@ -6639,12 +6634,12 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>알페온 (GM대우→쉐보레)</t>
+          <t>말리부 (쉐보레, 9세대)</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -6662,14 +6657,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr"/>
@@ -6679,23 +6674,23 @@
         </is>
       </c>
       <c r="K98" s="11" t="inlineStr"/>
-      <c r="L98" s="11" t="n"/>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>13508769, 13529662, FCC HYQ4EA</t>
+        </is>
+      </c>
       <c r="M98" s="11" t="inlineStr"/>
-      <c r="N98" s="5" t="inlineStr">
+      <c r="N98" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키)</t>
-        </is>
-      </c>
-      <c r="P98" s="5" t="inlineStr">
-        <is>
-          <t>칩은 뷰익 라크로스 기준 — 국내 품번 미확인</t>
-        </is>
-      </c>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019)</t>
+        </is>
+      </c>
+      <c r="P98" s="11" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
@@ -6705,12 +6700,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>알페온 (GM대우→쉐보레)</t>
+          <t>말리부 (쉐보레, 9세대)</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2022(단종)</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -6728,14 +6723,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr"/>
@@ -6745,23 +6740,23 @@
         </is>
       </c>
       <c r="K99" s="11" t="inlineStr"/>
-      <c r="L99" s="11" t="n"/>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>13508769, 13529662, FCC HYQ4EA</t>
+        </is>
+      </c>
       <c r="M99" s="11" t="inlineStr"/>
-      <c r="N99" s="5" t="inlineStr">
+      <c r="N99" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O99" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키)</t>
-        </is>
-      </c>
-      <c r="P99" s="5" t="inlineStr">
-        <is>
-          <t>칩은 뷰익 라크로스 기준 — 국내 품번 미확인</t>
-        </is>
-      </c>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), namu.wiki(말리부 9세대 2022.7 발주 중단·8.23 생산 종료, 재고 2023 상반기까지)</t>
+        </is>
+      </c>
+      <c r="P99" s="11" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
@@ -6776,7 +6771,7 @@
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -6842,7 +6837,7 @@
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -6908,7 +6903,7 @@
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -6974,7 +6969,7 @@
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -7018,7 +7013,7 @@
       </c>
       <c r="O103" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키), namu.wiki(2015.8 생산 종료, 재고 2016.12까지)</t>
+          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키)</t>
         </is>
       </c>
       <c r="P103" s="5" t="inlineStr">
@@ -7035,12 +7030,12 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>임팔라 (쉐보레)</t>
+          <t>알페온 (GM대우→쉐보레)</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -7058,7 +7053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G104" s="11" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
         </is>
@@ -7075,23 +7070,23 @@
         </is>
       </c>
       <c r="K104" s="11" t="inlineStr"/>
-      <c r="L104" s="11" t="inlineStr">
-        <is>
-          <t>5912546[수출형], 13587073[수출형]</t>
-        </is>
-      </c>
+      <c r="L104" s="11" t="n"/>
       <c r="M104" s="11" t="inlineStr"/>
-      <c r="N104" s="11" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O104" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), hankookilbo·kyeongin(임팔라 2015.9 국내 판매)</t>
-        </is>
-      </c>
-      <c r="P104" s="11" t="inlineStr"/>
+          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키)</t>
+        </is>
+      </c>
+      <c r="P104" s="5" t="inlineStr">
+        <is>
+          <t>칩은 뷰익 라크로스 기준 — 국내 품번 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
@@ -7101,12 +7096,12 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>임팔라 (쉐보레)</t>
+          <t>알페온 (GM대우→쉐보레)</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015(단종)</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -7124,7 +7119,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G105" s="11" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
         </is>
@@ -7141,23 +7136,23 @@
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr"/>
-      <c r="L105" s="11" t="inlineStr">
-        <is>
-          <t>5912546[수출형], 13587073[수출형]</t>
-        </is>
-      </c>
+      <c r="L105" s="11" t="n"/>
       <c r="M105" s="11" t="inlineStr"/>
-      <c r="N105" s="11" t="inlineStr">
+      <c r="N105" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O105" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199)</t>
-        </is>
-      </c>
-      <c r="P105" s="11" t="inlineStr"/>
+          <t>wikipedia(알페온 = 뷰익 라크로스 2010-2015), locksmithkeyless.com(라크로스 2010-2013 폴딩키 OHT01060512 ID46 HU100 5913397), ebay·abkeys(라크로스 2010-2016 스마트키 PCF7952E ID46), blog.daum.net/locksmith(알페온 = 크루즈와 같은 쉐보레 폴딩 스마트키), namu.wiki(2015.8 생산 종료, 재고 2016.12까지)</t>
+        </is>
+      </c>
+      <c r="P105" s="5" t="inlineStr">
+        <is>
+          <t>칩은 뷰익 라크로스 기준 — 국내 품번 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
@@ -7172,7 +7167,7 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -7220,7 +7215,7 @@
       </c>
       <c r="O106" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199)</t>
+          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), hankookilbo·kyeongin(임팔라 2015.9 국내 판매)</t>
         </is>
       </c>
       <c r="P106" s="11" t="inlineStr"/>
@@ -7238,7 +7233,7 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -7286,7 +7281,7 @@
       </c>
       <c r="O107" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), carwiki(2018년형 상위 트림 버튼시동&amp;스마트키)</t>
+          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199)</t>
         </is>
       </c>
       <c r="P107" s="11" t="inlineStr"/>
@@ -7304,7 +7299,7 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -7370,7 +7365,7 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>2020(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -7418,7 +7413,7 @@
       </c>
       <c r="O109" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), namu.wiki(2020 단종)</t>
+          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), carwiki(2018년형 상위 트림 버튼시동&amp;스마트키)</t>
         </is>
       </c>
       <c r="P109" s="11" t="inlineStr"/>
@@ -7431,63 +7426,63 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>레조 (GM대우, Rezzo)</t>
+          <t>임팔라 (쉐보레)</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>ID48[수출형 기준]</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr"/>
       <c r="J110" s="11" t="inlineStr">
         <is>
-          <t>DWO4R</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K110" s="11" t="inlineStr"/>
-      <c r="L110" s="11" t="inlineStr"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>5912546[수출형], 13587073[수출형]</t>
+        </is>
+      </c>
       <c r="M110" s="11" t="inlineStr"/>
-      <c r="N110" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), ko.wikipedia(레조 2000.1 생산 시작)</t>
-        </is>
-      </c>
-      <c r="P110" s="5" t="inlineStr">
-        <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 타쿠마 ID48 기준</t>
-        </is>
-      </c>
+          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199)</t>
+        </is>
+      </c>
+      <c r="P110" s="11" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
@@ -7497,63 +7492,63 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>레조 (GM대우, Rezzo)</t>
+          <t>임팔라 (쉐보레)</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>ID48[수출형 기준]</t>
+          <t>2020(단종)</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7952E)[스마트키], ID46(PCF7937E)[폴딩키]</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr"/>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>DWO4R</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
-      <c r="L111" s="11" t="inlineStr"/>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>5912546[수출형], 13587073[수출형]</t>
+        </is>
+      </c>
       <c r="M111" s="11" t="inlineStr"/>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
+      <c r="N111" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
-        </is>
-      </c>
-      <c r="P111" s="5" t="inlineStr">
-        <is>
-          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 타쿠마 ID48 기준</t>
-        </is>
-      </c>
+          <t>abkeys.com(임팔라·말리부 스마트키 PCF7952E ID46 HU100 433MHz 5912546/13587073), northcoastkeyless.com(임팔라 2014-2020 플립키 OHT01060512 13504199), namu.wiki(2020 단종)</t>
+        </is>
+      </c>
+      <c r="P111" s="11" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
@@ -7568,7 +7563,7 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -7612,7 +7607,7 @@
       </c>
       <c r="O112" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
+          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), ko.wikipedia(레조 2000.1 생산 시작)</t>
         </is>
       </c>
       <c r="P112" s="5" t="inlineStr">
@@ -7634,7 +7629,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -7700,7 +7695,7 @@
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -7766,7 +7761,7 @@
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -7832,7 +7827,7 @@
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -7898,7 +7893,7 @@
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>2007(단종)</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -7942,7 +7937,7 @@
       </c>
       <c r="O117" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), mediawatch·cctimes(레조 2007.6 단종)</t>
+          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
         </is>
       </c>
       <c r="P117" s="5" t="inlineStr">
@@ -7959,65 +7954,61 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>올란도 (쉐보레)</t>
+          <t>레조 (GM대우, Rezzo)</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)[폴딩키]</t>
+          <t>ID48[수출형 기준]</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr"/>
       <c r="J118" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO4R</t>
         </is>
       </c>
       <c r="K118" s="11" t="inlineStr"/>
-      <c r="L118" s="11" t="n"/>
-      <c r="M118" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
-        </is>
-      </c>
+      <c r="L118" s="11" t="inlineStr"/>
+      <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="5" t="inlineStr">
         <is>
-          <t>BCM, PEPS</t>
+          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
         </is>
       </c>
       <c r="O118" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키)</t>
+          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48)</t>
         </is>
       </c>
       <c r="P118" s="5" t="inlineStr">
         <is>
-          <t>스마트키 칩 표기 상충(PCF7952 계열 vs PCF7938X)</t>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 타쿠마 ID48 기준</t>
         </is>
       </c>
     </row>
@@ -8029,65 +8020,61 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>올란도 (쉐보레)</t>
+          <t>레조 (GM대우, Rezzo)</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2007(단종)</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)[폴딩키]</t>
+          <t>ID48[수출형 기준]</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr"/>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO4R</t>
         </is>
       </c>
       <c r="K119" s="11" t="inlineStr"/>
-      <c r="L119" s="11" t="n"/>
-      <c r="M119" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
-        </is>
-      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
       <c r="N119" s="5" t="inlineStr">
         <is>
-          <t>BCM, PEPS</t>
+          <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
         </is>
       </c>
       <c r="O119" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키)</t>
+          <t>wikipedia(레조 = 대우 타쿠마, 2000~2008), car-keys-online.com(DWO4R/ID48: 대우 타쿠마 2001-2006), bestkeysupply.com(TMPro 모듈113 대우/쉐보레 이모박스 ID48), mediawatch·cctimes(레조 2007.6 단종)</t>
         </is>
       </c>
       <c r="P119" s="5" t="inlineStr">
         <is>
-          <t>스마트키 칩 표기 상충(PCF7952 계열 vs PCF7938X)</t>
+          <t>국내형 이모빌라이저 적용 자료 없음 — 수출형 타쿠마 ID48 기준</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8091,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -8174,7 +8161,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
@@ -8244,7 +8231,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -8314,7 +8301,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
@@ -8384,7 +8371,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
@@ -8454,7 +8441,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -8502,7 +8489,7 @@
       </c>
       <c r="O125" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키), namu.wiki(2018.7 생산 중단, 연말 재고 소진 후 단종)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키)</t>
         </is>
       </c>
       <c r="P125" s="5" t="inlineStr">
@@ -8519,12 +8506,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>G2X (GM대우)</t>
+          <t>올란도 (쉐보레)</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -8542,36 +8529,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G126" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Circle Plus]</t>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)[폴딩키]</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr"/>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>B111</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K126" s="11" t="inlineStr"/>
-      <c r="L126" s="11" t="inlineStr"/>
-      <c r="M126" s="11" t="inlineStr"/>
-      <c r="N126" s="11" t="inlineStr">
-        <is>
-          <t>PassKey 3+</t>
+      <c r="L126" s="11" t="n"/>
+      <c r="M126" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O126" s="11" t="inlineStr">
         <is>
-          <t>amazon/RI-KEY(새턴 스카이 2007-2010 B111 ID46 Circle Plus), locksmithkeyless.com(폰티악 2005-2010 ID46 GM 칩 B111-PT), wikipedia(G2X = 새턴 스카이·폰티악 솔스티스 카파 플랫폼), namu.wiki(G2X 2007.8.6 출시)</t>
-        </is>
-      </c>
-      <c r="P126" s="11" t="inlineStr"/>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키)</t>
+        </is>
+      </c>
+      <c r="P126" s="5" t="inlineStr">
+        <is>
+          <t>스마트키 칩 표기 상충(PCF7952 계열 vs PCF7938X)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
@@ -8581,12 +8576,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>G2X (GM대우)</t>
+          <t>올란도 (쉐보레)</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>2008(단종)</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -8604,36 +8599,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G127" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Circle Plus]</t>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)[폴딩키]</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr"/>
       <c r="J127" s="11" t="inlineStr">
         <is>
-          <t>B111</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K127" s="11" t="inlineStr"/>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
-      <c r="N127" s="11" t="inlineStr">
-        <is>
-          <t>PassKey 3+</t>
+      <c r="L127" s="11" t="n"/>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>BCM, PEPS</t>
         </is>
       </c>
       <c r="O127" s="11" t="inlineStr">
         <is>
-          <t>amazon/RI-KEY(새턴 스카이 2007-2010 B111 ID46 Circle Plus), locksmithkeyless.com(폰티악 2005-2010 ID46 GM 칩 B111-PT), wikipedia(G2X = 새턴 스카이·폰티악 솔스티스 카파 플랫폼), namu.wiki(2008.9.30 수입 중단·단종)</t>
-        </is>
-      </c>
-      <c r="P127" s="11" t="inlineStr"/>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), autokeymaster·aliexpress(올란도 스마트 리모컨 433MHz PCF7938X), blog.daum.net/locksmith(올란도 = 크루즈 쉐보레 폴딩 스마트키), namu.wiki(2018.7 생산 중단, 연말 재고 소진 후 단종)</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>스마트키 칩 표기 상충(PCF7952 계열 vs PCF7938X)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
@@ -8643,12 +8646,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>카마로 (쉐보레, 5세대)</t>
+          <t>G2X (GM대우)</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -8668,18 +8671,18 @@
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7937E)</t>
+          <t>ID46[Circle Plus]</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr"/>
       <c r="J128" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>B111</t>
         </is>
       </c>
       <c r="K128" s="11" t="inlineStr"/>
@@ -8687,12 +8690,12 @@
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PassKey 3+</t>
         </is>
       </c>
       <c r="O128" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·myremotekey.com(카마로·말리부 2010+ 플립키 OHT01060512 ID46 PCF7937E HU100, 13504199/13504200), locksmithkeyless.com(카마로 2015 플립키)</t>
+          <t>amazon/RI-KEY(새턴 스카이 2007-2010 B111 ID46 Circle Plus), locksmithkeyless.com(폰티악 2005-2010 ID46 GM 칩 B111-PT), wikipedia(G2X = 새턴 스카이·폰티악 솔스티스 카파 플랫폼), namu.wiki(G2X 2007.8.6 출시)</t>
         </is>
       </c>
       <c r="P128" s="11" t="inlineStr"/>
@@ -8705,12 +8708,12 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>카마로 (쉐보레, 5세대)</t>
+          <t>G2X (GM대우)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2008(단종)</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -8730,18 +8733,18 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7937E)</t>
+          <t>ID46[Circle Plus]</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr"/>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>B111</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr"/>
@@ -8749,12 +8752,12 @@
       <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PassKey 3+</t>
         </is>
       </c>
       <c r="O129" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·myremotekey.com(카마로·말리부 2010+ 플립키 OHT01060512 ID46 PCF7937E HU100, 13504199/13504200), locksmithkeyless.com(카마로 2015 플립키)</t>
+          <t>amazon/RI-KEY(새턴 스카이 2007-2010 B111 ID46 Circle Plus), locksmithkeyless.com(폰티악 2005-2010 ID46 GM 칩 B111-PT), wikipedia(G2X = 새턴 스카이·폰티악 솔스티스 카파 플랫폼), namu.wiki(2008.9.30 수입 중단·단종)</t>
         </is>
       </c>
       <c r="P129" s="11" t="inlineStr"/>
@@ -8772,7 +8775,7 @@
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -8834,7 +8837,7 @@
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -8896,7 +8899,7 @@
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -8953,12 +8956,12 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>카마로 (쉐보레, 6세대)</t>
+          <t>카마로 (쉐보레, 5세대)</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -8983,7 +8986,7 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr"/>
@@ -8993,20 +8996,16 @@
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr"/>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>13508769, 13529662, FCC HYQ4EA</t>
-        </is>
-      </c>
+      <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O133" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769), dealsite·autotribune(카마로 6세대 2016.6 국내 도입)</t>
+          <t>abkeys.com·myremotekey.com(카마로·말리부 2010+ 플립키 OHT01060512 ID46 PCF7937E HU100, 13504199/13504200), locksmithkeyless.com(카마로 2015 플립키)</t>
         </is>
       </c>
       <c r="P133" s="11" t="inlineStr"/>
@@ -9019,12 +9018,12 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>카마로 (쉐보레, 6세대)</t>
+          <t>카마로 (쉐보레, 5세대)</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015(단종)</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -9049,7 +9048,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr"/>
@@ -9059,20 +9058,16 @@
         </is>
       </c>
       <c r="K134" s="11" t="inlineStr"/>
-      <c r="L134" s="11" t="inlineStr">
-        <is>
-          <t>13508769, 13529662, FCC HYQ4EA</t>
-        </is>
-      </c>
+      <c r="L134" s="11" t="inlineStr"/>
       <c r="M134" s="11" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O134" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
+          <t>abkeys.com·myremotekey.com(카마로·말리부 2010+ 플립키 OHT01060512 ID46 PCF7937E HU100, 13504199/13504200), locksmithkeyless.com(카마로 2015 플립키)</t>
         </is>
       </c>
       <c r="P134" s="11" t="inlineStr"/>
@@ -9090,7 +9085,7 @@
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -9138,7 +9133,7 @@
       </c>
       <c r="O135" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769), dealsite·autotribune(카마로 6세대 2016.6 국내 도입)</t>
         </is>
       </c>
       <c r="P135" s="11" t="inlineStr"/>
@@ -9156,7 +9151,7 @@
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -9174,7 +9169,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G136" s="14" t="inlineStr">
+      <c r="G136" s="11" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9197,7 +9192,7 @@
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr"/>
-      <c r="N136" s="14" t="inlineStr">
+      <c r="N136" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9207,7 +9202,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
-      <c r="P136" s="14" t="n"/>
+      <c r="P136" s="11" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
@@ -9222,7 +9217,7 @@
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -9240,7 +9235,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G137" s="14" t="inlineStr">
+      <c r="G137" s="11" t="inlineStr">
         <is>
           <t>ID46(PCF7937E)</t>
         </is>
@@ -9263,7 +9258,7 @@
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr"/>
-      <c r="N137" s="14" t="inlineStr">
+      <c r="N137" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -9273,7 +9268,7 @@
           <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
-      <c r="P137" s="14" t="n"/>
+      <c r="P137" s="11" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
@@ -9288,7 +9283,7 @@
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -9354,7 +9349,7 @@
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -9402,7 +9397,7 @@
       </c>
       <c r="O139" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769), autotribune(국내 11년간 1,941대 판매 후 단종)</t>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
         </is>
       </c>
       <c r="P139" s="14" t="n"/>
@@ -9415,12 +9410,12 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>카마로 (쉐보레, 6세대)</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
@@ -9438,9 +9433,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
@@ -9457,25 +9452,21 @@
       <c r="K140" s="11" t="inlineStr"/>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
+          <t>13508769, 13529662, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr"/>
-      <c r="N140" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N140" s="14" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O140" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P140" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769)</t>
+        </is>
+      </c>
+      <c r="P140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
@@ -9485,12 +9476,12 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>카마로 (쉐보레, 6세대)</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022(단종)</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -9508,9 +9499,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -9527,25 +9518,21 @@
       <c r="K141" s="11" t="inlineStr"/>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
+          <t>13508769, 13529662, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr"/>
-      <c r="N141" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N141" s="14" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O141" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P141" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>abkeys.com·bestkeysolution.com(HYQ4EA 433MHz 스마트키 ID46 PCF7937E/NCF2951E, 13508769·13529662·13508771: 카마로·말리부 2016+, 크루즈 2016-2019), tlkeys.com(순정 카마로 2016 스마트키 13508769), autotribune(국내 11년간 1,941대 판매 후 단종)</t>
+        </is>
+      </c>
+      <c r="P141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="inlineStr">
@@ -9560,7 +9547,7 @@
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -9630,7 +9617,7 @@
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -9700,7 +9687,7 @@
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -9770,7 +9757,7 @@
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -9835,22 +9822,22 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>콜벳 (쉐보레, C7)</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D146" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -9860,7 +9847,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7952E)</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
@@ -9869,11 +9856,15 @@
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr"/>
-      <c r="J146" s="11" t="inlineStr"/>
+      <c r="J146" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K146" s="11" t="inlineStr"/>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
+          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr"/>
@@ -9884,7 +9875,7 @@
       </c>
       <c r="O146" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
         </is>
       </c>
       <c r="P146" s="5" t="inlineStr">
@@ -9901,22 +9892,22 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>콜벳 (쉐보레, C7)</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D147" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2019(단종)</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -9926,7 +9917,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7952E)</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -9935,11 +9926,15 @@
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr"/>
-      <c r="J147" s="11" t="inlineStr"/>
+      <c r="J147" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K147" s="11" t="inlineStr"/>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
+          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr"/>
@@ -9950,7 +9945,7 @@
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
         </is>
       </c>
       <c r="P147" s="5" t="inlineStr">
@@ -9972,7 +9967,7 @@
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
@@ -10038,7 +10033,7 @@
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
@@ -10104,7 +10099,7 @@
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
@@ -10165,22 +10160,22 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>콜벳 (쉐보레, C8)</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -10188,40 +10183,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G151" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)</t>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
+      <c r="J151" s="11" t="inlineStr"/>
       <c r="K151" s="11" t="inlineStr"/>
-      <c r="L151" s="11" t="inlineStr"/>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
-        </is>
-      </c>
-      <c r="N151" s="11" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="L151" s="11" t="inlineStr">
+        <is>
+          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
+        </is>
+      </c>
+      <c r="M151" s="11" t="inlineStr"/>
+      <c r="N151" s="5" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
-        </is>
-      </c>
-      <c r="P151" s="11" t="inlineStr"/>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+        </is>
+      </c>
+      <c r="P151" s="5" t="inlineStr">
+        <is>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -10231,22 +10226,22 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>콜벳 (쉐보레, C8)</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -10254,40 +10249,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G152" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)</t>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
+      <c r="J152" s="11" t="inlineStr"/>
       <c r="K152" s="11" t="inlineStr"/>
-      <c r="L152" s="11" t="inlineStr"/>
-      <c r="M152" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
-        </is>
-      </c>
-      <c r="N152" s="11" t="inlineStr">
-        <is>
-          <t>BCM</t>
+      <c r="L152" s="11" t="inlineStr">
+        <is>
+          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
+        </is>
+      </c>
+      <c r="M152" s="11" t="inlineStr"/>
+      <c r="N152" s="5" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
-        </is>
-      </c>
-      <c r="P152" s="11" t="inlineStr"/>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+        </is>
+      </c>
+      <c r="P152" s="5" t="inlineStr">
+        <is>
+          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -10302,7 +10297,7 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
@@ -10368,7 +10363,7 @@
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
@@ -10434,7 +10429,7 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
@@ -10470,7 +10465,11 @@
       </c>
       <c r="K155" s="11" t="inlineStr"/>
       <c r="L155" s="11" t="inlineStr"/>
-      <c r="M155" s="11" t="n"/>
+      <c r="M155" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+        </is>
+      </c>
       <c r="N155" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10496,7 +10495,7 @@
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -10532,7 +10531,11 @@
       </c>
       <c r="K156" s="11" t="inlineStr"/>
       <c r="L156" s="11" t="inlineStr"/>
-      <c r="M156" s="11" t="n"/>
+      <c r="M156" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+        </is>
+      </c>
       <c r="N156" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10558,7 +10561,7 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
@@ -10620,7 +10623,7 @@
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -10682,7 +10685,7 @@
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -10744,7 +10747,7 @@
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -10788,7 +10791,7 @@
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736), namu.wiki(2022.8 내수 생산 종료, 11.4 홈페이지 삭제)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
         </is>
       </c>
       <c r="P160" s="11" t="inlineStr"/>
@@ -10801,12 +10804,12 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -10826,12 +10829,12 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
@@ -10841,20 +10844,16 @@
         </is>
       </c>
       <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr">
-        <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L161" s="11" t="inlineStr"/>
       <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
         </is>
       </c>
       <c r="P161" s="11" t="inlineStr"/>
@@ -10867,12 +10866,12 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022(단종)</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -10892,12 +10891,12 @@
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
@@ -10907,20 +10906,16 @@
         </is>
       </c>
       <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr">
-        <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L162" s="11" t="inlineStr"/>
       <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O162" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736), namu.wiki(2022.8 내수 생산 종료, 11.4 홈페이지 삭제)</t>
         </is>
       </c>
       <c r="P162" s="11" t="inlineStr"/>
@@ -10938,7 +10933,7 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -11004,7 +10999,7 @@
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -11065,12 +11060,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -11107,7 +11102,7 @@
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M165" s="11" t="n"/>
@@ -11118,7 +11113,7 @@
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
         </is>
       </c>
       <c r="P165" s="11" t="inlineStr"/>
@@ -11131,12 +11126,12 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -11173,7 +11168,7 @@
       <c r="K166" s="11" t="inlineStr"/>
       <c r="L166" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M166" s="11" t="n"/>
@@ -11184,7 +11179,7 @@
       </c>
       <c r="O166" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
         </is>
       </c>
       <c r="P166" s="11" t="inlineStr"/>
@@ -11202,7 +11197,7 @@
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
@@ -11268,7 +11263,7 @@
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
@@ -11334,7 +11329,7 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
@@ -11400,7 +11395,7 @@
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -11466,7 +11461,7 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -11527,12 +11522,12 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -11550,14 +11545,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G172" s="5" t="inlineStr">
+      <c r="G172" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr"/>
@@ -11567,23 +11562,23 @@
         </is>
       </c>
       <c r="K172" s="11" t="inlineStr"/>
-      <c r="L172" s="11" t="inlineStr"/>
-      <c r="M172" s="11" t="inlineStr"/>
-      <c r="N172" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L172" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M172" s="11" t="n"/>
+      <c r="N172" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P172" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+        </is>
+      </c>
+      <c r="P172" s="11" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -11593,12 +11588,12 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
@@ -11616,14 +11611,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G173" s="5" t="inlineStr">
+      <c r="G173" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I173" s="11" t="inlineStr"/>
@@ -11633,23 +11628,23 @@
         </is>
       </c>
       <c r="K173" s="11" t="inlineStr"/>
-      <c r="L173" s="11" t="inlineStr"/>
-      <c r="M173" s="11" t="inlineStr"/>
-      <c r="N173" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L173" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M173" s="11" t="n"/>
+      <c r="N173" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P173" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+        </is>
+      </c>
+      <c r="P173" s="11" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
@@ -11664,7 +11659,7 @@
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
@@ -11730,7 +11725,7 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
@@ -11796,7 +11791,7 @@
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -11862,17 +11857,17 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
@@ -11882,7 +11877,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>ID46, ID49</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
@@ -11897,11 +11892,7 @@
         </is>
       </c>
       <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr">
-        <is>
-          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L177" s="11" t="inlineStr"/>
       <c r="M177" s="11" t="inlineStr"/>
       <c r="N177" s="5" t="inlineStr">
         <is>
@@ -11910,12 +11901,12 @@
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기)</t>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
       <c r="P177" s="5" t="inlineStr">
         <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
+          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
         </is>
       </c>
     </row>
@@ -11932,17 +11923,17 @@
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -11952,7 +11943,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>ID46, ID49</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H178" s="11" t="inlineStr">
@@ -11967,11 +11958,7 @@
         </is>
       </c>
       <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr">
-        <is>
-          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L178" s="11" t="inlineStr"/>
       <c r="M178" s="11" t="inlineStr"/>
       <c r="N178" s="5" t="inlineStr">
         <is>
@@ -11980,12 +11967,12 @@
       </c>
       <c r="O178" s="11" t="inlineStr">
         <is>
-          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기), zdnet·namu.wiki(2023.12 단종, 2024.1 판매 중단)</t>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
       <c r="P178" s="5" t="inlineStr">
         <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
+          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11984,7 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>볼트 EUV (쉐보레)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
@@ -12039,7 +12026,7 @@
       <c r="K179" s="11" t="inlineStr"/>
       <c r="L179" s="11" t="inlineStr">
         <is>
-          <t>13535665, 13535664, FCC HYQ4ES</t>
+          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M179" s="11" t="inlineStr"/>
@@ -12050,7 +12037,7 @@
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개)</t>
+          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기)</t>
         </is>
       </c>
       <c r="P179" s="5" t="inlineStr">
@@ -12067,7 +12054,7 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>볼트 EUV (쉐보레)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr">
@@ -12109,7 +12096,7 @@
       <c r="K180" s="11" t="inlineStr"/>
       <c r="L180" s="11" t="inlineStr">
         <is>
-          <t>13535665, 13535664, FCC HYQ4ES</t>
+          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M180" s="11" t="inlineStr"/>
@@ -12120,7 +12107,7 @@
       </c>
       <c r="O180" s="11" t="inlineStr">
         <is>
-          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개), zdnet(2023.12 단종)</t>
+          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기), zdnet·namu.wiki(2023.12 단종, 2024.1 판매 중단)</t>
         </is>
       </c>
       <c r="P180" s="5" t="inlineStr">
@@ -12137,22 +12124,22 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>볼트 EUV (쉐보레)</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
@@ -12160,36 +12147,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G181" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>ID46, ID49</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I181" s="11" t="inlineStr"/>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K181" s="11" t="inlineStr"/>
-      <c r="L181" s="11" t="inlineStr"/>
-      <c r="M181" s="11" t="n"/>
-      <c r="N181" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L181" s="11" t="inlineStr">
+        <is>
+          <t>13535665, 13535664, FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M181" s="11" t="inlineStr"/>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(윈스톰 2006.6.7 출시)</t>
-        </is>
-      </c>
-      <c r="P181" s="11" t="inlineStr"/>
+          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개)</t>
+        </is>
+      </c>
+      <c r="P181" s="5" t="inlineStr">
+        <is>
+          <t>칩 표기 상충(ID46 vs ID49)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
@@ -12199,22 +12194,22 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>볼트 EUV (쉐보레)</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023(단종)</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -12222,36 +12217,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G182" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>ID46, ID49</t>
         </is>
       </c>
       <c r="H182" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I182" s="11" t="inlineStr"/>
       <c r="J182" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K182" s="11" t="inlineStr"/>
-      <c r="L182" s="11" t="inlineStr"/>
-      <c r="M182" s="11" t="n"/>
-      <c r="N182" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>13535665, 13535664, FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M182" s="11" t="inlineStr"/>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O182" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
-        </is>
-      </c>
-      <c r="P182" s="11" t="inlineStr"/>
+          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개), zdnet(2023.12 단종)</t>
+        </is>
+      </c>
+      <c r="P182" s="5" t="inlineStr">
+        <is>
+          <t>칩 표기 상충(ID46 vs ID49)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
@@ -12266,7 +12269,7 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -12310,7 +12313,7 @@
       </c>
       <c r="O183" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(윈스톰 2006.6.7 출시)</t>
         </is>
       </c>
       <c r="P183" s="11" t="inlineStr"/>
@@ -12328,7 +12331,7 @@
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -12390,7 +12393,7 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -12452,7 +12455,7 @@
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -12496,7 +12499,7 @@
       </c>
       <c r="O186" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(2011.4 캡티바로 변경)</t>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
         </is>
       </c>
       <c r="P186" s="11" t="inlineStr"/>
@@ -12509,12 +12512,12 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 맥스 (GM대우)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -12532,7 +12535,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr">
+      <c r="G187" s="11" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -12550,22 +12553,18 @@
       </c>
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr"/>
-      <c r="M187" s="11" t="inlineStr"/>
-      <c r="N187" s="5" t="inlineStr">
+      <c r="M187" s="11" t="n"/>
+      <c r="N187" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O187" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
-        </is>
-      </c>
-      <c r="P187" s="5" t="inlineStr">
-        <is>
-          <t>윈스톰 기준 추정</t>
-        </is>
-      </c>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
+        </is>
+      </c>
+      <c r="P187" s="11" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -12575,12 +12574,12 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 맥스 (GM대우)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -12598,7 +12597,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G188" s="5" t="inlineStr">
+      <c r="G188" s="11" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -12616,22 +12615,18 @@
       </c>
       <c r="K188" s="11" t="inlineStr"/>
       <c r="L188" s="11" t="inlineStr"/>
-      <c r="M188" s="11" t="inlineStr"/>
-      <c r="N188" s="5" t="inlineStr">
+      <c r="M188" s="11" t="n"/>
+      <c r="N188" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O188" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
-        </is>
-      </c>
-      <c r="P188" s="5" t="inlineStr">
-        <is>
-          <t>윈스톰 기준 추정</t>
-        </is>
-      </c>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(2011.4 캡티바로 변경)</t>
+        </is>
+      </c>
+      <c r="P188" s="11" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -12646,7 +12641,7 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>2010(단종)</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
@@ -12707,12 +12702,12 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>윈스톰 맥스 (GM대우)</t>
         </is>
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -12730,7 +12725,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G190" s="14" t="inlineStr">
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -12747,19 +12742,23 @@
         </is>
       </c>
       <c r="K190" s="11" t="inlineStr"/>
-      <c r="L190" s="11" t="n"/>
+      <c r="L190" s="11" t="inlineStr"/>
       <c r="M190" s="11" t="inlineStr"/>
-      <c r="N190" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="N190" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O190" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P190" s="14" t="n"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
+        </is>
+      </c>
+      <c r="P190" s="5" t="inlineStr">
+        <is>
+          <t>윈스톰 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -12769,12 +12768,12 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>윈스톰 맥스 (GM대우)</t>
         </is>
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010(단종)</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
@@ -12792,7 +12791,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G191" s="14" t="inlineStr">
+      <c r="G191" s="5" t="inlineStr">
         <is>
           <t>ID46(PCF7936)</t>
         </is>
@@ -12809,19 +12808,23 @@
         </is>
       </c>
       <c r="K191" s="11" t="inlineStr"/>
-      <c r="L191" s="11" t="n"/>
+      <c r="L191" s="11" t="inlineStr"/>
       <c r="M191" s="11" t="inlineStr"/>
-      <c r="N191" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="N191" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O191" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P191" s="14" t="n"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
+        </is>
+      </c>
+      <c r="P191" s="5" t="inlineStr">
+        <is>
+          <t>윈스톰 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -12836,7 +12839,7 @@
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
@@ -12856,26 +12859,22 @@
       </c>
       <c r="G192" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H192" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I192" s="11" t="inlineStr"/>
       <c r="J192" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K192" s="11" t="inlineStr"/>
-      <c r="L192" s="11" t="inlineStr">
-        <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L192" s="11" t="n"/>
       <c r="M192" s="11" t="inlineStr"/>
       <c r="N192" s="14" t="inlineStr">
         <is>
@@ -12902,7 +12901,7 @@
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
@@ -12922,26 +12921,22 @@
       </c>
       <c r="G193" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K193" s="11" t="inlineStr"/>
-      <c r="L193" s="11" t="inlineStr">
-        <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L193" s="11" t="n"/>
       <c r="M193" s="11" t="inlineStr"/>
       <c r="N193" s="14" t="inlineStr">
         <is>
@@ -12968,7 +12963,7 @@
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
@@ -13034,7 +13029,7 @@
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -13100,7 +13095,7 @@
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
@@ -13166,7 +13161,7 @@
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -13214,7 +13209,7 @@
       </c>
       <c r="O197" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz), namu.wiki(2018.5 생산 중단, 재고 판매 후 단종)</t>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
         </is>
       </c>
       <c r="P197" s="14" t="n"/>
@@ -13227,12 +13222,12 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -13250,40 +13245,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G198" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G198" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I198" s="11" t="inlineStr"/>
       <c r="J198" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K198" s="11" t="inlineStr"/>
       <c r="L198" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr"/>
-      <c r="N198" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N198" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O198" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P198" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
@@ -13293,12 +13288,12 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -13316,40 +13311,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G199" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G199" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I199" s="11" t="inlineStr"/>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K199" s="11" t="inlineStr"/>
       <c r="L199" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M199" s="11" t="inlineStr"/>
-      <c r="N199" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N199" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O199" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
-        </is>
-      </c>
-      <c r="P199" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz), namu.wiki(2018.5 생산 중단, 재고 판매 후 단종)</t>
+        </is>
+      </c>
+      <c r="P199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
@@ -13364,7 +13359,7 @@
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -13412,7 +13407,7 @@
       </c>
       <c r="O200" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
         </is>
       </c>
       <c r="P200" s="11" t="inlineStr"/>
@@ -13430,7 +13425,7 @@
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -13478,7 +13473,7 @@
       </c>
       <c r="O201" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
         </is>
       </c>
       <c r="P201" s="11" t="inlineStr"/>
@@ -13496,7 +13491,7 @@
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -13544,7 +13539,7 @@
       </c>
       <c r="O202" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
         </is>
       </c>
       <c r="P202" s="11" t="inlineStr"/>
@@ -13562,7 +13557,7 @@
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
@@ -13580,7 +13575,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G203" s="5" t="inlineStr">
+      <c r="G203" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13603,21 +13598,17 @@
         </is>
       </c>
       <c r="M203" s="11" t="inlineStr"/>
-      <c r="N203" s="5" t="inlineStr">
+      <c r="N203" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O203" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
-        </is>
-      </c>
-      <c r="P203" s="5" t="inlineStr">
-        <is>
-          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
+        </is>
+      </c>
+      <c r="P203" s="11" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
@@ -13632,7 +13623,7 @@
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
@@ -13650,7 +13641,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G204" s="5" t="inlineStr">
+      <c r="G204" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13673,21 +13664,17 @@
         </is>
       </c>
       <c r="M204" s="11" t="inlineStr"/>
-      <c r="N204" s="5" t="inlineStr">
+      <c r="N204" s="11" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O204" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
-        </is>
-      </c>
-      <c r="P204" s="5" t="inlineStr">
-        <is>
-          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
+        </is>
+      </c>
+      <c r="P204" s="11" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
@@ -13697,12 +13684,12 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
@@ -13720,7 +13707,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G205" s="11" t="inlineStr">
+      <c r="G205" s="5" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13739,21 +13726,25 @@
       <c r="K205" s="11" t="inlineStr"/>
       <c r="L205" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M205" s="11" t="inlineStr"/>
-      <c r="N205" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N205" s="5" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P205" s="11" t="inlineStr"/>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+        </is>
+      </c>
+      <c r="P205" s="5" t="inlineStr">
+        <is>
+          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -13763,12 +13754,12 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
@@ -13786,7 +13777,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G206" s="11" t="inlineStr">
+      <c r="G206" s="5" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13805,21 +13796,25 @@
       <c r="K206" s="11" t="inlineStr"/>
       <c r="L206" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N206" s="5" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O206" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
-        </is>
-      </c>
-      <c r="P206" s="11" t="inlineStr"/>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
+        </is>
+      </c>
+      <c r="P206" s="5" t="inlineStr">
+        <is>
+          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -13834,7 +13829,7 @@
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
@@ -13852,7 +13847,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G207" s="5" t="inlineStr">
+      <c r="G207" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13871,25 +13866,21 @@
       <c r="K207" s="11" t="inlineStr"/>
       <c r="L207" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M207" s="11" t="inlineStr"/>
-      <c r="N207" s="5" t="inlineStr">
+      <c r="N207" s="11" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P207" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P207" s="11" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -13904,7 +13895,7 @@
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
@@ -13922,7 +13913,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G208" s="5" t="inlineStr">
+      <c r="G208" s="11" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13941,25 +13932,21 @@
       <c r="K208" s="11" t="inlineStr"/>
       <c r="L208" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M208" s="11" t="inlineStr"/>
-      <c r="N208" s="5" t="inlineStr">
+      <c r="N208" s="11" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O208" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P208" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
+        </is>
+      </c>
+      <c r="P208" s="11" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -13974,7 +13961,7 @@
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
@@ -14044,7 +14031,7 @@
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -14114,7 +14101,7 @@
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -14162,7 +14149,7 @@
       </c>
       <c r="O211" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
       <c r="P211" s="5" t="inlineStr">
@@ -14179,22 +14166,22 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D212" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
@@ -14202,9 +14189,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G212" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H212" s="11" t="inlineStr">
@@ -14221,21 +14208,25 @@
       <c r="K212" s="11" t="inlineStr"/>
       <c r="L212" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M212" s="11" t="inlineStr"/>
-      <c r="N212" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N212" s="5" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O212" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P212" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+        </is>
+      </c>
+      <c r="P212" s="5" t="inlineStr">
+        <is>
+          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -14245,22 +14236,22 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D213" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2025(단종)</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
@@ -14268,9 +14259,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G213" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -14287,21 +14278,25 @@
       <c r="K213" s="11" t="inlineStr"/>
       <c r="L213" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M213" s="11" t="inlineStr"/>
-      <c r="N213" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="N213" s="5" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O213" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
-        </is>
-      </c>
-      <c r="P213" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
+        </is>
+      </c>
+      <c r="P213" s="5" t="inlineStr">
+        <is>
+          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -14316,7 +14311,7 @@
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
@@ -14364,7 +14359,7 @@
       </c>
       <c r="O214" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
         </is>
       </c>
       <c r="P214" s="11" t="inlineStr"/>
@@ -14382,7 +14377,7 @@
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
@@ -14430,7 +14425,7 @@
       </c>
       <c r="O215" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
         </is>
       </c>
       <c r="P215" s="11" t="inlineStr"/>
@@ -14443,7 +14438,7 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C216" s="11" t="inlineStr">
@@ -14466,7 +14461,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G216" s="14" t="inlineStr">
+      <c r="G216" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -14485,21 +14480,21 @@
       <c r="K216" s="11" t="inlineStr"/>
       <c r="L216" s="11" t="inlineStr">
         <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M216" s="11" t="inlineStr"/>
-      <c r="N216" s="14" t="inlineStr">
+      <c r="N216" s="11" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
       <c r="O216" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P216" s="14" t="n"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
+        </is>
+      </c>
+      <c r="P216" s="11" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -14509,12 +14504,12 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
@@ -14532,7 +14527,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G217" s="14" t="inlineStr">
+      <c r="G217" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -14551,21 +14546,21 @@
       <c r="K217" s="11" t="inlineStr"/>
       <c r="L217" s="11" t="inlineStr">
         <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M217" s="11" t="inlineStr"/>
-      <c r="N217" s="14" t="inlineStr">
+      <c r="N217" s="11" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
       <c r="O217" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P217" s="14" t="n"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
+        </is>
+      </c>
+      <c r="P217" s="11" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
@@ -14580,7 +14575,7 @@
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
@@ -14641,22 +14636,22 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>콜로라도 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C219" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E219" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -14664,40 +14659,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G219" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
+      <c r="G219" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I219" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I219" s="11" t="inlineStr"/>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K219" s="11" t="inlineStr"/>
-      <c r="L219" s="11" t="inlineStr"/>
+      <c r="L219" s="11" t="inlineStr">
+        <is>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
+        </is>
+      </c>
       <c r="M219" s="11" t="inlineStr"/>
-      <c r="N219" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="N219" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O219" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P219" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P219" s="14" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="inlineStr">
@@ -14707,22 +14702,22 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>콜로라도 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C220" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D220" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E220" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
@@ -14730,40 +14725,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G220" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
+      <c r="G220" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I220" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I220" s="11" t="inlineStr"/>
       <c r="J220" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K220" s="11" t="inlineStr"/>
-      <c r="L220" s="11" t="inlineStr"/>
+      <c r="L220" s="11" t="inlineStr">
+        <is>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
+        </is>
+      </c>
       <c r="M220" s="11" t="inlineStr"/>
-      <c r="N220" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="N220" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O220" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
-        </is>
-      </c>
-      <c r="P220" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P220" s="14" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
@@ -14778,7 +14773,7 @@
       </c>
       <c r="C221" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
@@ -14826,7 +14821,7 @@
       </c>
       <c r="O221" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
         </is>
       </c>
       <c r="P221" s="11" t="inlineStr"/>
@@ -14844,7 +14839,7 @@
       </c>
       <c r="C222" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
@@ -14910,7 +14905,7 @@
       </c>
       <c r="C223" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
@@ -14976,7 +14971,7 @@
       </c>
       <c r="C224" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
@@ -14996,7 +14991,7 @@
       </c>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>ID46[2세대, ~2024.4]</t>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H224" s="11" t="inlineStr">
@@ -15014,20 +15009,20 @@
           <t>HU100, ILCO B119</t>
         </is>
       </c>
-      <c r="K224" s="11" t="n"/>
-      <c r="L224" s="11" t="n"/>
-      <c r="M224" s="11" t="n"/>
+      <c r="K224" s="11" t="inlineStr"/>
+      <c r="L224" s="11" t="inlineStr"/>
+      <c r="M224" s="11" t="inlineStr"/>
       <c r="N224" s="11" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저[2세대]</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O224" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
-        </is>
-      </c>
-      <c r="P224" s="11" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P224" s="11" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
@@ -15042,17 +15037,17 @@
       </c>
       <c r="C225" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D225" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E225" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
@@ -15062,38 +15057,38 @@
       </c>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>ID49[3세대, 2024.7~]</t>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I225" s="11" t="n"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
           <t>HU100, ILCO B119</t>
         </is>
       </c>
-      <c r="K225" s="11" t="n"/>
-      <c r="L225" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M225" s="11" t="n"/>
+      <c r="K225" s="11" t="inlineStr"/>
+      <c r="L225" s="11" t="inlineStr"/>
+      <c r="M225" s="11" t="inlineStr"/>
       <c r="N225" s="11" t="inlineStr">
         <is>
-          <t>PEPS[3세대]</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O225" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
-        </is>
-      </c>
-      <c r="P225" s="11" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P225" s="11" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
@@ -15108,17 +15103,17 @@
       </c>
       <c r="C226" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D226" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E226" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -15128,38 +15123,38 @@
       </c>
       <c r="G226" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46[2세대, ~2024.4]</t>
         </is>
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I226" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I226" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J226" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K226" s="11" t="inlineStr"/>
-      <c r="L226" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M226" s="11" t="inlineStr"/>
+          <t>HU100, ILCO B119</t>
+        </is>
+      </c>
+      <c r="K226" s="11" t="n"/>
+      <c r="L226" s="11" t="n"/>
+      <c r="M226" s="11" t="n"/>
       <c r="N226" s="11" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>트랜스폰더 이모빌라이저[2세대]</t>
         </is>
       </c>
       <c r="O226" s="11" t="inlineStr">
         <is>
-          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
-        </is>
-      </c>
-      <c r="P226" s="11" t="inlineStr"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P226" s="11" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
@@ -15174,58 +15169,190 @@
       </c>
       <c r="C227" s="11" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>ID49[3세대, 2024.7~]</t>
+        </is>
+      </c>
+      <c r="H227" s="11" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="n"/>
+      <c r="J227" s="11" t="inlineStr">
+        <is>
+          <t>HU100, ILCO B119</t>
+        </is>
+      </c>
+      <c r="K227" s="11" t="n"/>
+      <c r="L227" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
+      <c r="M227" s="11" t="n"/>
+      <c r="N227" s="11" t="inlineStr">
+        <is>
+          <t>PEPS[3세대]</t>
+        </is>
+      </c>
+      <c r="O227" s="11" t="inlineStr">
+        <is>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P227" s="11" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>쉐보레(GM대우)</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>콜로라도 (쉐보레)</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G228" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
+        </is>
+      </c>
+      <c r="H228" s="11" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="inlineStr"/>
+      <c r="J228" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
+      <c r="K228" s="11" t="inlineStr"/>
+      <c r="L228" s="11" t="inlineStr">
+        <is>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
+      <c r="M228" s="11" t="inlineStr"/>
+      <c r="N228" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
+        </is>
+      </c>
+      <c r="O228" s="11" t="inlineStr">
+        <is>
+          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
+        </is>
+      </c>
+      <c r="P228" s="11" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>쉐보레(GM대우)</t>
+        </is>
+      </c>
+      <c r="B229" s="11" t="inlineStr">
+        <is>
+          <t>콜로라도 (쉐보레)</t>
+        </is>
+      </c>
+      <c r="C229" s="11" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D227" s="8" t="inlineStr">
+      <c r="D229" s="8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E227" s="7" t="inlineStr">
+      <c r="E229" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G227" s="11" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G229" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
       </c>
-      <c r="H227" s="11" t="inlineStr">
+      <c r="H229" s="11" t="inlineStr">
         <is>
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I227" s="11" t="inlineStr"/>
-      <c r="J227" s="11" t="inlineStr">
+      <c r="I229" s="11" t="inlineStr"/>
+      <c r="J229" s="11" t="inlineStr">
         <is>
           <t>HU100</t>
         </is>
       </c>
-      <c r="K227" s="11" t="inlineStr"/>
-      <c r="L227" s="11" t="inlineStr">
+      <c r="K229" s="11" t="inlineStr"/>
+      <c r="L229" s="11" t="inlineStr">
         <is>
           <t>13548441[3세대], FCC YG0G21TB2</t>
         </is>
       </c>
-      <c r="M227" s="11" t="inlineStr"/>
-      <c r="N227" s="11" t="inlineStr">
+      <c r="M229" s="11" t="inlineStr"/>
+      <c r="N229" s="11" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
-      <c r="O227" s="11" t="inlineStr">
+      <c r="O229" s="11" t="inlineStr">
         <is>
           <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
         </is>
       </c>
-      <c r="P227" s="11" t="inlineStr"/>
+      <c r="P229" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P226"/>
@@ -15239,335 +15366,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr"/>
+      <c r="A2" s="17" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr"/>
+      <c r="A14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr"/>
+      <c r="A18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>- 스파크 2013: 2013년형은 이모빌라이저 없음, 2014년형(2013.5.14 출시)부터 이모빌라이저 폴딩키 적용(나무위키 스파크 2세대·차프라이스 2013.5 가격표) — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>- 토스카 2006: 2007년형(2006.11 출시)부터 이모빌라이저 신규 적용(이투데이 "GM대우 2007년형 토스카 출시") — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>- 서버번: 한국GM이 2024.10부터 국내 정식 판매(위키백과) — 2023년식 행 삭제. 키는 타호와 같은 스마트키(YG0G21TB2, 433MHz, ID49)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>- 세대가 바뀌는 해는 세대별로 행을 나눔(구세대 1행 + 신세대 1행). 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 한 행에 전·후 값을 함께 적음</t>
+      <c r="A50" s="19" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>※ 행 구분 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1557,7 +1560,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>ID46(PCF7941E)</t>
         </is>
@@ -1576,7 +1579,7 @@
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="11" t="inlineStr"/>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>BCM</t>
         </is>
@@ -1586,11 +1589,7 @@
           <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>M300 폴딩키 자료 없음 — M400 폴딩키 기준 추정</t>
-        </is>
-      </c>
+      <c r="P20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -4807,7 +4806,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>ID46[Extended]</t>
         </is>
@@ -4826,7 +4825,7 @@
       <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr"/>
       <c r="M69" s="11" t="inlineStr"/>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="N69" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -4836,11 +4835,7 @@
           <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
         </is>
       </c>
-      <c r="P69" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
@@ -4873,7 +4868,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>ID46[Extended]</t>
         </is>
@@ -4892,7 +4887,7 @@
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr"/>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="N70" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -4902,11 +4897,7 @@
           <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
         </is>
       </c>
-      <c r="P70" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
@@ -4939,7 +4930,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>ID46[Extended]</t>
         </is>
@@ -4958,7 +4949,7 @@
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
       <c r="M71" s="11" t="inlineStr"/>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="N71" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -4968,11 +4959,7 @@
           <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
         </is>
       </c>
-      <c r="P71" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
@@ -5005,7 +4992,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>ID46[Extended]</t>
         </is>
@@ -5024,7 +5011,7 @@
       <c r="K72" s="11" t="inlineStr"/>
       <c r="L72" s="11" t="inlineStr"/>
       <c r="M72" s="11" t="inlineStr"/>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="N72" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -5034,11 +5021,7 @@
           <t>northcoastkeyless.com·uhs-hardware.com(볼트 2016-2019 스마트키 HYQ4AA 13585722/13508767/13529664, ID46), kama.or.kr·namu.wiki(2세대 볼트 2016.8 렌터카·카셰어링 공급, 2017.4 일반 출시, 2019.3 단종)</t>
         </is>
       </c>
-      <c r="P72" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
@@ -11677,7 +11660,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G174" s="5" t="inlineStr">
+      <c r="G174" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -11696,7 +11679,7 @@
       <c r="K174" s="11" t="inlineStr"/>
       <c r="L174" s="11" t="inlineStr"/>
       <c r="M174" s="11" t="inlineStr"/>
-      <c r="N174" s="5" t="inlineStr">
+      <c r="N174" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -11706,11 +11689,7 @@
           <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
-      <c r="P174" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -11743,7 +11722,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G175" s="5" t="inlineStr">
+      <c r="G175" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -11762,7 +11741,7 @@
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="11" t="inlineStr"/>
       <c r="M175" s="11" t="inlineStr"/>
-      <c r="N175" s="5" t="inlineStr">
+      <c r="N175" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -11772,11 +11751,7 @@
           <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
-      <c r="P175" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
@@ -11809,7 +11784,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G176" s="5" t="inlineStr">
+      <c r="G176" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -11828,7 +11803,7 @@
       <c r="K176" s="11" t="inlineStr"/>
       <c r="L176" s="11" t="inlineStr"/>
       <c r="M176" s="11" t="inlineStr"/>
-      <c r="N176" s="5" t="inlineStr">
+      <c r="N176" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -11838,11 +11813,7 @@
           <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
-      <c r="P176" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -11875,7 +11846,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G177" s="5" t="inlineStr">
+      <c r="G177" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -11894,7 +11865,7 @@
       <c r="K177" s="11" t="inlineStr"/>
       <c r="L177" s="11" t="inlineStr"/>
       <c r="M177" s="11" t="inlineStr"/>
-      <c r="N177" s="5" t="inlineStr">
+      <c r="N177" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -11904,11 +11875,7 @@
           <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
-      <c r="P177" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -11941,7 +11908,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G178" s="5" t="inlineStr">
+      <c r="G178" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -11960,7 +11927,7 @@
       <c r="K178" s="11" t="inlineStr"/>
       <c r="L178" s="11" t="inlineStr"/>
       <c r="M178" s="11" t="inlineStr"/>
-      <c r="N178" s="5" t="inlineStr">
+      <c r="N178" s="14" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
@@ -11970,11 +11937,7 @@
           <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
         </is>
       </c>
-      <c r="P178" s="5" t="inlineStr">
-        <is>
-          <t>국내형(433MHz) 스마트키 자료 없음 — 칩은 미국형 기준</t>
-        </is>
-      </c>
+      <c r="P178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -13707,7 +13670,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G205" s="5" t="inlineStr">
+      <c r="G205" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13730,7 +13693,7 @@
         </is>
       </c>
       <c r="M205" s="11" t="inlineStr"/>
-      <c r="N205" s="5" t="inlineStr">
+      <c r="N205" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -13740,11 +13703,7 @@
           <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
         </is>
       </c>
-      <c r="P205" s="5" t="inlineStr">
-        <is>
-          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
-        </is>
-      </c>
+      <c r="P205" s="14" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -13777,7 +13736,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G206" s="5" t="inlineStr">
+      <c r="G206" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13800,7 +13759,7 @@
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="5" t="inlineStr">
+      <c r="N206" s="14" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
         </is>
@@ -13810,11 +13769,7 @@
           <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
         </is>
       </c>
-      <c r="P206" s="5" t="inlineStr">
-        <is>
-          <t>HYQ4EA 적용 자료가 2022년까지 — 이후 연식 추정</t>
-        </is>
-      </c>
+      <c r="P206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -13979,7 +13934,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G209" s="5" t="inlineStr">
+      <c r="G209" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -14002,7 +13957,7 @@
         </is>
       </c>
       <c r="M209" s="11" t="inlineStr"/>
-      <c r="N209" s="5" t="inlineStr">
+      <c r="N209" s="14" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
@@ -14012,11 +13967,7 @@
           <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
-      <c r="P209" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P209" s="14" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
@@ -14049,7 +14000,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G210" s="5" t="inlineStr">
+      <c r="G210" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -14072,7 +14023,7 @@
         </is>
       </c>
       <c r="M210" s="11" t="inlineStr"/>
-      <c r="N210" s="5" t="inlineStr">
+      <c r="N210" s="14" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
@@ -14082,11 +14033,7 @@
           <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
-      <c r="P210" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P210" s="14" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
@@ -14119,7 +14066,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G211" s="5" t="inlineStr">
+      <c r="G211" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -14142,7 +14089,7 @@
         </is>
       </c>
       <c r="M211" s="11" t="inlineStr"/>
-      <c r="N211" s="5" t="inlineStr">
+      <c r="N211" s="14" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
@@ -14152,11 +14099,7 @@
           <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
-      <c r="P211" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P211" s="14" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
@@ -14189,7 +14132,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G212" s="5" t="inlineStr">
+      <c r="G212" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -14212,7 +14155,7 @@
         </is>
       </c>
       <c r="M212" s="11" t="inlineStr"/>
-      <c r="N212" s="5" t="inlineStr">
+      <c r="N212" s="14" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
@@ -14222,11 +14165,7 @@
           <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
-      <c r="P212" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P212" s="14" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -14259,7 +14198,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G213" s="5" t="inlineStr">
+      <c r="G213" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -14282,7 +14221,7 @@
         </is>
       </c>
       <c r="M213" s="11" t="inlineStr"/>
-      <c r="N213" s="5" t="inlineStr">
+      <c r="N213" s="14" t="inlineStr">
         <is>
           <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
@@ -14292,11 +14231,7 @@
           <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
         </is>
       </c>
-      <c r="P213" s="5" t="inlineStr">
-        <is>
-          <t>2021년 이후 키(HYQ4ES)는 해외 판매처 적용표 기준 — 국내 확인 안 됨</t>
-        </is>
-      </c>
+      <c r="P213" s="14" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -15366,352 +15301,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr"/>
+      <c r="A2" s="20" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr"/>
+      <c r="A14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr"/>
+      <c r="A18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
+      <c r="A27" s="20" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="n"/>
+      <c r="A35" s="20" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
+      <c r="A44" s="20" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>- 스파크 2013: 2013년형은 이모빌라이저 없음, 2014년형(2013.5.14 출시)부터 이모빌라이저 폴딩키 적용(나무위키 스파크 2세대·차프라이스 2013.5 가격표) — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>- 토스카 2006: 2007년형(2006.11 출시)부터 이모빌라이저 신규 적용(이투데이 "GM대우 2007년형 토스카 출시") — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>- 서버번: 한국GM이 2024.10부터 국내 정식 판매(위키백과) — 2023년식 행 삭제. 키는 타호와 같은 스마트키(YG0G21TB2, 433MHz, ID49)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="n"/>
+      <c r="A50" s="20" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>- 스파크 M300 2014: GM 부품몰(c-mall) "스파크 2014년형 폴딩 키", 스파크 2012-2016 폴딩키 ID46(PCF7941E) 433MHz, 한국GM 블로그 "스파크S 폴딩키는 아베오·크루즈·알페온 키와 거의 같음" — 추정 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>- 볼트(Volt) 2016-2019: 433MHz 스마트키 FCC HYQ4EA(13585728·13529638) = Philips ID46(locksmithkeyless) — 국내(433MHz) 사양과 같은 주파수 키로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>- 볼트 EV 2017-2021: 433MHz 스마트키 HYQ4EA ID46(2017-2022 볼트 적용), 미국형 315MHz는 HYQ4AA — 국내 433MHz 키 칩 ID46 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>- 이쿼녹스 2023-2024: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 이쿼녹스 적용, 46E 칩), 미국형 315MHz HYQ4AS도 ID46 — 칩 ID46 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>- 트래버스(2세대) 2021-2025: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 트래버스 적용) ID46 — 국내 판매분(2025.3 종료)은 2세대</t>
         </is>
       </c>
     </row>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -15518,7 +15518,7 @@
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -14743,7 +14743,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K221" s="11" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="J222" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K222" s="11" t="inlineStr"/>
@@ -14875,7 +14875,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K223" s="11" t="inlineStr"/>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="J224" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K224" s="11" t="inlineStr"/>
@@ -15007,7 +15007,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K225" s="11" t="inlineStr"/>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="J226" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K226" s="11" t="n"/>
@@ -15135,7 +15135,7 @@
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>HU100, ILCO B119</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K227" s="11" t="n"/>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -690,7 +693,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr"/>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
+        </is>
+      </c>
       <c r="J2" s="11" t="inlineStr"/>
       <c r="K2" s="11" t="inlineStr"/>
       <c r="L2" s="11" t="inlineStr"/>
@@ -740,7 +747,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
+        </is>
+      </c>
       <c r="J3" s="11" t="inlineStr"/>
       <c r="K3" s="11" t="inlineStr"/>
       <c r="L3" s="11" t="inlineStr"/>
@@ -790,7 +801,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="inlineStr"/>
       <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr"/>
@@ -840,11 +855,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr"/>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
+        </is>
+      </c>
       <c r="J5" s="11" t="inlineStr"/>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr"/>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>96567446[리모콘]</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
@@ -890,11 +913,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
+        </is>
+      </c>
       <c r="J6" s="11" t="inlineStr"/>
       <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>96567446[리모콘]</t>
+        </is>
+      </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
           <t>확인 불가</t>
@@ -940,7 +971,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr"/>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
+        </is>
+      </c>
       <c r="J7" s="11" t="inlineStr"/>
       <c r="K7" s="11" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
@@ -990,11 +1025,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr"/>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>96601589</t>
+        </is>
+      </c>
       <c r="J8" s="11" t="inlineStr"/>
       <c r="K8" s="11" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>96498848[리모콘, 추정]</t>
+        </is>
+      </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1036,11 +1079,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>96601589</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>96498848[리모콘]</t>
+        </is>
+      </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1082,11 +1133,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>96601589</t>
+        </is>
+      </c>
       <c r="J10" s="11" t="inlineStr"/>
       <c r="K10" s="11" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>96498848[리모콘]</t>
+        </is>
+      </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1128,11 +1187,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr"/>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>96601589</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="inlineStr"/>
       <c r="K11" s="11" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>96498848[리모콘]</t>
+        </is>
+      </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1174,11 +1241,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>96601589</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>96498848[리모콘]</t>
+        </is>
+      </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1358,11 +1433,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr"/>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>94823322[리모콘 미적용]</t>
+        </is>
+      </c>
       <c r="J16" s="11" t="inlineStr"/>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>95487768[리모콘]</t>
+        </is>
+      </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1404,11 +1487,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>94823322[리모콘 미적용]</t>
+        </is>
+      </c>
       <c r="J17" s="11" t="inlineStr"/>
       <c r="K17" s="11" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
-      <c r="M17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>95487768[리모콘], 95016182[리모콘, 원격시동]</t>
+        </is>
+      </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
           <t>미적용[국내형]</t>
@@ -1450,11 +1541,19 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I18" s="11" t="n"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>94823322[리모콘 미적용]</t>
+        </is>
+      </c>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>95487768[리모콘], 95016182[리모콘, 원격시동]</t>
+        </is>
+      </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
           <t>미적용[2013년형]</t>
@@ -1483,45 +1582,29 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>ID46(PCF7941E)[2014년형~]</t>
-        </is>
-      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="14" t="n"/>
       <c r="H19" s="11" t="inlineStr">
         <is>
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>HU100[M400 폴딩키 기준]</t>
-        </is>
-      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>94823322[리모콘 미적용]</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[2014년형~]</t>
-        </is>
-      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>95487768[리모콘], 95016182[리모콘, 원격시동], 42670241[2014년형~, CVT 제외], 42695008[2014년형~, 스파크S CVT]</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="n"/>
       <c r="O19" s="11" t="inlineStr">
         <is>
           <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
@@ -1570,7 +1653,11 @@
           <t>폴딩키</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>94823322[리모콘 미적용]</t>
+        </is>
+      </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
           <t>HU100[M400 폴딩키 기준]</t>
@@ -1578,7 +1665,11 @@
       </c>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>42670241[2014년형~, CVT 제외], 42695008[2014년형~, 스파크S CVT]</t>
+        </is>
+      </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -3488,7 +3579,11 @@
       </c>
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
-      <c r="M49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>96550512[리모콘, 무선시동 미적용], 96499642[리모콘, 세단, 무선시동]</t>
+        </is>
+      </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -3554,7 +3649,11 @@
       </c>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
-      <c r="M50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>96550512[리모콘, 무선시동 미적용], 96499642[리모콘, 세단, 무선시동]</t>
+        </is>
+      </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -3620,7 +3719,11 @@
       </c>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
-      <c r="M51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>96550512[리모콘, 무선시동 미적용], 96499642[리모콘, 세단, 무선시동]</t>
+        </is>
+      </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -3686,7 +3789,11 @@
       </c>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
-      <c r="M52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>96499642[리모콘, 세단, 무선시동], 96458343[리모콘, 도난경보], 96458344[리모콘, 도난경보]</t>
+        </is>
+      </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -3752,7 +3859,11 @@
       </c>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr"/>
-      <c r="M53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>96499642[리모콘, 세단, 무선시동], 96458343[리모콘, 도난경보], 96458344[리모콘, 도난경보]</t>
+        </is>
+      </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -3818,7 +3929,11 @@
       </c>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
-      <c r="M54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>96458343[리모콘, 도난경보], 96458344[리모콘, 도난경보]</t>
+        </is>
+      </c>
       <c r="N54" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5072,7 +5187,11 @@
       </c>
       <c r="K73" s="11" t="inlineStr"/>
       <c r="L73" s="11" t="inlineStr"/>
-      <c r="M73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5138,7 +5257,11 @@
       </c>
       <c r="K74" s="11" t="inlineStr"/>
       <c r="L74" s="11" t="inlineStr"/>
-      <c r="M74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5204,7 +5327,11 @@
       </c>
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="11" t="inlineStr"/>
-      <c r="M75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5270,7 +5397,11 @@
       </c>
       <c r="K76" s="11" t="inlineStr"/>
       <c r="L76" s="11" t="inlineStr"/>
-      <c r="M76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5336,7 +5467,11 @@
       </c>
       <c r="K77" s="11" t="inlineStr"/>
       <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5402,7 +5537,11 @@
       </c>
       <c r="K78" s="11" t="inlineStr"/>
       <c r="L78" s="11" t="inlineStr"/>
-      <c r="M78" s="11" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5468,7 +5607,11 @@
       </c>
       <c r="K79" s="11" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>96438485[리모콘, 도난방지, 무선시동], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[수출형 기준]</t>
@@ -5518,7 +5661,11 @@
       <c r="J80" s="11" t="n"/>
       <c r="K80" s="11" t="n"/>
       <c r="L80" s="11" t="n"/>
-      <c r="M80" s="11" t="n"/>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N80" s="14" t="inlineStr">
         <is>
           <t>미적용[2006년형]</t>
@@ -5576,7 +5723,11 @@
       <c r="J81" s="11" t="n"/>
       <c r="K81" s="11" t="n"/>
       <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N81" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저[2007년형, 2006.11~]</t>
@@ -5634,7 +5785,11 @@
       <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="11" t="inlineStr"/>
       <c r="L82" s="11" t="inlineStr"/>
-      <c r="M82" s="11" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N82" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -5696,7 +5851,11 @@
       <c r="J83" s="11" t="inlineStr"/>
       <c r="K83" s="11" t="inlineStr"/>
       <c r="L83" s="11" t="inlineStr"/>
-      <c r="M83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N83" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -5758,7 +5917,11 @@
       <c r="J84" s="11" t="inlineStr"/>
       <c r="K84" s="11" t="inlineStr"/>
       <c r="L84" s="11" t="inlineStr"/>
-      <c r="M84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N84" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -5820,7 +5983,11 @@
       <c r="J85" s="11" t="inlineStr"/>
       <c r="K85" s="11" t="inlineStr"/>
       <c r="L85" s="11" t="inlineStr"/>
-      <c r="M85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -5882,7 +6049,11 @@
       <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr"/>
       <c r="L86" s="11" t="inlineStr"/>
-      <c r="M86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr">
+        <is>
+          <t>96646269[리모콘, 이모빌라이저], 96327968[리모콘, 이모빌라이저 미적용]</t>
+        </is>
+      </c>
       <c r="N86" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -5947,8 +6118,16 @@
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>13582828</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>13582829</t>
+        </is>
+      </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
           <t>BCM, PEPS</t>
@@ -6009,8 +6188,16 @@
         </is>
       </c>
       <c r="K88" s="11" t="inlineStr"/>
-      <c r="L88" s="11" t="n"/>
-      <c r="M88" s="11" t="n"/>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>13582828</t>
+        </is>
+      </c>
+      <c r="M88" s="11" t="inlineStr">
+        <is>
+          <t>13582829</t>
+        </is>
+      </c>
       <c r="N88" s="11" t="inlineStr">
         <is>
           <t>BCM, PEPS</t>
@@ -6071,8 +6258,16 @@
         </is>
       </c>
       <c r="K89" s="11" t="inlineStr"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>13582828</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>13582829</t>
+        </is>
+      </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
           <t>BCM, PEPS</t>
@@ -6135,7 +6330,7 @@
       <c r="K90" s="11" t="inlineStr"/>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>P13586777[2014~2015]</t>
+          <t>13586777</t>
         </is>
       </c>
       <c r="M90" s="11" t="n"/>
@@ -6201,7 +6396,7 @@
       <c r="K91" s="11" t="inlineStr"/>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>P13586777[2014~2015]</t>
+          <t>13586777</t>
         </is>
       </c>
       <c r="M91" s="11" t="n"/>
@@ -6265,8 +6460,16 @@
         </is>
       </c>
       <c r="K92" s="11" t="inlineStr"/>
-      <c r="L92" s="11" t="n"/>
-      <c r="M92" s="11" t="n"/>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
+          <t>13586777[추정]</t>
+        </is>
+      </c>
+      <c r="M92" s="11" t="inlineStr">
+        <is>
+          <t>13582829[추정]</t>
+        </is>
+      </c>
       <c r="N92" s="11" t="inlineStr">
         <is>
           <t>BCM, PEPS</t>
@@ -6790,7 +6993,11 @@
       </c>
       <c r="K100" s="11" t="inlineStr"/>
       <c r="L100" s="11" t="n"/>
-      <c r="M100" s="11" t="inlineStr"/>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>20972992[추정]</t>
+        </is>
+      </c>
       <c r="N100" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -6856,7 +7063,11 @@
       </c>
       <c r="K101" s="11" t="inlineStr"/>
       <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>20972992</t>
+        </is>
+      </c>
       <c r="N101" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -6922,7 +7133,11 @@
       </c>
       <c r="K102" s="11" t="inlineStr"/>
       <c r="L102" s="11" t="n"/>
-      <c r="M102" s="11" t="inlineStr"/>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>20972992</t>
+        </is>
+      </c>
       <c r="N102" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -6988,7 +7203,11 @@
       </c>
       <c r="K103" s="11" t="inlineStr"/>
       <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>20972992</t>
+        </is>
+      </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -7054,7 +7273,11 @@
       </c>
       <c r="K104" s="11" t="inlineStr"/>
       <c r="L104" s="11" t="n"/>
-      <c r="M104" s="11" t="inlineStr"/>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>23111355</t>
+        </is>
+      </c>
       <c r="N104" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -7120,7 +7343,11 @@
       </c>
       <c r="K105" s="11" t="inlineStr"/>
       <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>23111355</t>
+        </is>
+      </c>
       <c r="N105" s="5" t="inlineStr">
         <is>
           <t>PEPS, BCM</t>
@@ -10318,7 +10545,7 @@
       <c r="L153" s="11" t="inlineStr"/>
       <c r="M153" s="11" t="inlineStr">
         <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
         </is>
       </c>
       <c r="N153" s="11" t="inlineStr">
@@ -10384,7 +10611,7 @@
       <c r="L154" s="11" t="inlineStr"/>
       <c r="M154" s="11" t="inlineStr">
         <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
         </is>
       </c>
       <c r="N154" s="11" t="inlineStr">
@@ -10450,7 +10677,7 @@
       <c r="L155" s="11" t="inlineStr"/>
       <c r="M155" s="11" t="inlineStr">
         <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
         </is>
       </c>
       <c r="N155" s="11" t="inlineStr">
@@ -10516,7 +10743,7 @@
       <c r="L156" s="11" t="inlineStr"/>
       <c r="M156" s="11" t="inlineStr">
         <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형]</t>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
         </is>
       </c>
       <c r="N156" s="11" t="inlineStr">
@@ -10580,7 +10807,11 @@
       </c>
       <c r="K157" s="11" t="inlineStr"/>
       <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="n"/>
+      <c r="M157" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N157" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10642,7 +10873,11 @@
       </c>
       <c r="K158" s="11" t="inlineStr"/>
       <c r="L158" s="11" t="inlineStr"/>
-      <c r="M158" s="11" t="n"/>
+      <c r="M158" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N158" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10704,7 +10939,11 @@
       </c>
       <c r="K159" s="11" t="inlineStr"/>
       <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="n"/>
+      <c r="M159" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N159" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10766,7 +11005,11 @@
       </c>
       <c r="K160" s="11" t="inlineStr"/>
       <c r="L160" s="11" t="inlineStr"/>
-      <c r="M160" s="11" t="n"/>
+      <c r="M160" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N160" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10828,7 +11071,11 @@
       </c>
       <c r="K161" s="11" t="inlineStr"/>
       <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="n"/>
+      <c r="M161" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N161" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -10890,7 +11137,11 @@
       </c>
       <c r="K162" s="11" t="inlineStr"/>
       <c r="L162" s="11" t="inlineStr"/>
-      <c r="M162" s="11" t="n"/>
+      <c r="M162" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
       <c r="N162" s="11" t="inlineStr">
         <is>
           <t>BCM</t>
@@ -11677,7 +11928,11 @@
         </is>
       </c>
       <c r="K174" s="11" t="inlineStr"/>
-      <c r="L174" s="11" t="inlineStr"/>
+      <c r="L174" s="11" t="inlineStr">
+        <is>
+          <t>13529642</t>
+        </is>
+      </c>
       <c r="M174" s="11" t="inlineStr"/>
       <c r="N174" s="14" t="inlineStr">
         <is>
@@ -11739,7 +11994,11 @@
         </is>
       </c>
       <c r="K175" s="11" t="inlineStr"/>
-      <c r="L175" s="11" t="inlineStr"/>
+      <c r="L175" s="11" t="inlineStr">
+        <is>
+          <t>13529642</t>
+        </is>
+      </c>
       <c r="M175" s="11" t="inlineStr"/>
       <c r="N175" s="14" t="inlineStr">
         <is>
@@ -11801,7 +12060,11 @@
         </is>
       </c>
       <c r="K176" s="11" t="inlineStr"/>
-      <c r="L176" s="11" t="inlineStr"/>
+      <c r="L176" s="11" t="inlineStr">
+        <is>
+          <t>13529642</t>
+        </is>
+      </c>
       <c r="M176" s="11" t="inlineStr"/>
       <c r="N176" s="14" t="inlineStr">
         <is>
@@ -11863,7 +12126,11 @@
         </is>
       </c>
       <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr"/>
+      <c r="L177" s="11" t="inlineStr">
+        <is>
+          <t>13529642</t>
+        </is>
+      </c>
       <c r="M177" s="11" t="inlineStr"/>
       <c r="N177" s="14" t="inlineStr">
         <is>
@@ -11925,7 +12192,11 @@
         </is>
       </c>
       <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr"/>
+      <c r="L178" s="11" t="inlineStr">
+        <is>
+          <t>13529642</t>
+        </is>
+      </c>
       <c r="M178" s="11" t="inlineStr"/>
       <c r="N178" s="14" t="inlineStr">
         <is>
@@ -12268,7 +12539,11 @@
       </c>
       <c r="K183" s="11" t="inlineStr"/>
       <c r="L183" s="11" t="inlineStr"/>
-      <c r="M183" s="11" t="n"/>
+      <c r="M183" s="11" t="inlineStr">
+        <is>
+          <t>96628227[리모콘, 추정]</t>
+        </is>
+      </c>
       <c r="N183" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12330,7 +12605,11 @@
       </c>
       <c r="K184" s="11" t="inlineStr"/>
       <c r="L184" s="11" t="inlineStr"/>
-      <c r="M184" s="11" t="n"/>
+      <c r="M184" s="11" t="inlineStr">
+        <is>
+          <t>96628227[리모콘]</t>
+        </is>
+      </c>
       <c r="N184" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12392,7 +12671,11 @@
       </c>
       <c r="K185" s="11" t="inlineStr"/>
       <c r="L185" s="11" t="inlineStr"/>
-      <c r="M185" s="11" t="n"/>
+      <c r="M185" s="11" t="inlineStr">
+        <is>
+          <t>96870247</t>
+        </is>
+      </c>
       <c r="N185" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12454,7 +12737,11 @@
       </c>
       <c r="K186" s="11" t="inlineStr"/>
       <c r="L186" s="11" t="inlineStr"/>
-      <c r="M186" s="11" t="n"/>
+      <c r="M186" s="11" t="inlineStr">
+        <is>
+          <t>20760902</t>
+        </is>
+      </c>
       <c r="N186" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12516,7 +12803,11 @@
       </c>
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr"/>
-      <c r="M187" s="11" t="n"/>
+      <c r="M187" s="11" t="inlineStr">
+        <is>
+          <t>20760902</t>
+        </is>
+      </c>
       <c r="N187" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12578,7 +12869,11 @@
       </c>
       <c r="K188" s="11" t="inlineStr"/>
       <c r="L188" s="11" t="inlineStr"/>
-      <c r="M188" s="11" t="n"/>
+      <c r="M188" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
       <c r="N188" s="11" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12640,7 +12935,11 @@
       </c>
       <c r="K189" s="11" t="inlineStr"/>
       <c r="L189" s="11" t="inlineStr"/>
-      <c r="M189" s="11" t="inlineStr"/>
+      <c r="M189" s="11" t="inlineStr">
+        <is>
+          <t>96870247[추정]</t>
+        </is>
+      </c>
       <c r="N189" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12706,7 +13005,11 @@
       </c>
       <c r="K190" s="11" t="inlineStr"/>
       <c r="L190" s="11" t="inlineStr"/>
-      <c r="M190" s="11" t="inlineStr"/>
+      <c r="M190" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
       <c r="N190" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12772,7 +13075,11 @@
       </c>
       <c r="K191" s="11" t="inlineStr"/>
       <c r="L191" s="11" t="inlineStr"/>
-      <c r="M191" s="11" t="inlineStr"/>
+      <c r="M191" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
       <c r="N191" s="5" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저</t>
@@ -12838,7 +13145,11 @@
       </c>
       <c r="K192" s="11" t="inlineStr"/>
       <c r="L192" s="11" t="n"/>
-      <c r="M192" s="11" t="inlineStr"/>
+      <c r="M192" s="11" t="inlineStr">
+        <is>
+          <t>42418198</t>
+        </is>
+      </c>
       <c r="N192" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
@@ -12900,7 +13211,11 @@
       </c>
       <c r="K193" s="11" t="inlineStr"/>
       <c r="L193" s="11" t="n"/>
-      <c r="M193" s="11" t="inlineStr"/>
+      <c r="M193" s="11" t="inlineStr">
+        <is>
+          <t>42418198</t>
+        </is>
+      </c>
       <c r="N193" s="14" t="inlineStr">
         <is>
           <t>트랜스폰더 이모빌라이저, PEPS</t>
@@ -13953,7 +14268,7 @@
       <c r="K209" s="11" t="inlineStr"/>
       <c r="L209" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>FCC HYQ4ES, 13532766</t>
         </is>
       </c>
       <c r="M209" s="11" t="inlineStr"/>
@@ -14019,7 +14334,7 @@
       <c r="K210" s="11" t="inlineStr"/>
       <c r="L210" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>FCC HYQ4ES, 13532767</t>
         </is>
       </c>
       <c r="M210" s="11" t="inlineStr"/>
@@ -14085,7 +14400,7 @@
       <c r="K211" s="11" t="inlineStr"/>
       <c r="L211" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES</t>
+          <t>FCC HYQ4ES, 13532767</t>
         </is>
       </c>
       <c r="M211" s="11" t="inlineStr"/>
@@ -15301,387 +15616,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr"/>
+      <c r="A2" s="21" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr"/>
+      <c r="A14" s="21" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr"/>
+      <c r="A18" s="21" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n"/>
+      <c r="A27" s="21" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="n"/>
+      <c r="A35" s="21" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n"/>
+      <c r="A44" s="21" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>- 스파크 2013: 2013년형은 이모빌라이저 없음, 2014년형(2013.5.14 출시)부터 이모빌라이저 폴딩키 적용(나무위키 스파크 2세대·차프라이스 2013.5 가격표) — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>- 토스카 2006: 2007년형(2006.11 출시)부터 이모빌라이저 신규 적용(이투데이 "GM대우 2007년형 토스카 출시") — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>- 서버번: 한국GM이 2024.10부터 국내 정식 판매(위키백과) — 2023년식 행 삭제. 키는 타호와 같은 스마트키(YG0G21TB2, 433MHz, ID49)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n"/>
+      <c r="A50" s="21" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>- 스파크 M300 2014: GM 부품몰(c-mall) "스파크 2014년형 폴딩 키", 스파크 2012-2016 폴딩키 ID46(PCF7941E) 433MHz, 한국GM 블로그 "스파크S 폴딩키는 아베오·크루즈·알페온 키와 거의 같음" — 추정 해제</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>- 볼트(Volt) 2016-2019: 433MHz 스마트키 FCC HYQ4EA(13585728·13529638) = Philips ID46(locksmithkeyless) — 국내(433MHz) 사양과 같은 주파수 키로 확인</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>- 볼트 EV 2017-2021: 433MHz 스마트키 HYQ4EA ID46(2017-2022 볼트 적용), 미국형 315MHz는 HYQ4AA — 국내 433MHz 키 칩 ID46 확인</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>- 이쿼녹스 2023-2024: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 이쿼녹스 적용, 46E 칩), 미국형 315MHz HYQ4AS도 ID46 — 칩 ID46 확인</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>- 트래버스(2세대) 2021-2025: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 트래버스 적용) ID46 — 국내 판매분(2025.3 종료)은 2세대</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>- 쉐보레(GM대우) 순정 키 번호: GM 한국 순정부품몰 gmplusmall.com 상품명(적용 차종·연식) — 마티즈 II 키 세트 96611858(경보기 미적용)·96611863(경보기 적용)·블랭크키 96611864(2003~2005)·리모콘 96567446(2003~2004), 올 뉴 마티즈 블랭크키 96601589·리모콘 96498848(2006~2009), 스파크 키(리모콘 미적용) 94823322·리모콘 95487768(2011~2013)·원격시동 95016182(2012~2013)·폴딩 42670241(2014~2015, CVT 제외)·42695008(스파크S CVT), 라세티 리모콘 96550512(2003~2005)·96499642(세단 무선시동, 2003~2007)·96458343·96458344(도난경보, 2006~2008), 매그너스 96438485(도난방지·무선시동)·토스카·매그너스 96327968(이모빌라이저 미적용)·토스카 96646269(이모빌라이저), 말리부 스마트키 13582828(2012~2013)·13586777(2014~2015)·폴딩 13582829(2012~2015), 알페온 폴딩 20972992(2011~2013)·23111355(2014~2015), 윈스톰 96628227(2007)·96870247(2008)·20760902(2009~2010), 캡티바 폴딩 42418198, 트랙스 폴딩 95076523(2012~2022), 볼트 EV 스마트키 13529642, 트래버스 스마트키 13532766(2020~2021)·13532767(2022~2023). 몰 표기 앞 글자 P·I는 몰 구분 기호라 뺌. 리모컨(분리형)은 기아·현대 파일과 같이 폴딩키 칸에 [리모콘]으로 기재. 판매 연식 밖 연식은 [추정]</t>
         </is>
       </c>
     </row>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -698,7 +701,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr"/>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K2" s="11" t="inlineStr"/>
       <c r="L2" s="11" t="inlineStr"/>
       <c r="M2" s="11" t="inlineStr"/>
@@ -709,7 +716,7 @@
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), pechanara.com(마티즈2 M150 [00~05])</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), pechanara.com(마티즈2 M150 [00~05]), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -752,7 +759,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K3" s="11" t="inlineStr"/>
       <c r="L3" s="11" t="inlineStr"/>
       <c r="M3" s="11" t="inlineStr"/>
@@ -763,7 +774,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용)</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
@@ -806,7 +817,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용]</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr"/>
       <c r="M4" s="11" t="inlineStr"/>
@@ -817,7 +832,7 @@
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용)</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -860,7 +875,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr"/>
       <c r="M5" s="11" t="inlineStr">
@@ -875,7 +894,7 @@
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용)</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
@@ -918,7 +937,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="11" t="inlineStr">
@@ -933,7 +956,7 @@
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용)</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -976,7 +999,11 @@
           <t>96611858[키 세트, 경보기 미적용], 96611863[키 세트, 경보기 적용], 96611864</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -987,7 +1014,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용)</t>
+          <t>namu.wiki(마티즈Ⅱ M150 2000.8.11 출시~2005), tisdory(후속 올뉴마티즈 국내형 이모빌라이저 미적용), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
@@ -1030,7 +1057,11 @@
           <t>96601589</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1045,7 +1076,7 @@
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매)</t>
+          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr"/>
@@ -1084,7 +1115,11 @@
           <t>96601589</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1099,7 +1134,7 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매)</t>
+          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr"/>
@@ -1138,7 +1173,11 @@
           <t>96601589</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K10" s="11" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="11" t="inlineStr">
@@ -1153,7 +1192,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매)</t>
+          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr"/>
@@ -1192,7 +1231,11 @@
           <t>96601589</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K11" s="11" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="11" t="inlineStr">
@@ -1207,7 +1250,7 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매)</t>
+          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr"/>
@@ -1246,7 +1289,11 @@
           <t>96601589</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1261,7 +1308,7 @@
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매)</t>
+          <t>tisdory(올뉴마티즈 국내형 이모빌라이저 없음), namu.wiki(올 뉴 마티즈 2005.2.10 양산·판매), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
@@ -1296,7 +1343,11 @@
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K13" s="11" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="11" t="inlineStr"/>
@@ -1307,7 +1358,7 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키)</t>
+          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr"/>
@@ -1342,7 +1393,11 @@
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr"/>
-      <c r="J14" s="11" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="11" t="inlineStr"/>
@@ -1353,7 +1408,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키)</t>
+          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -1388,7 +1443,11 @@
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K15" s="11" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="11" t="inlineStr"/>
@@ -1399,7 +1458,7 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키)</t>
+          <t>namu.wiki·thewiki.kr(마티즈 크리에이티브/스파크 M300: 2013년형까지 이모빌라이저·폴딩키 없음, 2014년형부터 이모빌라이저 폴딩키), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>
@@ -1438,7 +1497,11 @@
           <t>94823322[리모콘 미적용]</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="11" t="inlineStr">
@@ -1453,7 +1516,7 @@
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr"/>
@@ -1492,7 +1555,11 @@
           <t>94823322[리모콘 미적용]</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>DWO4R</t>
+        </is>
+      </c>
       <c r="K17" s="11" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="11" t="inlineStr">
@@ -1507,7 +1574,7 @@
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키)</t>
         </is>
       </c>
       <c r="P17" s="11" t="inlineStr"/>
@@ -1528,12 +1595,24 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>해당 없음[2013년형]</t>
+          <t>ID46(PCF7937E)</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -1546,7 +1625,11 @@
           <t>94823322[리모콘 미적용]</t>
         </is>
       </c>
-      <c r="J18" s="11" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
       <c r="M18" s="11" t="inlineStr">
@@ -1561,7 +1644,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키), transpondery(Chevrolet Spark 2013+ Hitag2 Extended ID46E PCF7937E·NCF2951E), 같은 세대 다른 연식 행 키웨이와 동일(스파크 폴딩키 2014~ HU100)</t>
         </is>
       </c>
       <c r="P18" s="14" t="n"/>
@@ -1582,10 +1665,26 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7937E)</t>
+        </is>
+      </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
           <t>폴딩키</t>
@@ -1596,7 +1695,11 @@
           <t>94823322[리모콘 미적용]</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K19" s="11" t="n"/>
       <c r="L19" s="11" t="n"/>
       <c r="M19" s="11" t="inlineStr">
@@ -1607,7 +1710,7 @@
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E)</t>
+          <t>namu.wiki·thewiki.kr(스파크 M300 2013년형까지 이모빌라이저 없음, 2014년형부터 이모빌라이저 폴딩키), keydiy·ebay(미국형 스파크 2013-2016 ID46 GM EXT PCF7937E / 플립키 PCF7941E), Eurocarkeyshop(Chevrolet Matiz 2005-2012 키 블레이드 DWO4R), UHS(Daewoo DWO4RAP 기계식 키), transpondery(Chevrolet Spark 2013+ Hitag2 Extended ID46E PCF7937E·NCF2951E), 같은 세대 다른 연식 행 키웨이와 동일(스파크 폴딩키 2014~ HU100)</t>
         </is>
       </c>
       <c r="P19" s="14" t="n"/>
@@ -5658,7 +5761,11 @@
         </is>
       </c>
       <c r="I80" s="11" t="n"/>
-      <c r="J80" s="11" t="n"/>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K80" s="11" t="n"/>
       <c r="L80" s="11" t="n"/>
       <c r="M80" s="11" t="inlineStr">
@@ -5673,7 +5780,7 @@
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P80" s="14" t="n"/>
@@ -5720,7 +5827,11 @@
         </is>
       </c>
       <c r="I81" s="11" t="n"/>
-      <c r="J81" s="11" t="n"/>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K81" s="11" t="n"/>
       <c r="L81" s="11" t="n"/>
       <c r="M81" s="11" t="inlineStr">
@@ -5735,7 +5846,7 @@
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P81" s="14" t="n"/>
@@ -5782,7 +5893,11 @@
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr"/>
-      <c r="J82" s="11" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K82" s="11" t="inlineStr"/>
       <c r="L82" s="11" t="inlineStr"/>
       <c r="M82" s="11" t="inlineStr">
@@ -5797,7 +5912,7 @@
       </c>
       <c r="O82" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P82" s="5" t="inlineStr">
@@ -5848,7 +5963,11 @@
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr"/>
-      <c r="J83" s="11" t="inlineStr"/>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K83" s="11" t="inlineStr"/>
       <c r="L83" s="11" t="inlineStr"/>
       <c r="M83" s="11" t="inlineStr">
@@ -5863,7 +5982,7 @@
       </c>
       <c r="O83" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P83" s="5" t="inlineStr">
@@ -5914,7 +6033,11 @@
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr"/>
-      <c r="J84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K84" s="11" t="inlineStr"/>
       <c r="L84" s="11" t="inlineStr"/>
       <c r="M84" s="11" t="inlineStr">
@@ -5929,7 +6052,7 @@
       </c>
       <c r="O84" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P84" s="5" t="inlineStr">
@@ -5980,7 +6103,11 @@
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr"/>
-      <c r="J85" s="11" t="inlineStr"/>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K85" s="11" t="inlineStr"/>
       <c r="L85" s="11" t="inlineStr"/>
       <c r="M85" s="11" t="inlineStr">
@@ -5995,7 +6122,7 @@
       </c>
       <c r="O85" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P85" s="5" t="inlineStr">
@@ -6046,7 +6173,11 @@
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr"/>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>DWO5</t>
+        </is>
+      </c>
       <c r="K86" s="11" t="inlineStr"/>
       <c r="L86" s="11" t="inlineStr"/>
       <c r="M86" s="11" t="inlineStr">
@@ -6061,7 +6192,7 @@
       </c>
       <c r="O86" s="11" t="inlineStr">
         <is>
-          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존)</t>
+          <t>etoday.co.kr·namu.wiki(2007년형 토스카 2006.11 출시, 이모빌라이저 신규 적용), smartkeys.ru(에피카 2버튼 리모컨키 4D-60), 군산희망열쇠 blog.daum.net/cider5851(토스카 이모빌라이저 키·일반 키 차량 공존), CLK Supplies·Ilco(Chevrolet Epica 2004-2007 트랜스폰더 키 DW05T5), car-keys-online(Epica·Evanda DWO5 ID60) — 토스카는 수출명 Epica(V250)</t>
         </is>
       </c>
       <c r="P86" s="5" t="inlineStr">
@@ -10206,7 +10337,11 @@
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr"/>
-      <c r="J148" s="11" t="inlineStr"/>
+      <c r="J148" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K148" s="11" t="inlineStr"/>
       <c r="L148" s="11" t="inlineStr">
         <is>
@@ -10221,7 +10356,7 @@
       </c>
       <c r="O148" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
         </is>
       </c>
       <c r="P148" s="5" t="inlineStr">
@@ -10272,7 +10407,11 @@
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr"/>
-      <c r="J149" s="11" t="inlineStr"/>
+      <c r="J149" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="11" t="inlineStr">
         <is>
@@ -10287,7 +10426,7 @@
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
         </is>
       </c>
       <c r="P149" s="5" t="inlineStr">
@@ -10338,7 +10477,11 @@
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr"/>
-      <c r="J150" s="11" t="inlineStr"/>
+      <c r="J150" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K150" s="11" t="inlineStr"/>
       <c r="L150" s="11" t="inlineStr">
         <is>
@@ -10353,7 +10496,7 @@
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
         </is>
       </c>
       <c r="P150" s="5" t="inlineStr">
@@ -10404,7 +10547,11 @@
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr"/>
+      <c r="J151" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K151" s="11" t="inlineStr"/>
       <c r="L151" s="11" t="inlineStr">
         <is>
@@ -10419,7 +10566,7 @@
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
         </is>
       </c>
       <c r="P151" s="5" t="inlineStr">
@@ -10470,7 +10617,11 @@
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr"/>
+      <c r="J152" s="11" t="inlineStr">
+        <is>
+          <t>HU100</t>
+        </is>
+      </c>
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr">
         <is>
@@ -10485,7 +10636,7 @@
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음)</t>
+          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
         </is>
       </c>
       <c r="P152" s="5" t="inlineStr">
@@ -15616,7 +15767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -16007,6 +16158,13 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>- 6차 세대별 보완: 마티즈·스파크(M150~M300) DWO4R, 토스카(Epica) DWO5, 콜벳 C8 HU100, 스파크 2013 폴딩키 ID46(PCF7937E)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/쉐보레_models.xlsx
+++ b/쉐보레_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'쉐보레(GM대우) 트랜스폰더 DB'!$A$1:$P$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'쉐보레(GM대우) 트랜스폰더 DB'!$A$1:$P$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -564,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P229"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9883,12 +9886,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -9906,14 +9909,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I142" s="11" t="inlineStr"/>
@@ -9923,27 +9926,23 @@
         </is>
       </c>
       <c r="K142" s="11" t="inlineStr"/>
-      <c r="L142" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M142" s="11" t="inlineStr"/>
-      <c r="N142" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L142" s="11" t="inlineStr"/>
+      <c r="M142" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
+        </is>
+      </c>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O142" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P142" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P142" s="11" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
@@ -9953,12 +9952,12 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -9976,14 +9975,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr"/>
@@ -9993,27 +9992,23 @@
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr"/>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr"/>
-      <c r="N143" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
+        </is>
+      </c>
+      <c r="N143" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O143" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P143" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P143" s="11" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
@@ -10023,12 +10018,12 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -10046,14 +10041,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I144" s="11" t="inlineStr"/>
@@ -10063,27 +10058,23 @@
         </is>
       </c>
       <c r="K144" s="11" t="inlineStr"/>
-      <c r="L144" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M144" s="11" t="inlineStr"/>
-      <c r="N144" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L144" s="11" t="inlineStr"/>
+      <c r="M144" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
+        </is>
+      </c>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O144" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P144" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P144" s="11" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
@@ -10093,12 +10084,12 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -10116,14 +10107,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr"/>
@@ -10133,27 +10124,23 @@
         </is>
       </c>
       <c r="K145" s="11" t="inlineStr"/>
-      <c r="L145" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M145" s="11" t="inlineStr"/>
-      <c r="N145" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr">
+        <is>
+          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
+        </is>
+      </c>
+      <c r="N145" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O145" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P145" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P145" s="11" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
@@ -10163,12 +10150,12 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -10186,14 +10173,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr"/>
@@ -10203,27 +10190,23 @@
         </is>
       </c>
       <c r="K146" s="11" t="inlineStr"/>
-      <c r="L146" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M146" s="11" t="inlineStr"/>
-      <c r="N146" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L146" s="11" t="inlineStr"/>
+      <c r="M146" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N146" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O146" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P146" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P146" s="11" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
@@ -10233,12 +10216,12 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C7)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -10256,14 +10239,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7952E)</t>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr"/>
@@ -10273,27 +10256,23 @@
         </is>
       </c>
       <c r="K147" s="11" t="inlineStr"/>
-      <c r="L147" s="11" t="inlineStr">
-        <is>
-          <t>23465951[쿠페, 5버튼], 22779880[쿠페, 5버튼], FCC NBGGD9C04</t>
-        </is>
-      </c>
-      <c r="M147" s="11" t="inlineStr"/>
-      <c r="N147" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N147" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O147" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·abkeys.com(콜벳 2014-2019 스마트키 NBGGD9C04 PCF7952E ID46 434MHz 23465951/22779880), motorgraph.com·namu.wiki(한국GM C7 출시 무기한 연기 — 공식 판매는 C6(2012)뿐, 직수입만 존재)</t>
-        </is>
-      </c>
-      <c r="P147" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P147" s="11" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="inlineStr">
@@ -10303,22 +10282,22 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -10326,14 +10305,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr"/>
@@ -10343,27 +10322,23 @@
         </is>
       </c>
       <c r="K148" s="11" t="inlineStr"/>
-      <c r="L148" s="11" t="inlineStr">
-        <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
-        </is>
-      </c>
-      <c r="M148" s="11" t="inlineStr"/>
-      <c r="N148" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L148" s="11" t="inlineStr"/>
+      <c r="M148" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N148" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O148" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
-        </is>
-      </c>
-      <c r="P148" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P148" s="11" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
@@ -10373,22 +10348,22 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D149" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
@@ -10396,14 +10371,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I149" s="11" t="inlineStr"/>
@@ -10413,27 +10388,23 @@
         </is>
       </c>
       <c r="K149" s="11" t="inlineStr"/>
-      <c r="L149" s="11" t="inlineStr">
-        <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
-        </is>
-      </c>
-      <c r="M149" s="11" t="inlineStr"/>
-      <c r="N149" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N149" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O149" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
-        </is>
-      </c>
-      <c r="P149" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P149" s="11" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
@@ -10443,22 +10414,22 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D150" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
@@ -10466,14 +10437,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G150" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr"/>
@@ -10483,27 +10454,23 @@
         </is>
       </c>
       <c r="K150" s="11" t="inlineStr"/>
-      <c r="L150" s="11" t="inlineStr">
-        <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
-        </is>
-      </c>
-      <c r="M150" s="11" t="inlineStr"/>
-      <c r="N150" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L150" s="11" t="inlineStr"/>
+      <c r="M150" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N150" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
-        </is>
-      </c>
-      <c r="P150" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+        </is>
+      </c>
+      <c r="P150" s="11" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
@@ -10513,22 +10480,22 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>트랙스 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2022(단종)</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -10536,14 +10503,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7941E)</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr"/>
@@ -10553,27 +10520,23 @@
         </is>
       </c>
       <c r="K151" s="11" t="inlineStr"/>
-      <c r="L151" s="11" t="inlineStr">
-        <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
-        </is>
-      </c>
-      <c r="M151" s="11" t="inlineStr"/>
-      <c r="N151" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr">
+        <is>
+          <t>95076523</t>
+        </is>
+      </c>
+      <c r="N151" s="11" t="inlineStr">
+        <is>
+          <t>BCM</t>
         </is>
       </c>
       <c r="O151" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
-        </is>
-      </c>
-      <c r="P151" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736), namu.wiki(2022.8 내수 생산 종료, 11.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P151" s="11" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -10583,22 +10546,22 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>콜벳 (쉐보레, C8)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -10606,14 +10569,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr"/>
@@ -10625,25 +10588,21 @@
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>13538852[7버튼], 13545157[7버튼], FCC YG0G20TB1</t>
-        </is>
-      </c>
-      <c r="M152" s="11" t="inlineStr"/>
-      <c r="N152" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M152" s="11" t="n"/>
+      <c r="N152" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com·uhs-hardware.com(콜벳 C8 2020-2024 스마트키 YG0G20TB1 Hitag Pro ID49 434MHz, 13538852 등), hankookilbo(2021.3 국내 출시 미정), sisaweek(AP오토모티브 등 수입업체 판매), zdnet(2025 E-Ray 시승 — 공식 출시 발표 없음), UHS·American Key Supply(Corvette C8 2020-2024 스마트키 13538852 YG0G20TB1, 비상키 HU100)</t>
-        </is>
-      </c>
-      <c r="P152" s="5" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음(정식 판매 콜벳은 C6뿐) — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
+        </is>
+      </c>
+      <c r="P152" s="11" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
@@ -10653,12 +10612,12 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
@@ -10678,12 +10637,12 @@
       </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr"/>
@@ -10693,20 +10652,20 @@
         </is>
       </c>
       <c r="K153" s="11" t="inlineStr"/>
-      <c r="L153" s="11" t="inlineStr"/>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
-        </is>
-      </c>
+      <c r="L153" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="n"/>
       <c r="N153" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O153" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
         </is>
       </c>
       <c r="P153" s="11" t="inlineStr"/>
@@ -10719,12 +10678,12 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
@@ -10744,12 +10703,12 @@
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I154" s="11" t="inlineStr"/>
@@ -10759,20 +10718,20 @@
         </is>
       </c>
       <c r="K154" s="11" t="inlineStr"/>
-      <c r="L154" s="11" t="inlineStr"/>
-      <c r="M154" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
-        </is>
-      </c>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M154" s="11" t="n"/>
       <c r="N154" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O154" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
         </is>
       </c>
       <c r="P154" s="11" t="inlineStr"/>
@@ -10785,12 +10744,12 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
@@ -10810,12 +10769,12 @@
       </c>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr"/>
@@ -10825,20 +10784,20 @@
         </is>
       </c>
       <c r="K155" s="11" t="inlineStr"/>
-      <c r="L155" s="11" t="inlineStr"/>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
-        </is>
-      </c>
+      <c r="L155" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M155" s="11" t="n"/>
       <c r="N155" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O155" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
         </is>
       </c>
       <c r="P155" s="11" t="inlineStr"/>
@@ -10851,12 +10810,12 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
@@ -10876,12 +10835,12 @@
       </c>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr"/>
@@ -10891,20 +10850,20 @@
         </is>
       </c>
       <c r="K156" s="11" t="inlineStr"/>
-      <c r="L156" s="11" t="inlineStr"/>
-      <c r="M156" s="11" t="inlineStr">
-        <is>
-          <t>13500218[2버튼, 수출형], 13504196[2버튼, 수출형], 13504273[2버튼, 수출형], 95076523</t>
-        </is>
-      </c>
+      <c r="L156" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M156" s="11" t="n"/>
       <c r="N156" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O156" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P156" s="11" t="inlineStr"/>
@@ -10917,12 +10876,12 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
@@ -10942,12 +10901,12 @@
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr"/>
@@ -10957,20 +10916,20 @@
         </is>
       </c>
       <c r="K157" s="11" t="inlineStr"/>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L157" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M157" s="11" t="n"/>
       <c r="N157" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O157" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P157" s="11" t="inlineStr"/>
@@ -10983,12 +10942,12 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -11008,12 +10967,12 @@
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I158" s="11" t="inlineStr"/>
@@ -11023,20 +10982,20 @@
         </is>
       </c>
       <c r="K158" s="11" t="inlineStr"/>
-      <c r="L158" s="11" t="inlineStr"/>
-      <c r="M158" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L158" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M158" s="11" t="n"/>
       <c r="N158" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O158" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P158" s="11" t="inlineStr"/>
@@ -11049,12 +11008,12 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
@@ -11074,12 +11033,12 @@
       </c>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr"/>
@@ -11089,20 +11048,20 @@
         </is>
       </c>
       <c r="K159" s="11" t="inlineStr"/>
-      <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O159" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P159" s="11" t="inlineStr"/>
@@ -11115,12 +11074,12 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
@@ -11140,12 +11099,12 @@
       </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr"/>
@@ -11155,20 +11114,20 @@
         </is>
       </c>
       <c r="K160" s="11" t="inlineStr"/>
-      <c r="L160" s="11" t="inlineStr"/>
-      <c r="M160" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L160" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P160" s="11" t="inlineStr"/>
@@ -11181,12 +11140,12 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
@@ -11206,12 +11165,12 @@
       </c>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr"/>
@@ -11221,20 +11180,20 @@
         </is>
       </c>
       <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L161" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="n"/>
       <c r="N161" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O161" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P161" s="11" t="inlineStr"/>
@@ -11247,12 +11206,12 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>트랙스 (쉐보레, 1세대)</t>
+          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>2022(단종)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -11272,12 +11231,12 @@
       </c>
       <c r="G162" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7941E)</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I162" s="11" t="inlineStr"/>
@@ -11287,20 +11246,20 @@
         </is>
       </c>
       <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr"/>
-      <c r="M162" s="11" t="inlineStr">
-        <is>
-          <t>95076523</t>
-        </is>
-      </c>
+      <c r="L162" s="11" t="inlineStr">
+        <is>
+          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M162" s="11" t="n"/>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O162" s="11" t="inlineStr">
         <is>
-          <t>remkeys.com(아베오·크루즈·올란도·트랙스 2012-2015 2버튼 플립키 ID46 PCF7937/PCF7941E 433MHz HU100, OEM 13500218/13504196/13504273), keyshop-online.com(크루즈 2010-2014 3버튼 플립키 ID46 HU100 433MHz 13500219), auto-keys.eu(쉐보레 순정 플립키 13513927 HITAG2/ID46/PCF7937, HU100, 이모빌라이저 BCM), uhs-hardware·ebay(미국형 트랙스 2013-2021 플립키 13504265 ID46 / 2019-2022 13530736), namu.wiki(2022.8 내수 생산 종료, 11.4 홈페이지 삭제)</t>
+          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
         </is>
       </c>
       <c r="P162" s="11" t="inlineStr"/>
@@ -11313,12 +11272,12 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -11336,14 +11295,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G163" s="11" t="inlineStr">
+      <c r="G163" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr"/>
@@ -11355,21 +11314,21 @@
       <c r="K163" s="11" t="inlineStr"/>
       <c r="L163" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M163" s="11" t="n"/>
-      <c r="N163" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13529642</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="inlineStr"/>
+      <c r="N163" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O163" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
-        </is>
-      </c>
-      <c r="P163" s="11" t="inlineStr"/>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
+        </is>
+      </c>
+      <c r="P163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
@@ -11379,12 +11338,12 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -11402,14 +11361,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G164" s="11" t="inlineStr">
+      <c r="G164" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I164" s="11" t="inlineStr"/>
@@ -11421,21 +11380,21 @@
       <c r="K164" s="11" t="inlineStr"/>
       <c r="L164" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M164" s="11" t="n"/>
-      <c r="N164" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13529642</t>
+        </is>
+      </c>
+      <c r="M164" s="11" t="inlineStr"/>
+      <c r="N164" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O164" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
-        </is>
-      </c>
-      <c r="P164" s="11" t="inlineStr"/>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
+        </is>
+      </c>
+      <c r="P164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
@@ -11445,12 +11404,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -11468,14 +11427,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G165" s="11" t="inlineStr">
+      <c r="G165" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I165" s="11" t="inlineStr"/>
@@ -11487,21 +11446,21 @@
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M165" s="11" t="n"/>
-      <c r="N165" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13529642</t>
+        </is>
+      </c>
+      <c r="M165" s="11" t="inlineStr"/>
+      <c r="N165" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O165" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
-        </is>
-      </c>
-      <c r="P165" s="11" t="inlineStr"/>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
+        </is>
+      </c>
+      <c r="P165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
@@ -11511,12 +11470,12 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>트랙스 크로스오버 (쉐보레, 2세대)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -11534,14 +11493,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G166" s="11" t="inlineStr">
+      <c r="G166" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I166" s="11" t="inlineStr"/>
@@ -11553,21 +11512,21 @@
       <c r="K166" s="11" t="inlineStr"/>
       <c r="L166" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M166" s="11" t="n"/>
-      <c r="N166" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13529642</t>
+        </is>
+      </c>
+      <c r="M166" s="11" t="inlineStr"/>
+      <c r="N166" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O166" s="11" t="inlineStr">
         <is>
-          <t>ebay(2024-2025 트랙스 순정 스마트키 HYQ4ES 13530712 엔진 이모빌라이저), sffobsinc.com(HYQ4ES: 블레이저·볼트·트레일블레이저·트래버스·트랙스 2021-2026), enjoyyourpost.com(트랙스 크로스오버 LT 트림부터 버튼시동)</t>
-        </is>
-      </c>
-      <c r="P166" s="11" t="inlineStr"/>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
+        </is>
+      </c>
+      <c r="P166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
@@ -11577,12 +11536,12 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
@@ -11600,14 +11559,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G167" s="11" t="inlineStr">
+      <c r="G167" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I167" s="11" t="inlineStr"/>
@@ -11619,21 +11578,21 @@
       <c r="K167" s="11" t="inlineStr"/>
       <c r="L167" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M167" s="11" t="n"/>
-      <c r="N167" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13529642</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="inlineStr"/>
+      <c r="N167" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
-        </is>
-      </c>
-      <c r="P167" s="11" t="inlineStr"/>
+          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
+        </is>
+      </c>
+      <c r="P167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -11643,22 +11602,22 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -11666,14 +11625,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G168" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G168" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I168" s="11" t="inlineStr"/>
@@ -11685,21 +11644,21 @@
       <c r="K168" s="11" t="inlineStr"/>
       <c r="L168" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M168" s="11" t="n"/>
-      <c r="N168" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M168" s="11" t="inlineStr"/>
+      <c r="N168" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O168" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
-        </is>
-      </c>
-      <c r="P168" s="11" t="inlineStr"/>
+          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기), Intelligent Key Solutions·American Key Supply(2022-2023 Bolt EV·EUV 순정 스마트키 13535665·13535663 HYQ4ES 434MHz NXP HITAG-PRO ID49 — ID46 표기는 애프터마켓 호환품)</t>
+        </is>
+      </c>
+      <c r="P168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
@@ -11709,22 +11668,22 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>볼트 EV (쉐보레)</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023(단종)</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
@@ -11732,14 +11691,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G169" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G169" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I169" s="11" t="inlineStr"/>
@@ -11751,21 +11710,21 @@
       <c r="K169" s="11" t="inlineStr"/>
       <c r="L169" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M169" s="11" t="n"/>
-      <c r="N169" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M169" s="11" t="inlineStr"/>
+      <c r="N169" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
-        </is>
-      </c>
-      <c r="P169" s="11" t="inlineStr"/>
+          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기), zdnet·namu.wiki(2023.12 단종, 2024.1 판매 중단), Intelligent Key Solutions·American Key Supply(2022-2023 Bolt EV·EUV 순정 스마트키 13535665·13535663 HYQ4ES 434MHz NXP HITAG-PRO ID49 — ID46 표기는 애프터마켓 호환품)</t>
+        </is>
+      </c>
+      <c r="P169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -11775,22 +11734,22 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>볼트 EUV (쉐보레)</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -11798,14 +11757,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G170" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G170" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H170" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I170" s="11" t="inlineStr"/>
@@ -11817,21 +11776,21 @@
       <c r="K170" s="11" t="inlineStr"/>
       <c r="L170" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M170" s="11" t="n"/>
-      <c r="N170" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13535665, 13535664, FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M170" s="11" t="inlineStr"/>
+      <c r="N170" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O170" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
-        </is>
-      </c>
-      <c r="P170" s="11" t="inlineStr"/>
+          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개), Intelligent Key Solutions·American Key Supply(2022-2023 Bolt EV·EUV 순정 스마트키 13535665·13535663 HYQ4ES 434MHz NXP HITAG-PRO ID49 — ID46 표기는 애프터마켓 호환품)</t>
+        </is>
+      </c>
+      <c r="P170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
@@ -11841,22 +11800,22 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>볼트 EUV (쉐보레)</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023(단종)</t>
+        </is>
+      </c>
+      <c r="D171" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
@@ -11864,14 +11823,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G171" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G171" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr"/>
@@ -11883,21 +11842,21 @@
       <c r="K171" s="11" t="inlineStr"/>
       <c r="L171" s="11" t="inlineStr">
         <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M171" s="11" t="n"/>
-      <c r="N171" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>13535665, 13535664, FCC HYQ4ES</t>
+        </is>
+      </c>
+      <c r="M171" s="11" t="inlineStr"/>
+      <c r="N171" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
-        </is>
-      </c>
-      <c r="P171" s="11" t="inlineStr"/>
+          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개), zdnet(2023.12 단종), Intelligent Key Solutions·American Key Supply(2022-2023 Bolt EV·EUV 순정 스마트키 13535665·13535663 HYQ4ES 434MHz NXP HITAG-PRO ID49 — ID46 표기는 애프터마켓 호환품)</t>
+        </is>
+      </c>
+      <c r="P171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -11907,12 +11866,12 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
@@ -11932,35 +11891,35 @@
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr"/>
       <c r="J172" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K172" s="11" t="inlineStr"/>
-      <c r="L172" s="11" t="inlineStr">
-        <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M172" s="11" t="n"/>
+      <c r="L172" s="11" t="inlineStr"/>
+      <c r="M172" s="11" t="inlineStr">
+        <is>
+          <t>96628227[리모콘, 추정]</t>
+        </is>
+      </c>
       <c r="N172" s="11" t="inlineStr">
         <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(윈스톰 2006.6.7 출시)</t>
         </is>
       </c>
       <c r="P172" s="11" t="inlineStr"/>
@@ -11973,12 +11932,12 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>트레일블레이저 (쉐보레, 소형 SUV)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
@@ -11998,35 +11957,35 @@
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I173" s="11" t="inlineStr"/>
       <c r="J173" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K173" s="11" t="inlineStr"/>
-      <c r="L173" s="11" t="inlineStr">
-        <is>
-          <t>13530712[LT 이상], 13530713[LT 이상], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M173" s="11" t="n"/>
+      <c r="L173" s="11" t="inlineStr"/>
+      <c r="M173" s="11" t="inlineStr">
+        <is>
+          <t>96628227[리모콘]</t>
+        </is>
+      </c>
       <c r="N173" s="11" t="inlineStr">
         <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
         <is>
-          <t>keyecu·ebay(트레일블레이저 2021-2025 스마트키 HYQ4ES 13530712/13530713 433MHz ID46), encar mocha·namu.wiki(LS 트림 버튼시동 선택 불가, LT부터 스마트키)</t>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
         </is>
       </c>
       <c r="P173" s="11" t="inlineStr"/>
@@ -12039,12 +11998,12 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C174" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
@@ -12062,40 +12021,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G174" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H174" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I174" s="11" t="inlineStr"/>
       <c r="J174" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K174" s="11" t="inlineStr"/>
-      <c r="L174" s="11" t="inlineStr">
-        <is>
-          <t>13529642</t>
-        </is>
-      </c>
-      <c r="M174" s="11" t="inlineStr"/>
-      <c r="N174" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L174" s="11" t="inlineStr"/>
+      <c r="M174" s="11" t="inlineStr">
+        <is>
+          <t>96870247</t>
+        </is>
+      </c>
+      <c r="N174" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O174" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P174" s="14" t="n"/>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
+        </is>
+      </c>
+      <c r="P174" s="11" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -12105,12 +12064,12 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
@@ -12128,40 +12087,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G175" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I175" s="11" t="inlineStr"/>
       <c r="J175" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K175" s="11" t="inlineStr"/>
-      <c r="L175" s="11" t="inlineStr">
-        <is>
-          <t>13529642</t>
-        </is>
-      </c>
-      <c r="M175" s="11" t="inlineStr"/>
-      <c r="N175" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L175" s="11" t="inlineStr"/>
+      <c r="M175" s="11" t="inlineStr">
+        <is>
+          <t>20760902</t>
+        </is>
+      </c>
+      <c r="N175" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P175" s="14" t="n"/>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
+        </is>
+      </c>
+      <c r="P175" s="11" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
@@ -12171,12 +12130,12 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
@@ -12194,40 +12153,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G176" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G176" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I176" s="11" t="inlineStr"/>
       <c r="J176" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K176" s="11" t="inlineStr"/>
-      <c r="L176" s="11" t="inlineStr">
-        <is>
-          <t>13529642</t>
-        </is>
-      </c>
-      <c r="M176" s="11" t="inlineStr"/>
-      <c r="N176" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L176" s="11" t="inlineStr"/>
+      <c r="M176" s="11" t="inlineStr">
+        <is>
+          <t>20760902</t>
+        </is>
+      </c>
+      <c r="N176" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O176" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P176" s="14" t="n"/>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
+        </is>
+      </c>
+      <c r="P176" s="11" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
@@ -12237,12 +12196,12 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 (GM대우)</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2011(단종)</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
@@ -12260,40 +12219,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G177" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I177" s="11" t="inlineStr"/>
       <c r="J177" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr">
-        <is>
-          <t>13529642</t>
-        </is>
-      </c>
-      <c r="M177" s="11" t="inlineStr"/>
-      <c r="N177" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L177" s="11" t="inlineStr"/>
+      <c r="M177" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
+      <c r="N177" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O177" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P177" s="14" t="n"/>
+          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(2011.4 캡티바로 변경)</t>
+        </is>
+      </c>
+      <c r="P177" s="11" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
@@ -12303,12 +12262,12 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 맥스 (GM대우)</t>
         </is>
       </c>
       <c r="C178" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
@@ -12326,40 +12285,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G178" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I178" s="11" t="inlineStr"/>
       <c r="J178" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr">
-        <is>
-          <t>13529642</t>
-        </is>
-      </c>
-      <c r="M178" s="11" t="inlineStr"/>
-      <c r="N178" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L178" s="11" t="inlineStr"/>
+      <c r="M178" s="11" t="inlineStr">
+        <is>
+          <t>96870247[추정]</t>
+        </is>
+      </c>
+      <c r="N178" s="5" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O178" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com·locksmithkeyless.com(볼트 EV 2017-2021 스마트키 HYQ4AA Philips ID46, 13585722/13529664/13508767)</t>
-        </is>
-      </c>
-      <c r="P178" s="14" t="n"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
+        </is>
+      </c>
+      <c r="P178" s="5" t="inlineStr">
+        <is>
+          <t>윈스톰 기준 추정</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
@@ -12369,22 +12332,22 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 맥스 (GM대우)</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr">
@@ -12394,40 +12357,40 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>ID46, ID49</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I179" s="11" t="inlineStr"/>
       <c r="J179" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K179" s="11" t="inlineStr"/>
-      <c r="L179" s="11" t="inlineStr">
-        <is>
-          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M179" s="11" t="inlineStr"/>
+      <c r="L179" s="11" t="inlineStr"/>
+      <c r="M179" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
       <c r="N179" s="5" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O179" s="11" t="inlineStr">
         <is>
-          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기)</t>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
         </is>
       </c>
       <c r="P179" s="5" t="inlineStr">
         <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
+          <t>윈스톰 기준 추정</t>
         </is>
       </c>
     </row>
@@ -12439,22 +12402,22 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>볼트 EV (쉐보레)</t>
+          <t>윈스톰 맥스 (GM대우)</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
-        </is>
-      </c>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010(단종)</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
@@ -12464,40 +12427,40 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>ID46, ID49</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I180" s="11" t="inlineStr"/>
       <c r="J180" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K180" s="11" t="inlineStr"/>
-      <c r="L180" s="11" t="inlineStr">
-        <is>
-          <t>13535663[5버튼], 13547839[5버튼], FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M180" s="11" t="inlineStr"/>
+      <c r="L180" s="11" t="inlineStr"/>
+      <c r="M180" s="11" t="inlineStr">
+        <is>
+          <t>20760902[추정]</t>
+        </is>
+      </c>
       <c r="N180" s="5" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O180" s="11" t="inlineStr">
         <is>
-          <t>amazon·royalkeysupply.com(볼트 EV 2022-2023 스마트키 HYQ4ES 13535663/13547839 — ID46 / 일부 ID49 표기), zdnet·namu.wiki(2023.12 단종, 2024.1 판매 중단)</t>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
         </is>
       </c>
       <c r="P180" s="5" t="inlineStr">
         <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
+          <t>윈스톰 기준 추정</t>
         </is>
       </c>
     </row>
@@ -12509,22 +12472,22 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>볼트 EUV (쉐보레)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
@@ -12532,44 +12495,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>ID46, ID49</t>
+      <c r="G181" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I181" s="11" t="inlineStr"/>
       <c r="J181" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K181" s="11" t="inlineStr"/>
-      <c r="L181" s="11" t="inlineStr">
-        <is>
-          <t>13535665, 13535664, FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M181" s="11" t="inlineStr"/>
-      <c r="N181" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L181" s="11" t="n"/>
+      <c r="M181" s="11" t="inlineStr">
+        <is>
+          <t>42418198</t>
+        </is>
+      </c>
+      <c r="N181" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O181" s="11" t="inlineStr">
         <is>
-          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개)</t>
-        </is>
-      </c>
-      <c r="P181" s="5" t="inlineStr">
-        <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
-        </is>
-      </c>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
@@ -12579,22 +12538,22 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>볼트 EUV (쉐보레)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr">
         <is>
-          <t>2023(단종)</t>
-        </is>
-      </c>
-      <c r="D182" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -12602,44 +12561,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>ID46, ID49</t>
+      <c r="G182" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H182" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I182" s="11" t="inlineStr"/>
       <c r="J182" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>DWO5</t>
         </is>
       </c>
       <c r="K182" s="11" t="inlineStr"/>
-      <c r="L182" s="11" t="inlineStr">
-        <is>
-          <t>13535665, 13535664, FCC HYQ4ES</t>
-        </is>
-      </c>
-      <c r="M182" s="11" t="inlineStr"/>
-      <c r="N182" s="5" t="inlineStr">
-        <is>
-          <t>PEPS</t>
+      <c r="L182" s="11" t="n"/>
+      <c r="M182" s="11" t="inlineStr">
+        <is>
+          <t>42418198</t>
+        </is>
+      </c>
+      <c r="N182" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O182" s="11" t="inlineStr">
         <is>
-          <t>remotesandkeys.com·northcoastkeyless.com(볼트 EUV 2022-2023 스마트키 HYQ4ES 13535665, 433MHz ID46), transponderisland.com(13535664), media.gmc.com(2021.8 볼트 EUV 국내 제원 공개), zdnet(2023.12 단종)</t>
-        </is>
-      </c>
-      <c r="P182" s="5" t="inlineStr">
-        <is>
-          <t>칩 표기 상충(ID46 vs ID49)</t>
-        </is>
-      </c>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
@@ -12649,12 +12604,12 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
@@ -12672,40 +12627,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G183" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G183" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I183" s="11" t="inlineStr"/>
       <c r="J183" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K183" s="11" t="inlineStr"/>
-      <c r="L183" s="11" t="inlineStr"/>
-      <c r="M183" s="11" t="inlineStr">
-        <is>
-          <t>96628227[리모콘, 추정]</t>
-        </is>
-      </c>
-      <c r="N183" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L183" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M183" s="11" t="inlineStr"/>
+      <c r="N183" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O183" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(윈스톰 2006.6.7 출시)</t>
-        </is>
-      </c>
-      <c r="P183" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
@@ -12715,12 +12670,12 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C184" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
@@ -12738,40 +12693,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G184" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G184" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I184" s="11" t="inlineStr"/>
       <c r="J184" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K184" s="11" t="inlineStr"/>
-      <c r="L184" s="11" t="inlineStr"/>
-      <c r="M184" s="11" t="inlineStr">
-        <is>
-          <t>96628227[리모콘]</t>
-        </is>
-      </c>
-      <c r="N184" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L184" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M184" s="11" t="inlineStr"/>
+      <c r="N184" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O184" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
-        </is>
-      </c>
-      <c r="P184" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
@@ -12781,12 +12736,12 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
@@ -12804,40 +12759,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G185" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G185" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr"/>
       <c r="J185" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K185" s="11" t="inlineStr"/>
-      <c r="L185" s="11" t="inlineStr"/>
-      <c r="M185" s="11" t="inlineStr">
-        <is>
-          <t>96870247</t>
-        </is>
-      </c>
-      <c r="N185" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L185" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M185" s="11" t="inlineStr"/>
+      <c r="N185" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O185" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
-        </is>
-      </c>
-      <c r="P185" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
@@ -12847,12 +12802,12 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C186" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
@@ -12870,40 +12825,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G186" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G186" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr"/>
       <c r="J186" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K186" s="11" t="inlineStr"/>
-      <c r="L186" s="11" t="inlineStr"/>
-      <c r="M186" s="11" t="inlineStr">
-        <is>
-          <t>20760902</t>
-        </is>
-      </c>
-      <c r="N186" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L186" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M186" s="11" t="inlineStr"/>
+      <c r="N186" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O186" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
-        </is>
-      </c>
-      <c r="P186" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
@@ -12913,12 +12868,12 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
@@ -12936,40 +12891,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G187" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G187" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I187" s="11" t="inlineStr"/>
       <c r="J187" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K187" s="11" t="inlineStr"/>
-      <c r="L187" s="11" t="inlineStr"/>
-      <c r="M187" s="11" t="inlineStr">
-        <is>
-          <t>20760902</t>
-        </is>
-      </c>
-      <c r="N187" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L187" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M187" s="11" t="inlineStr"/>
+      <c r="N187" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O187" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법)</t>
-        </is>
-      </c>
-      <c r="P187" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+        </is>
+      </c>
+      <c r="P187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="inlineStr">
@@ -12979,12 +12934,12 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 (GM대우)</t>
+          <t>캡티바 (쉐보레, 1세대)</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr">
         <is>
-          <t>2011(단종)</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
@@ -13002,40 +12957,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G188" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G188" s="14" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
         </is>
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I188" s="11" t="inlineStr"/>
       <c r="J188" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>DWO5[일반 키], HU100[스마트키]</t>
         </is>
       </c>
       <c r="K188" s="11" t="inlineStr"/>
-      <c r="L188" s="11" t="inlineStr"/>
-      <c r="M188" s="11" t="inlineStr">
-        <is>
-          <t>20760902[추정]</t>
-        </is>
-      </c>
-      <c r="N188" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L188" s="11" t="inlineStr">
+        <is>
+          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M188" s="11" t="inlineStr"/>
+      <c r="N188" s="14" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저, PEPS</t>
         </is>
       </c>
       <c r="O188" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(쉐보레 캡티바 C100(=윈스톰) 2007-2013 PCF7936 ID46, DWO5, 433MHz), blog.daum.net/13114(윈스톰 이모빌라이저 키 추가 등록 방법), namu.wiki(2011.4 캡티바로 변경)</t>
-        </is>
-      </c>
-      <c r="P188" s="11" t="inlineStr"/>
+          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz), namu.wiki(2018.5 생산 중단, 재고 판매 후 단종)</t>
+        </is>
+      </c>
+      <c r="P188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
@@ -13045,12 +13000,12 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 맥스 (GM대우)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
@@ -13068,44 +13023,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I189" s="11" t="inlineStr"/>
       <c r="J189" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K189" s="11" t="inlineStr"/>
-      <c r="L189" s="11" t="inlineStr"/>
-      <c r="M189" s="11" t="inlineStr">
-        <is>
-          <t>96870247[추정]</t>
-        </is>
-      </c>
-      <c r="N189" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L189" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
+      <c r="M189" s="11" t="inlineStr"/>
+      <c r="N189" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O189" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
-        </is>
-      </c>
-      <c r="P189" s="5" t="inlineStr">
-        <is>
-          <t>윈스톰 기준 추정</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P189" s="11" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
@@ -13115,12 +13066,12 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 맥스 (GM대우)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C190" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
@@ -13138,44 +13089,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G190" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H190" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I190" s="11" t="inlineStr"/>
       <c r="J190" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K190" s="11" t="inlineStr"/>
-      <c r="L190" s="11" t="inlineStr"/>
-      <c r="M190" s="11" t="inlineStr">
-        <is>
-          <t>20760902[추정]</t>
-        </is>
-      </c>
-      <c r="N190" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L190" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
+      <c r="M190" s="11" t="inlineStr"/>
+      <c r="N190" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O190" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
-        </is>
-      </c>
-      <c r="P190" s="5" t="inlineStr">
-        <is>
-          <t>윈스톰 기준 추정</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+        </is>
+      </c>
+      <c r="P190" s="11" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
@@ -13185,12 +13132,12 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>윈스톰 맥스 (GM대우)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>2010(단종)</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
@@ -13208,44 +13155,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I191" s="11" t="inlineStr"/>
       <c r="J191" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K191" s="11" t="inlineStr"/>
-      <c r="L191" s="11" t="inlineStr"/>
-      <c r="M191" s="11" t="inlineStr">
-        <is>
-          <t>20760902[추정]</t>
-        </is>
-      </c>
-      <c r="N191" s="5" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
+      <c r="L191" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
+      <c r="M191" s="11" t="inlineStr"/>
+      <c r="N191" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O191" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5), namu.wiki(윈스톰 맥스 C105 2008.6.18 시판, 2010.12 단종)</t>
-        </is>
-      </c>
-      <c r="P191" s="5" t="inlineStr">
-        <is>
-          <t>윈스톰 기준 추정</t>
-        </is>
-      </c>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
+        </is>
+      </c>
+      <c r="P191" s="11" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
@@ -13255,12 +13198,12 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C192" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
@@ -13278,40 +13221,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G192" s="14" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H192" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I192" s="11" t="inlineStr"/>
       <c r="J192" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K192" s="11" t="inlineStr"/>
-      <c r="L192" s="11" t="n"/>
-      <c r="M192" s="11" t="inlineStr">
-        <is>
-          <t>42418198</t>
-        </is>
-      </c>
-      <c r="N192" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="L192" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
+      <c r="M192" s="11" t="inlineStr"/>
+      <c r="N192" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O192" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P192" s="14" t="n"/>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
+        </is>
+      </c>
+      <c r="P192" s="11" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
@@ -13321,12 +13264,12 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
@@ -13344,40 +13287,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G193" s="14" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I193" s="11" t="inlineStr"/>
       <c r="J193" s="11" t="inlineStr">
         <is>
-          <t>DWO5</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K193" s="11" t="inlineStr"/>
-      <c r="L193" s="11" t="n"/>
-      <c r="M193" s="11" t="inlineStr">
-        <is>
-          <t>42418198</t>
-        </is>
-      </c>
-      <c r="N193" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="L193" s="11" t="inlineStr">
+        <is>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
+        </is>
+      </c>
+      <c r="M193" s="11" t="inlineStr"/>
+      <c r="N193" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O193" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P193" s="14" t="n"/>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
+        </is>
+      </c>
+      <c r="P193" s="11" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
@@ -13387,12 +13330,12 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
@@ -13412,35 +13355,35 @@
       </c>
       <c r="G194" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I194" s="11" t="inlineStr"/>
       <c r="J194" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K194" s="11" t="inlineStr"/>
       <c r="L194" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M194" s="11" t="inlineStr"/>
       <c r="N194" s="14" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O194" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
         </is>
       </c>
       <c r="P194" s="14" t="n"/>
@@ -13453,12 +13396,12 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>이쿼녹스 (쉐보레, 가솔린)</t>
         </is>
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
@@ -13478,35 +13421,35 @@
       </c>
       <c r="G195" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I195" s="11" t="inlineStr"/>
       <c r="J195" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K195" s="11" t="inlineStr"/>
       <c r="L195" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>13585720, 13529648, FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M195" s="11" t="inlineStr"/>
       <c r="N195" s="14" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+          <t>PEPS, BCM</t>
         </is>
       </c>
       <c r="O195" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
         </is>
       </c>
       <c r="P195" s="14" t="n"/>
@@ -13519,12 +13462,12 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
@@ -13542,40 +13485,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G196" s="14" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I196" s="11" t="inlineStr"/>
       <c r="J196" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K196" s="11" t="inlineStr"/>
       <c r="L196" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M196" s="11" t="inlineStr"/>
-      <c r="N196" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="N196" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O196" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P196" s="14" t="n"/>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P196" s="11" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
@@ -13585,12 +13528,12 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
@@ -13608,40 +13551,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G197" s="14" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I197" s="11" t="inlineStr"/>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K197" s="11" t="inlineStr"/>
       <c r="L197" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>13591384[3버튼], FCC HYQ4EA</t>
         </is>
       </c>
       <c r="M197" s="11" t="inlineStr"/>
-      <c r="N197" s="14" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+      <c r="N197" s="11" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O197" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
-        </is>
-      </c>
-      <c r="P197" s="14" t="n"/>
+          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
+        </is>
+      </c>
+      <c r="P197" s="11" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
@@ -13651,12 +13594,12 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
@@ -13676,35 +13619,35 @@
       </c>
       <c r="G198" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I198" s="11" t="inlineStr"/>
       <c r="J198" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K198" s="11" t="inlineStr"/>
       <c r="L198" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>FCC HYQ4ES, 13532766</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr"/>
       <c r="N198" s="14" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O198" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz)</t>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
       <c r="P198" s="14" t="n"/>
@@ -13717,12 +13660,12 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>캡티바 (쉐보레, 1세대)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
@@ -13742,35 +13685,35 @@
       </c>
       <c r="G199" s="14" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)[일반 키], ID46(PCF7952A)[스마트키]</t>
+          <t>ID46</t>
         </is>
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I199" s="11" t="inlineStr"/>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>DWO5[일반 키], HU100[스마트키]</t>
+          <t>HU100</t>
         </is>
       </c>
       <c r="K199" s="11" t="inlineStr"/>
       <c r="L199" s="11" t="inlineStr">
         <is>
-          <t>95129967[해외 공용 품번], 95129968[해외 공용 품번]</t>
+          <t>FCC HYQ4ES, 13532767</t>
         </is>
       </c>
       <c r="M199" s="11" t="inlineStr"/>
       <c r="N199" s="14" t="inlineStr">
         <is>
-          <t>트랜스폰더 이모빌라이저, PEPS</t>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O199" s="11" t="inlineStr">
         <is>
-          <t>originalkey.ru(캡티바 C100 2007-2013 PCF7936 ID46 DWO5 433MHz), autokeymaster(캡티바 2013-2016 스마트키 PCF7952 434MHz 4버튼), keyecu.com(홀덴/쉐보레 캡티바 2014-2018 스마트키 PCF7952A ID46 433MHz), namu.wiki(2018.5 생산 중단, 재고 판매 후 단종)</t>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
         </is>
       </c>
       <c r="P199" s="14" t="n"/>
@@ -13783,12 +13726,12 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
@@ -13806,7 +13749,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G200" s="11" t="inlineStr">
+      <c r="G200" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13825,21 +13768,21 @@
       <c r="K200" s="11" t="inlineStr"/>
       <c r="L200" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>FCC HYQ4ES, 13532767</t>
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr"/>
-      <c r="N200" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N200" s="14" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O200" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), encar(2018.6.7 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P200" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+        </is>
+      </c>
+      <c r="P200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
@@ -13849,12 +13792,12 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
@@ -13872,7 +13815,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G201" s="11" t="inlineStr">
+      <c r="G201" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13891,21 +13834,21 @@
       <c r="K201" s="11" t="inlineStr"/>
       <c r="L201" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M201" s="11" t="inlineStr"/>
-      <c r="N201" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N201" s="14" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O201" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
-        </is>
-      </c>
-      <c r="P201" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+        </is>
+      </c>
+      <c r="P201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
@@ -13915,12 +13858,12 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>트래버스 (쉐보레)</t>
         </is>
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
@@ -13938,7 +13881,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G202" s="11" t="inlineStr">
+      <c r="G202" s="14" t="inlineStr">
         <is>
           <t>ID46</t>
         </is>
@@ -13957,21 +13900,21 @@
       <c r="K202" s="11" t="inlineStr"/>
       <c r="L202" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>FCC HYQ4ES</t>
         </is>
       </c>
       <c r="M202" s="11" t="inlineStr"/>
-      <c r="N202" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N202" s="14" t="inlineStr">
+        <is>
+          <t>PEPS, 트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O202" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
-        </is>
-      </c>
-      <c r="P202" s="11" t="inlineStr"/>
+          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
+        </is>
+      </c>
+      <c r="P202" s="14" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
@@ -13981,22 +13924,22 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D203" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
@@ -14006,7 +13949,7 @@
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H203" s="11" t="inlineStr">
@@ -14023,18 +13966,18 @@
       <c r="K203" s="11" t="inlineStr"/>
       <c r="L203" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M203" s="11" t="inlineStr"/>
       <c r="N203" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O203" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2021.3 수입 중단)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
         </is>
       </c>
       <c r="P203" s="11" t="inlineStr"/>
@@ -14047,22 +13990,22 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C204" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
@@ -14072,7 +14015,7 @@
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H204" s="11" t="inlineStr">
@@ -14089,18 +14032,18 @@
       <c r="K204" s="11" t="inlineStr"/>
       <c r="L204" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M204" s="11" t="inlineStr"/>
       <c r="N204" s="11" t="inlineStr">
         <is>
-          <t>PEPS, BCM</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O204" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), gpkorea(2022.6 더 넥스트 이쿼녹스 재출시)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
         </is>
       </c>
       <c r="P204" s="11" t="inlineStr"/>
@@ -14113,22 +14056,22 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C205" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
@@ -14136,9 +14079,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G205" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H205" s="11" t="inlineStr">
@@ -14155,21 +14098,21 @@
       <c r="K205" s="11" t="inlineStr"/>
       <c r="L205" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M205" s="11" t="inlineStr"/>
-      <c r="N205" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N205" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O205" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648)</t>
-        </is>
-      </c>
-      <c r="P205" s="14" t="n"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
+        </is>
+      </c>
+      <c r="P205" s="11" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
@@ -14179,22 +14122,22 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>이쿼녹스 (쉐보레, 가솔린)</t>
+          <t>타호 (쉐보레)</t>
         </is>
       </c>
       <c r="C206" s="11" t="inlineStr">
         <is>
-          <t>2024(단종)</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025(단종)</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -14202,9 +14145,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G206" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H206" s="11" t="inlineStr">
@@ -14221,21 +14164,21 @@
       <c r="K206" s="11" t="inlineStr"/>
       <c r="L206" s="11" t="inlineStr">
         <is>
-          <t>13585720, 13529648, FCC HYQ4EA</t>
+          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr"/>
-      <c r="N206" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, BCM</t>
+      <c r="N206" s="11" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O206" s="11" t="inlineStr">
         <is>
-          <t>amazon·key4.com(이쿼녹스 2018-2022 스마트키 HYQ4EA 433MHz Philips ID46, 13585720/13529648), namu.wiki(2024.4 홈페이지에서 삭제·단종)</t>
-        </is>
-      </c>
-      <c r="P206" s="14" t="n"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
+        </is>
+      </c>
+      <c r="P206" s="11" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
@@ -14245,22 +14188,22 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C207" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D207" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
@@ -14268,9 +14211,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G207" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G207" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H207" s="11" t="inlineStr">
@@ -14287,21 +14230,21 @@
       <c r="K207" s="11" t="inlineStr"/>
       <c r="L207" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M207" s="11" t="inlineStr"/>
-      <c r="N207" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N207" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O207" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA), top-rider(트래버스 2019.9 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P207" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P207" s="14" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
@@ -14311,22 +14254,22 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C208" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E208" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
@@ -14334,9 +14277,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G208" s="11" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G208" s="14" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H208" s="11" t="inlineStr">
@@ -14353,21 +14296,21 @@
       <c r="K208" s="11" t="inlineStr"/>
       <c r="L208" s="11" t="inlineStr">
         <is>
-          <t>13591384[3버튼], FCC HYQ4EA</t>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M208" s="11" t="inlineStr"/>
-      <c r="N208" s="11" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N208" s="14" t="inlineStr">
+        <is>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O208" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(블레이저·트래버스 2018+ 순정 스마트키 13591384 433MHz HYQ4EA), americankeysupply(이쿼녹스/트래버스 2018-2020 HYQ4EA)</t>
-        </is>
-      </c>
-      <c r="P208" s="11" t="inlineStr"/>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
+        </is>
+      </c>
+      <c r="P208" s="14" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
@@ -14377,22 +14320,22 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>서버번 (쉐보레)</t>
         </is>
       </c>
       <c r="C209" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D209" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
@@ -14402,7 +14345,7 @@
       </c>
       <c r="G209" s="14" t="inlineStr">
         <is>
-          <t>ID46</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H209" s="11" t="inlineStr">
@@ -14419,18 +14362,18 @@
       <c r="K209" s="11" t="inlineStr"/>
       <c r="L209" s="11" t="inlineStr">
         <is>
-          <t>FCC HYQ4ES, 13532766</t>
+          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M209" s="11" t="inlineStr"/>
       <c r="N209" s="14" t="inlineStr">
         <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+          <t>PEPS</t>
         </is>
       </c>
       <c r="O209" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
+          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
         </is>
       </c>
       <c r="P209" s="14" t="n"/>
@@ -14443,12 +14386,12 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C210" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
@@ -14466,40 +14409,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G210" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H210" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I210" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J210" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K210" s="11" t="inlineStr"/>
-      <c r="L210" s="11" t="inlineStr">
-        <is>
-          <t>FCC HYQ4ES, 13532767</t>
-        </is>
-      </c>
+      <c r="L210" s="11" t="inlineStr"/>
       <c r="M210" s="11" t="inlineStr"/>
-      <c r="N210" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N210" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O210" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P210" s="14" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P210" s="11" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="inlineStr">
@@ -14509,12 +14452,12 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C211" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
@@ -14532,40 +14475,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G211" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I211" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K211" s="11" t="inlineStr"/>
-      <c r="L211" s="11" t="inlineStr">
-        <is>
-          <t>FCC HYQ4ES, 13532767</t>
-        </is>
-      </c>
+      <c r="L211" s="11" t="inlineStr"/>
       <c r="M211" s="11" t="inlineStr"/>
-      <c r="N211" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N211" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O211" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P211" s="14" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P211" s="11" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
@@ -14575,12 +14518,12 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C212" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
@@ -14598,40 +14541,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G212" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H212" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I212" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J212" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K212" s="11" t="inlineStr"/>
-      <c r="L212" s="11" t="inlineStr">
-        <is>
-          <t>FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L212" s="11" t="inlineStr"/>
       <c r="M212" s="11" t="inlineStr"/>
-      <c r="N212" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O212" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46)</t>
-        </is>
-      </c>
-      <c r="P212" s="14" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P212" s="11" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
@@ -14641,12 +14584,12 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>트래버스 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C213" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
@@ -14664,40 +14607,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G213" s="14" t="inlineStr">
-        <is>
-          <t>ID46</t>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I213" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K213" s="11" t="inlineStr"/>
-      <c r="L213" s="11" t="inlineStr">
-        <is>
-          <t>FCC HYQ4ES</t>
-        </is>
-      </c>
+      <c r="L213" s="11" t="inlineStr"/>
       <c r="M213" s="11" t="inlineStr"/>
-      <c r="N213" s="14" t="inlineStr">
-        <is>
-          <t>PEPS, 트랜스폰더 이모빌라이저</t>
+      <c r="N213" s="11" t="inlineStr">
+        <is>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O213" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(블레이저·트래버스 2021-2023 스마트키 HYQ4ES/HYQ4AS ID46), namu.wiki(2025.3 판매 종료)</t>
-        </is>
-      </c>
-      <c r="P213" s="14" t="n"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
+        </is>
+      </c>
+      <c r="P213" s="11" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
@@ -14707,22 +14650,22 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C214" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D214" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
@@ -14732,35 +14675,35 @@
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46[Extended]</t>
         </is>
       </c>
       <c r="H214" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I214" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I214" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J214" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
+          <t>HU100, B119[ILCO]</t>
         </is>
       </c>
       <c r="K214" s="11" t="inlineStr"/>
-      <c r="L214" s="11" t="inlineStr">
-        <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
+      <c r="L214" s="11" t="inlineStr"/>
       <c r="M214" s="11" t="inlineStr"/>
       <c r="N214" s="11" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>트랜스폰더 이모빌라이저</t>
         </is>
       </c>
       <c r="O214" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), sedaily·news1(타호 2022.1 국내 출시)</t>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
         </is>
       </c>
       <c r="P214" s="11" t="inlineStr"/>
@@ -14773,22 +14716,22 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C215" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D215" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E215" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
@@ -14798,38 +14741,38 @@
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46[2세대, ~2024.4]</t>
         </is>
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I215" s="11" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="inlineStr">
+        <is>
+          <t>23209427[2세대]</t>
+        </is>
+      </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K215" s="11" t="inlineStr"/>
-      <c r="L215" s="11" t="inlineStr">
-        <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M215" s="11" t="inlineStr"/>
+          <t>HU100, B119[ILCO]</t>
+        </is>
+      </c>
+      <c r="K215" s="11" t="n"/>
+      <c r="L215" s="11" t="n"/>
+      <c r="M215" s="11" t="n"/>
       <c r="N215" s="11" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>트랜스폰더 이모빌라이저[2세대]</t>
         </is>
       </c>
       <c r="O215" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
-        </is>
-      </c>
-      <c r="P215" s="11" t="inlineStr"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P215" s="11" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
@@ -14839,7 +14782,7 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C216" s="11" t="inlineStr">
@@ -14864,7 +14807,7 @@
       </c>
       <c r="G216" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49[3세대, 2024.7~]</t>
         </is>
       </c>
       <c r="H216" s="11" t="inlineStr">
@@ -14872,30 +14815,30 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I216" s="11" t="inlineStr"/>
+      <c r="I216" s="11" t="n"/>
       <c r="J216" s="11" t="inlineStr">
         <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K216" s="11" t="inlineStr"/>
+          <t>HU100, B119[ILCO]</t>
+        </is>
+      </c>
+      <c r="K216" s="11" t="n"/>
       <c r="L216" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M216" s="11" t="inlineStr"/>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
+        </is>
+      </c>
+      <c r="M216" s="11" t="n"/>
       <c r="N216" s="11" t="inlineStr">
         <is>
-          <t>PEPS</t>
+          <t>PEPS[3세대]</t>
         </is>
       </c>
       <c r="O216" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962)</t>
-        </is>
-      </c>
-      <c r="P216" s="11" t="inlineStr"/>
+          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
+        </is>
+      </c>
+      <c r="P216" s="11" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
@@ -14905,12 +14848,12 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>타호 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C217" s="11" t="inlineStr">
         <is>
-          <t>2025(단종)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
@@ -14947,7 +14890,7 @@
       <c r="K217" s="11" t="inlineStr"/>
       <c r="L217" s="11" t="inlineStr">
         <is>
-          <t>13548442[4버튼], 13537962[6버튼], FCC YG0G21TB2</t>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M217" s="11" t="inlineStr"/>
@@ -14958,7 +14901,7 @@
       </c>
       <c r="O217" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), remotesandkeys.com(2023 타호 스마트키 13548442), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962), namu.wiki(2025.3.2 판매 종료)</t>
+          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
         </is>
       </c>
       <c r="P217" s="11" t="inlineStr"/>
@@ -14971,12 +14914,12 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>서버번 (쉐보레)</t>
+          <t>콜로라도 (쉐보레)</t>
         </is>
       </c>
       <c r="C218" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
@@ -14994,7 +14937,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G218" s="14" t="inlineStr">
+      <c r="G218" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -15013,750 +14956,24 @@
       <c r="K218" s="11" t="inlineStr"/>
       <c r="L218" s="11" t="inlineStr">
         <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
+          <t>13548441[3세대], FCC YG0G21TB2</t>
         </is>
       </c>
       <c r="M218" s="11" t="inlineStr"/>
-      <c r="N218" s="14" t="inlineStr">
+      <c r="N218" s="11" t="inlineStr">
         <is>
           <t>PEPS</t>
         </is>
       </c>
       <c r="O218" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P218" s="14" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B219" s="11" t="inlineStr">
-        <is>
-          <t>서버번 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C219" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D219" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G219" s="14" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H219" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I219" s="11" t="inlineStr"/>
-      <c r="J219" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K219" s="11" t="inlineStr"/>
-      <c r="L219" s="11" t="inlineStr">
-        <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M219" s="11" t="inlineStr"/>
-      <c r="N219" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O219" s="11" t="inlineStr">
-        <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P219" s="14" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B220" s="11" t="inlineStr">
-        <is>
-          <t>서버번 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C220" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D220" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G220" s="14" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H220" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I220" s="11" t="inlineStr"/>
-      <c r="J220" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K220" s="11" t="inlineStr"/>
-      <c r="L220" s="11" t="inlineStr">
-        <is>
-          <t>13537962[6버튼], 13548431[6버튼], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M220" s="11" t="inlineStr"/>
-      <c r="N220" s="14" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O220" s="11" t="inlineStr">
-        <is>
-          <t>abkeys.com·locksmithkeyless.com·royalkeysupply.com(YG0G21TB2 433MHz 스마트키 NXP HITAG-PRO ID49 128bit, CR2450), amazon(서버번·타호 2021-2025 YG0G21TB2 13537962/13548431), explorervan.co.kr(서버번 국내 판매 — 수입업체), namu.wiki(한국GM 도입 검토만)</t>
-        </is>
-      </c>
-      <c r="P220" s="14" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B221" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C221" s="11" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G221" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
-        </is>
-      </c>
-      <c r="H221" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I221" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J221" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K221" s="11" t="inlineStr"/>
-      <c r="L221" s="11" t="inlineStr"/>
-      <c r="M221" s="11" t="inlineStr"/>
-      <c r="N221" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
-        </is>
-      </c>
-      <c r="O221" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), edaily(콜로라도 2019.8 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P221" s="11" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B222" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C222" s="11" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D222" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G222" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
-        </is>
-      </c>
-      <c r="H222" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I222" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J222" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K222" s="11" t="inlineStr"/>
-      <c r="L222" s="11" t="inlineStr"/>
-      <c r="M222" s="11" t="inlineStr"/>
-      <c r="N222" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
-        </is>
-      </c>
-      <c r="O222" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
-        </is>
-      </c>
-      <c r="P222" s="11" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B223" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C223" s="11" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D223" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G223" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
-        </is>
-      </c>
-      <c r="H223" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I223" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J223" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K223" s="11" t="inlineStr"/>
-      <c r="L223" s="11" t="inlineStr"/>
-      <c r="M223" s="11" t="inlineStr"/>
-      <c r="N223" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
-        </is>
-      </c>
-      <c r="O223" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
-        </is>
-      </c>
-      <c r="P223" s="11" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B224" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C224" s="11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D224" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G224" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
-        </is>
-      </c>
-      <c r="H224" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I224" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J224" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K224" s="11" t="inlineStr"/>
-      <c r="L224" s="11" t="inlineStr"/>
-      <c r="M224" s="11" t="inlineStr"/>
-      <c r="N224" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
-        </is>
-      </c>
-      <c r="O224" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
-        </is>
-      </c>
-      <c r="P224" s="11" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B225" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C225" s="11" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D225" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G225" s="11" t="inlineStr">
-        <is>
-          <t>ID46[Extended]</t>
-        </is>
-      </c>
-      <c r="H225" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I225" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J225" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K225" s="11" t="inlineStr"/>
-      <c r="L225" s="11" t="inlineStr"/>
-      <c r="M225" s="11" t="inlineStr"/>
-      <c r="N225" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저</t>
-        </is>
-      </c>
-      <c r="O225" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리)</t>
-        </is>
-      </c>
-      <c r="P225" s="11" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B226" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C226" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G226" s="11" t="inlineStr">
-        <is>
-          <t>ID46[2세대, ~2024.4]</t>
-        </is>
-      </c>
-      <c r="H226" s="11" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I226" s="11" t="inlineStr">
-        <is>
-          <t>23209427[2세대]</t>
-        </is>
-      </c>
-      <c r="J226" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K226" s="11" t="n"/>
-      <c r="L226" s="11" t="n"/>
-      <c r="M226" s="11" t="n"/>
-      <c r="N226" s="11" t="inlineStr">
-        <is>
-          <t>트랜스폰더 이모빌라이저[2세대]</t>
-        </is>
-      </c>
-      <c r="O226" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
-        </is>
-      </c>
-      <c r="P226" s="11" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B227" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C227" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D227" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G227" s="11" t="inlineStr">
-        <is>
-          <t>ID49[3세대, 2024.7~]</t>
-        </is>
-      </c>
-      <c r="H227" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I227" s="11" t="n"/>
-      <c r="J227" s="11" t="inlineStr">
-        <is>
-          <t>HU100, B119[ILCO]</t>
-        </is>
-      </c>
-      <c r="K227" s="11" t="n"/>
-      <c r="L227" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M227" s="11" t="n"/>
-      <c r="N227" s="11" t="inlineStr">
-        <is>
-          <t>PEPS[3세대]</t>
-        </is>
-      </c>
-      <c r="O227" s="11" t="inlineStr">
-        <is>
-          <t>carandtruckremotes.com·oemcarkeymall.com(콜로라도 2015-2021 트랜스폰더 키 23209427 B119-PT ID46 HU100), coloradofans.com(2019 콜로라도 키 시동·리모컨 분리), royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49), autocast·jasonryu.net(3세대 올 뉴 콜로라도 2024.7.15 국내 출시), namu.wiki(2세대 2024.4 홈페이지 삭제)</t>
-        </is>
-      </c>
-      <c r="P227" s="11" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B228" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C228" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D228" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G228" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H228" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="inlineStr"/>
-      <c r="J228" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K228" s="11" t="inlineStr"/>
-      <c r="L228" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M228" s="11" t="inlineStr"/>
-      <c r="N228" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O228" s="11" t="inlineStr">
-        <is>
           <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
         </is>
       </c>
-      <c r="P228" s="11" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="11" t="inlineStr">
-        <is>
-          <t>쉐보레(GM대우)</t>
-        </is>
-      </c>
-      <c r="B229" s="11" t="inlineStr">
-        <is>
-          <t>콜로라도 (쉐보레)</t>
-        </is>
-      </c>
-      <c r="C229" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D229" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G229" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H229" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I229" s="11" t="inlineStr"/>
-      <c r="J229" s="11" t="inlineStr">
-        <is>
-          <t>HU100</t>
-        </is>
-      </c>
-      <c r="K229" s="11" t="inlineStr"/>
-      <c r="L229" s="11" t="inlineStr">
-        <is>
-          <t>13548441[3세대], FCC YG0G21TB2</t>
-        </is>
-      </c>
-      <c r="M229" s="11" t="inlineStr"/>
-      <c r="N229" s="11" t="inlineStr">
-        <is>
-          <t>PEPS</t>
-        </is>
-      </c>
-      <c r="O229" s="11" t="inlineStr">
-        <is>
-          <t>royalkeysupply.com·locksmithkeyless.com(2023-2025 콜로라도 스마트키 YG0G21TB2 13548441 Hitag Pro ID49)</t>
-        </is>
-      </c>
-      <c r="P229" s="11" t="inlineStr"/>
+      <c r="P218" s="11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P226"/>
+  <autoFilter ref="A1:P218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15767,401 +14984,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr"/>
+      <c r="A2" s="23" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>- 원본 목록 연식이 실제 국내 판매와 다른 모델은 실제 기준으로 적었습니다(마티즈Ⅱ 2000.8~, 매그너스 1999.12~2006.1, 레조 2000.1~2007.6, 크루즈 J300 ~2017.11, 올 뉴 크루즈 2017.1~, 볼트(Volt) 2세대 2016.8~2019.3, 임팔라 ~2020, G2X ~2008.9, 트랙스 ~2022.11, 이쿼녹스 ~2024.4, 트래버스·타호 ~2025.3, 콜로라도 3세대 2024.7~).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>- 캡티바 2세대(리뱃지)·이쿼녹스 EV는 국내에 출시되지 않아 '국내 미출시' 한 행만 남겼습니다(빨간색). 삭제할지 알려주세요.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>- 콜벳 C7·C8, 서버번은 한국GM 공식 판매 자료가 없고 수입업체 판매만 확인되어 주황색으로 표시했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 기아 파일 규칙을 따랐습니다: ID46·ID60(4D60) → O/O/O, ID49(Hitag Pro) → X/△/O, ID48(Megamos Crypto) → △/△/△, ID46·ID49 병기 → △/△/O. 실제 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>- 출처 칸은 해당 연식 검색에서 근거로 쓴 페이지입니다. 원문 페이지는 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr"/>
+      <c r="A14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가 또는 국내 미출시 — 마티즈Ⅱ(국내형 이모빌라이저 적용 자료 없음), 캡티바 2세대·이쿼녹스 EV(국내 미출시).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다르거나, 수출형 자료로 대신 채운 값 — 실물 키/VIN으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr"/>
+      <c r="A18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>- GM대우 국내형은 이모빌라이저가 없거나 트림/연식별로 달랐습니다: 올 뉴 마티즈 국내형 미적용, 마티즈 크리에이티브/스파크 M300은 2013년형까지 미적용·2014년형부터 이모빌라이저 폴딩키, 토스카는 2007년형(2006.11)부터 이모빌라이저 적용.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>- 칼로스·젠트라·레조·매그너스·라세티 J200은 국내형 적용 자료를 찾지 못해 같은 차의 수출형 자료로 채웠습니다: 칼로스/아베오 T250/타쿠마 ID48(DWO4R, TMPro 모듈113 대우 이모박스), 에반다(매그너스) ID48(DWO5), 라세티/옵트라 2004-2013 4D60(DWO4R).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>- 2011년 이후 쉐보레(아베오·크루즈·올란도·트랙스·말리부): 폴딩키 ID46 Hitag2(PCF7937/PCF7941E) HU100 433MHz, 이모빌라이저는 BCM 통합. 스마트키는 PCF7952 계열 ID46.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>- 2016년 이후 스마트키 HYQ4EA(433MHz, ID46): 말리부 9세대·카마로 6세대·올 뉴 크루즈·이쿼녹스·트래버스. HYQ4ES(ID46): 트레일블레이저·트랙스 크로스오버.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>- 2021년 이후 대형 SUV/픽업(타호·서버번·콜로라도 3세대)·콜벳 C8: Hitag Pro ID49(YG0G21TB2 / YG0G20TB1).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>- 콜로라도 2세대(2019~2024.4)는 버튼시동 없이 키 시동(트랜스폰더 키 23209427, B119/HU100, ID46), 3세대(2024.7~)부터 스마트키.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>- 트레일블레이저·트랙스 크로스오버는 LS 트림이 키 시동, LT 이상이 스마트키입니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n"/>
+      <c r="A27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="n"/>
+      <c r="A35" s="23" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="n"/>
+      <c r="A44" s="23" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>- 스파크 2013: 2013년형은 이모빌라이저 없음, 2014년형(2013.5.14 출시)부터 이모빌라이저 폴딩키 적용(나무위키 스파크 2세대·차프라이스 2013.5 가격표) — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>- 토스카 2006: 2007년형(2006.11 출시)부터 이모빌라이저 신규 적용(이투데이 "GM대우 2007년형 토스카 출시") — 전환기라 색 없음</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>- 서버번: 한국GM이 2024.10부터 국내 정식 판매(위키백과) — 2023년식 행 삭제. 키는 타호와 같은 스마트키(YG0G21TB2, 433MHz, ID49)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>- 캡티바 2세대·이쿼녹스 EV: 국내 미출시(이쿼녹스 EV는 2024.12 인증 후 출시 철회, EBN) — 행 삭제</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n"/>
+      <c r="A50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>- 스파크 M300 2014: GM 부품몰(c-mall) "스파크 2014년형 폴딩 키", 스파크 2012-2016 폴딩키 ID46(PCF7941E) 433MHz, 한국GM 블로그 "스파크S 폴딩키는 아베오·크루즈·알페온 키와 거의 같음" — 추정 해제</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>- 볼트(Volt) 2016-2019: 433MHz 스마트키 FCC HYQ4EA(13585728·13529638) = Philips ID46(locksmithkeyless) — 국내(433MHz) 사양과 같은 주파수 키로 확인</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>- 볼트 EV 2017-2021: 433MHz 스마트키 HYQ4EA ID46(2017-2022 볼트 적용), 미국형 315MHz는 HYQ4AA — 국내 433MHz 키 칩 ID46 확인</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>- 이쿼녹스 2023-2024: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 이쿼녹스 적용, 46E 칩), 미국형 315MHz HYQ4AS도 ID46 — 칩 ID46 확인</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>- 트래버스(2세대) 2021-2025: 433MHz 스마트키 HYQ4ES·HYQ4EA(2018-2024 트래버스 적용) ID46 — 국내 판매분(2025.3 종료)은 2세대</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>- 쉐보레(GM대우) 순정 키 번호: GM 한국 순정부품몰 gmplusmall.com 상품명(적용 차종·연식) — 마티즈 II 키 세트 96611858(경보기 미적용)·96611863(경보기 적용)·블랭크키 96611864(2003~2005)·리모콘 96567446(2003~2004), 올 뉴 마티즈 블랭크키 96601589·리모콘 96498848(2006~2009), 스파크 키(리모콘 미적용) 94823322·리모콘 95487768(2011~2013)·원격시동 95016182(2012~2013)·폴딩 42670241(2014~2015, CVT 제외)·42695008(스파크S CVT), 라세티 리모콘 96550512(2003~2005)·96499642(세단 무선시동, 2003~2007)·96458343·96458344(도난경보, 2006~2008), 매그너스 96438485(도난방지·무선시동)·토스카·매그너스 96327968(이모빌라이저 미적용)·토스카 96646269(이모빌라이저), 말리부 스마트키 13582828(2012~2013)·13586777(2014~2015)·폴딩 13582829(2012~2015), 알페온 폴딩 20972992(2011~2013)·23111355(2014~2015), 윈스톰 96628227(2007)·96870247(2008)·20760902(2009~2010), 캡티바 폴딩 42418198, 트랙스 폴딩 95076523(2012~2022), 볼트 EV 스마트키 13529642, 트래버스 스마트키 13532766(2020~2021)·13532767(2022~2023). 몰 표기 앞 글자 P·I는 몰 구분 기호라 뺌. 리모컨(분리형)은 기아·현대 파일과 같이 폴딩키 칸에 [리모콘]으로 기재. 판매 연식 밖 연식은 [추정]</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>- 6차 세대별 보완: 마티즈·스파크(M150~M300) DWO4R, 토스카(Epica) DWO5, 콜벳 C8 HU100, 스파크 2013 폴딩키 ID46(PCF7937E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>- 국내 미출시로 삭제: 콜벳 C7(한국GM 정식 수입 없음, 그레이 임포터 직수입만 — 콜벳 정식 수입은 C6까지), 콜벳 C8(국내 정식 출시 기록 없음) — 모터그래프·위키백과</t>
         </is>
       </c>
     </row>
